--- a/2026/ITALIA/ENERO/ENERO ITALIA.xlsx
+++ b/2026/ITALIA/ENERO/ENERO ITALIA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\2026\ITALIA\ENERO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2645FDE0-E29C-4B3F-AF92-AB1374F5F590}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C8954D6-8AB1-4205-9F5C-FF1D34558C02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="4" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="847" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="417">
   <si>
     <t xml:space="preserve">                                                            GRAL. PAZ 83/85 Pº 2 "B" - AVELLANEDA -CP 1870</t>
   </si>
@@ -1114,9 +1114,6 @@
     <t>PERÍODO: ENERO</t>
   </si>
   <si>
-    <t xml:space="preserve">EL 4F PAGO DOS VECES $86.950,32 (09/01 Y 24/01) - ADEMAS ABONO $5.065,32 EL 24 - 25 - 26 - 27 </t>
-  </si>
-  <si>
     <t>Haberes</t>
   </si>
   <si>
@@ -1272,11 +1269,6 @@
     <t>Silvana Valeria Arredondo - Braian Brito</t>
   </si>
   <si>
-    <t xml:space="preserve">
-● UF 71: transferencias sin identificar meses anteriores (noviembre y diciembre)
-</t>
-  </si>
-  <si>
     <t>Taiel Alejandro Biscarra</t>
   </si>
   <si>
@@ -1300,6 +1292,17 @@
   </si>
   <si>
     <t>Diferencia mes anterior Sueldo Sr. Cesar por atraso en traspaso de cuenta (INCLUYE SAC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+● UF 71: transferencias sin identificar meses anteriores (noviembre y diciembre)
+</t>
+  </si>
+  <si>
+    <t>EL 12A Y 12 B TIENE GASTOS (QUE PAGARON ELLOS ) PENDIENTES QUE LES PONGAMOS COMO INGRESO DEL ASCENSOR. DEBEMOS AGREGARLE $272.252 A CADA UNO</t>
+  </si>
+  <si>
+    <t>El 2C habia abonado el mes anterior $250.932,15 - Lo pusimos impago - Debe abonar $123.612,15.</t>
   </si>
 </sst>
 </file>
@@ -1576,7 +1579,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1646,6 +1649,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2204,7 +2219,7 @@
     </xf>
     <xf numFmtId="44" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="374">
+  <cellXfs count="384">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2778,159 +2793,6 @@
     <xf numFmtId="44" fontId="25" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2943,6 +2805,179 @@
     <xf numFmtId="44" fontId="27" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="30" fillId="13" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="13" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="13" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="13" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="31" fillId="13" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="14" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="14" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="14" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="31" fillId="14" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -3325,12 +3360,12 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="143"/>
-      <c r="B1" s="323" t="s">
+      <c r="B1" s="338" t="s">
         <v>333</v>
       </c>
-      <c r="C1" s="323"/>
-      <c r="D1" s="323"/>
-      <c r="E1" s="324"/>
+      <c r="C1" s="338"/>
+      <c r="D1" s="338"/>
+      <c r="E1" s="339"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="144"/>
@@ -3343,12 +3378,12 @@
     </row>
     <row r="3" spans="1:5" ht="51.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="144"/>
-      <c r="B3" s="325" t="s">
+      <c r="B3" s="334" t="s">
         <v>334</v>
       </c>
-      <c r="C3" s="325"/>
-      <c r="D3" s="325"/>
-      <c r="E3" s="326"/>
+      <c r="C3" s="334"/>
+      <c r="D3" s="334"/>
+      <c r="E3" s="335"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="147" t="s">
@@ -3386,49 +3421,49 @@
       <c r="E6" s="150"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="327" t="s">
+      <c r="B8" s="336" t="s">
         <v>356</v>
       </c>
-      <c r="C8" s="327"/>
+      <c r="C8" s="336"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="327"/>
-      <c r="C9" s="327"/>
+      <c r="B9" s="336"/>
+      <c r="C9" s="336"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="327"/>
-      <c r="C10" s="327"/>
+      <c r="B10" s="336"/>
+      <c r="C10" s="336"/>
     </row>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="328" t="s">
+      <c r="A13" s="337" t="s">
         <v>286</v>
       </c>
-      <c r="B13" s="328"/>
-      <c r="C13" s="328"/>
-      <c r="D13" s="328"/>
-      <c r="E13" s="328"/>
+      <c r="B13" s="337"/>
+      <c r="C13" s="337"/>
+      <c r="D13" s="337"/>
+      <c r="E13" s="337"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="328"/>
-      <c r="B14" s="328"/>
-      <c r="C14" s="328"/>
-      <c r="D14" s="328"/>
-      <c r="E14" s="328"/>
+      <c r="A14" s="337"/>
+      <c r="B14" s="337"/>
+      <c r="C14" s="337"/>
+      <c r="D14" s="337"/>
+      <c r="E14" s="337"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="328"/>
-      <c r="B15" s="328"/>
-      <c r="C15" s="328"/>
-      <c r="D15" s="328"/>
-      <c r="E15" s="328"/>
+      <c r="A15" s="337"/>
+      <c r="B15" s="337"/>
+      <c r="C15" s="337"/>
+      <c r="D15" s="337"/>
+      <c r="E15" s="337"/>
     </row>
     <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="328"/>
-      <c r="B16" s="328"/>
-      <c r="C16" s="328"/>
-      <c r="D16" s="328"/>
-      <c r="E16" s="328"/>
+      <c r="A16" s="337"/>
+      <c r="B16" s="337"/>
+      <c r="C16" s="337"/>
+      <c r="D16" s="337"/>
+      <c r="E16" s="337"/>
     </row>
     <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="18" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -3454,10 +3489,10 @@
       <c r="E21" s="160"/>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="321" t="s">
-        <v>359</v>
-      </c>
-      <c r="B22" s="322"/>
+      <c r="A22" s="332" t="s">
+        <v>358</v>
+      </c>
+      <c r="B22" s="333"/>
       <c r="C22" s="163"/>
       <c r="D22" s="285">
         <v>2182238</v>
@@ -3466,10 +3501,10 @@
       <c r="H22" s="164"/>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="321" t="s">
-        <v>360</v>
-      </c>
-      <c r="B23" s="322"/>
+      <c r="A23" s="332" t="s">
+        <v>359</v>
+      </c>
+      <c r="B23" s="333"/>
       <c r="C23" s="163"/>
       <c r="D23" s="285">
         <v>-474636.76</v>
@@ -3478,10 +3513,10 @@
       <c r="H23" s="164"/>
     </row>
     <row r="24" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="321" t="s">
-        <v>415</v>
-      </c>
-      <c r="B24" s="322"/>
+      <c r="A24" s="332" t="s">
+        <v>413</v>
+      </c>
+      <c r="B24" s="333"/>
       <c r="C24" s="163"/>
       <c r="D24" s="286">
         <v>1381383</v>
@@ -3490,10 +3525,10 @@
       <c r="H24" s="164"/>
     </row>
     <row r="25" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="321" t="s">
+      <c r="A25" s="332" t="s">
         <v>54</v>
       </c>
-      <c r="B25" s="322"/>
+      <c r="B25" s="333"/>
       <c r="C25" s="163"/>
       <c r="D25" s="286">
         <v>0.76</v>
@@ -3515,7 +3550,7 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="166" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B27" s="166"/>
       <c r="C27" s="166"/>
@@ -3524,7 +3559,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="163" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B28" s="163"/>
       <c r="C28" s="163"/>
@@ -3557,7 +3592,7 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="163" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B31" s="267"/>
       <c r="C31" s="267"/>
@@ -3565,7 +3600,7 @@
         <v>14015.68</v>
       </c>
       <c r="E31" s="278" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -3578,7 +3613,7 @@
         <v>1235711.01</v>
       </c>
       <c r="E32" s="278" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -3591,7 +3626,7 @@
         <v>225414.17</v>
       </c>
       <c r="E33" s="278" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -3653,29 +3688,29 @@
       <c r="E38" s="170"/>
     </row>
     <row r="39" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="318" t="s">
+      <c r="A39" s="329" t="s">
         <v>329</v>
       </c>
-      <c r="B39" s="319"/>
+      <c r="B39" s="330"/>
       <c r="C39" s="173"/>
-      <c r="D39" s="371">
+      <c r="D39" s="320">
         <v>313739</v>
       </c>
       <c r="E39" s="165" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="318" t="s">
+      <c r="A40" s="329" t="s">
         <v>330</v>
       </c>
-      <c r="B40" s="319"/>
+      <c r="B40" s="330"/>
       <c r="C40" s="173"/>
-      <c r="D40" s="372">
+      <c r="D40" s="321">
         <v>5204</v>
       </c>
       <c r="E40" s="165" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -3709,7 +3744,7 @@
         <v>29750.38</v>
       </c>
       <c r="E43" s="165" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3722,7 +3757,7 @@
         <v>15585.29</v>
       </c>
       <c r="E44" s="165" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3735,7 +3770,7 @@
         <v>578076.46</v>
       </c>
       <c r="E45" s="165" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3748,7 +3783,7 @@
         <v>312536.71999999997</v>
       </c>
       <c r="E46" s="165" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -3761,7 +3796,7 @@
         <v>10562.67</v>
       </c>
       <c r="E47" s="165" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -3774,16 +3809,16 @@
       <c r="E48" s="165"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="318" t="s">
+      <c r="A49" s="329" t="s">
         <v>294</v>
       </c>
-      <c r="B49" s="319"/>
+      <c r="B49" s="330"/>
       <c r="C49" s="178"/>
       <c r="D49" s="180">
         <v>3444706.16</v>
       </c>
       <c r="E49" s="278" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -3815,10 +3850,10 @@
       <c r="E52" s="185"/>
     </row>
     <row r="53" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="321" t="s">
-        <v>369</v>
-      </c>
-      <c r="B53" s="322"/>
+      <c r="A53" s="332" t="s">
+        <v>368</v>
+      </c>
+      <c r="B53" s="333"/>
       <c r="C53" s="178"/>
       <c r="D53" s="180">
         <v>0</v>
@@ -3826,34 +3861,34 @@
       <c r="E53" s="186"/>
     </row>
     <row r="54" spans="1:6" ht="156.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="321" t="s">
-        <v>412</v>
-      </c>
-      <c r="B54" s="322"/>
+      <c r="A54" s="332" t="s">
+        <v>410</v>
+      </c>
+      <c r="B54" s="333"/>
       <c r="C54" s="178"/>
       <c r="D54" s="180">
         <v>570000</v>
       </c>
-      <c r="E54" s="368" t="s">
-        <v>413</v>
+      <c r="E54" s="317" t="s">
+        <v>411</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="96.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="321" t="s">
-        <v>411</v>
-      </c>
-      <c r="B55" s="322"/>
+      <c r="A55" s="332" t="s">
+        <v>409</v>
+      </c>
+      <c r="B55" s="333"/>
       <c r="C55" s="178"/>
       <c r="D55" s="180">
         <v>950000</v>
       </c>
       <c r="E55" s="186" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="287" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B56" s="162"/>
       <c r="C56" s="178"/>
@@ -3862,68 +3897,68 @@
         <v>964820</v>
       </c>
       <c r="E56" s="186" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="321" t="s">
-        <v>414</v>
-      </c>
-      <c r="B57" s="322"/>
+      <c r="A57" s="332" t="s">
+        <v>412</v>
+      </c>
+      <c r="B57" s="333"/>
       <c r="C57" s="178"/>
       <c r="D57" s="180">
         <v>85000</v>
       </c>
       <c r="E57" s="186" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F57" s="205"/>
     </row>
     <row r="58" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="321" t="s">
-        <v>377</v>
-      </c>
-      <c r="B58" s="322"/>
+      <c r="A58" s="332" t="s">
+        <v>376</v>
+      </c>
+      <c r="B58" s="333"/>
       <c r="C58" s="178"/>
       <c r="D58" s="180">
         <v>85000</v>
       </c>
       <c r="E58" s="189" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F58" s="205"/>
     </row>
     <row r="59" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="321" t="s">
-        <v>379</v>
-      </c>
-      <c r="B59" s="322"/>
+      <c r="A59" s="332" t="s">
+        <v>378</v>
+      </c>
+      <c r="B59" s="333"/>
       <c r="C59" s="178"/>
       <c r="D59" s="180">
         <v>150000</v>
       </c>
       <c r="E59" s="189" t="s">
+        <v>379</v>
+      </c>
+      <c r="F59" s="205"/>
+    </row>
+    <row r="60" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="332" t="s">
         <v>380</v>
       </c>
-      <c r="F59" s="205"/>
-    </row>
-    <row r="60" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="321" t="s">
-        <v>381</v>
-      </c>
-      <c r="B60" s="322"/>
+      <c r="B60" s="333"/>
       <c r="C60" s="178"/>
       <c r="D60" s="180">
         <v>250000</v>
       </c>
       <c r="E60" s="189" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="F60" s="205"/>
     </row>
     <row r="61" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="287" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B61" s="162"/>
       <c r="C61" s="178"/>
@@ -3937,7 +3972,7 @@
     </row>
     <row r="62" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="287" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B62" s="162"/>
       <c r="C62" s="178"/>
@@ -3945,13 +3980,13 @@
         <v>1820000</v>
       </c>
       <c r="E62" s="189" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F62" s="205"/>
     </row>
     <row r="63" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="287" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B63" s="162"/>
       <c r="C63" s="178"/>
@@ -3959,13 +3994,13 @@
         <v>3000000</v>
       </c>
       <c r="E63" s="189" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F63" s="205"/>
     </row>
     <row r="64" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="287" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B64" s="162"/>
       <c r="C64" s="178"/>
@@ -3973,21 +4008,21 @@
         <v>256900</v>
       </c>
       <c r="E64" s="189" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F64" s="205"/>
     </row>
     <row r="65" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="321" t="s">
-        <v>376</v>
-      </c>
-      <c r="B65" s="322"/>
+      <c r="A65" s="332" t="s">
+        <v>375</v>
+      </c>
+      <c r="B65" s="333"/>
       <c r="C65" s="178"/>
       <c r="D65" s="180">
         <v>303033.69</v>
       </c>
       <c r="E65" s="189" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
@@ -4012,10 +4047,10 @@
       <c r="E67" s="160"/>
     </row>
     <row r="68" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="321" t="s">
-        <v>387</v>
-      </c>
-      <c r="B68" s="322"/>
+      <c r="A68" s="332" t="s">
+        <v>386</v>
+      </c>
+      <c r="B68" s="333"/>
       <c r="C68" s="163"/>
       <c r="D68" s="285">
         <v>650000</v>
@@ -4023,10 +4058,10 @@
       <c r="E68" s="189"/>
     </row>
     <row r="69" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="321" t="s">
-        <v>388</v>
-      </c>
-      <c r="B69" s="322"/>
+      <c r="A69" s="332" t="s">
+        <v>387</v>
+      </c>
+      <c r="B69" s="333"/>
       <c r="C69" s="163"/>
       <c r="D69" s="285">
         <v>650000</v>
@@ -4035,7 +4070,7 @@
     </row>
     <row r="70" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="161" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B70" s="162"/>
       <c r="C70" s="163"/>
@@ -4043,12 +4078,12 @@
         <v>95200</v>
       </c>
       <c r="E70" s="189" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="161" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B71" s="162"/>
       <c r="C71" s="163"/>
@@ -4056,12 +4091,12 @@
         <v>60000</v>
       </c>
       <c r="E71" s="189" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="161" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B72" s="162"/>
       <c r="C72" s="163"/>
@@ -4069,12 +4104,12 @@
         <v>42350</v>
       </c>
       <c r="E72" s="189" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="161" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B73" s="162"/>
       <c r="C73" s="163"/>
@@ -4082,12 +4117,12 @@
         <v>100000</v>
       </c>
       <c r="E73" s="189" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="287" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B74" s="162"/>
       <c r="C74" s="163"/>
@@ -4095,7 +4130,7 @@
         <v>70000</v>
       </c>
       <c r="E74" s="189" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
@@ -4147,7 +4182,7 @@
       </c>
       <c r="B79" s="270"/>
       <c r="C79" s="270"/>
-      <c r="D79" s="370">
+      <c r="D79" s="319">
         <v>45000</v>
       </c>
       <c r="E79" s="193"/>
@@ -4158,7 +4193,7 @@
       </c>
       <c r="B80" s="270"/>
       <c r="C80" s="270"/>
-      <c r="D80" s="370">
+      <c r="D80" s="319">
         <f>218314.23-14061</f>
         <v>204253.23</v>
       </c>
@@ -4238,8 +4273,8 @@
       <c r="E89" s="215"/>
     </row>
     <row r="90" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="321"/>
-      <c r="B90" s="322"/>
+      <c r="A90" s="332"/>
+      <c r="B90" s="333"/>
       <c r="C90" s="178"/>
       <c r="D90" s="187"/>
       <c r="E90" s="215"/>
@@ -4329,14 +4364,14 @@
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A105" s="320" t="s">
-        <v>391</v>
-      </c>
-      <c r="B105" s="320"/>
+      <c r="A105" s="331" t="s">
+        <v>390</v>
+      </c>
+      <c r="B105" s="331"/>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A106" s="320"/>
-      <c r="B106" s="320"/>
+      <c r="A106" s="331"/>
+      <c r="B106" s="331"/>
     </row>
     <row r="107" spans="1:6" s="226" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107"/>
@@ -4375,7 +4410,7 @@
     </row>
     <row r="111" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="173" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B111" s="304">
         <v>-123000</v>
@@ -4384,7 +4419,7 @@
     </row>
     <row r="112" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="173" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B112" s="305">
         <v>-3689.2069499999998</v>
@@ -4393,7 +4428,7 @@
     </row>
     <row r="113" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="173" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B113" s="305">
         <v>-130000</v>
@@ -4402,7 +4437,7 @@
     </row>
     <row r="114" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="173" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B114" s="303">
         <v>-99011.93</v>
@@ -4421,9 +4456,9 @@
     </row>
     <row r="116" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A116" s="231" t="s">
-        <v>364</v>
-      </c>
-      <c r="B116" s="369">
+        <v>363</v>
+      </c>
+      <c r="B116" s="318">
         <v>122500</v>
       </c>
       <c r="F116" s="224"/>
@@ -4442,20 +4477,20 @@
     </row>
     <row r="118" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="119" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A119" s="317" t="s">
+      <c r="A119" s="328" t="s">
         <v>309</v>
       </c>
-      <c r="B119" s="317"/>
-      <c r="C119" s="317"/>
+      <c r="B119" s="328"/>
+      <c r="C119" s="328"/>
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A120" s="317"/>
-      <c r="B120" s="317"/>
-      <c r="C120" s="317"/>
+      <c r="A120" s="328"/>
+      <c r="B120" s="328"/>
+      <c r="C120" s="328"/>
     </row>
     <row r="121" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="234" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B121" s="316">
         <v>3400</v>
@@ -4465,7 +4500,7 @@
     </row>
     <row r="122" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="234" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B122" s="316">
         <v>110000</v>
@@ -4493,18 +4528,11 @@
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="A68:B68"/>
-    <mergeCell ref="A90:B90"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B8:C10"/>
     <mergeCell ref="A13:E16"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A58:B58"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="A60:B60"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="A69:B69"/>
-    <mergeCell ref="A55:B55"/>
     <mergeCell ref="A119:C120"/>
     <mergeCell ref="A40:B40"/>
     <mergeCell ref="A105:B106"/>
@@ -4512,6 +4540,13 @@
     <mergeCell ref="A53:B53"/>
     <mergeCell ref="A57:B57"/>
     <mergeCell ref="A65:B65"/>
+    <mergeCell ref="A90:B90"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="A55:B55"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="5" orientation="portrait" r:id="rId1"/>
@@ -4545,14 +4580,14 @@
       <c r="A1" s="288"/>
       <c r="B1" s="289"/>
       <c r="C1" s="289"/>
-      <c r="D1" s="336"/>
-      <c r="E1" s="336"/>
-      <c r="F1" s="336"/>
-      <c r="G1" s="336"/>
-      <c r="H1" s="336"/>
-      <c r="I1" s="336"/>
-      <c r="J1" s="336"/>
-      <c r="K1" s="336"/>
+      <c r="D1" s="340"/>
+      <c r="E1" s="340"/>
+      <c r="F1" s="340"/>
+      <c r="G1" s="340"/>
+      <c r="H1" s="340"/>
+      <c r="I1" s="340"/>
+      <c r="J1" s="340"/>
+      <c r="K1" s="340"/>
       <c r="L1" s="290"/>
     </row>
     <row r="2" spans="1:14" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -4562,10 +4597,10 @@
       <c r="D2" s="293" t="s">
         <v>310</v>
       </c>
-      <c r="E2" s="357">
+      <c r="E2" s="363">
         <v>3000000</v>
       </c>
-      <c r="F2" s="357"/>
+      <c r="F2" s="363"/>
       <c r="G2" s="293"/>
       <c r="H2" s="293"/>
       <c r="I2" s="293" t="s">
@@ -4594,167 +4629,167 @@
       <c r="M3" s="240"/>
     </row>
     <row r="4" spans="1:14" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="337" t="s">
+      <c r="A4" s="341" t="s">
         <v>352</v>
       </c>
-      <c r="B4" s="338"/>
-      <c r="C4" s="338"/>
-      <c r="D4" s="338"/>
-      <c r="E4" s="338"/>
-      <c r="F4" s="338"/>
-      <c r="G4" s="338"/>
-      <c r="H4" s="338"/>
-      <c r="I4" s="338"/>
-      <c r="J4" s="338"/>
-      <c r="K4" s="338"/>
-      <c r="L4" s="339"/>
+      <c r="B4" s="342"/>
+      <c r="C4" s="342"/>
+      <c r="D4" s="342"/>
+      <c r="E4" s="342"/>
+      <c r="F4" s="342"/>
+      <c r="G4" s="342"/>
+      <c r="H4" s="342"/>
+      <c r="I4" s="342"/>
+      <c r="J4" s="342"/>
+      <c r="K4" s="342"/>
+      <c r="L4" s="343"/>
       <c r="M4" s="240"/>
     </row>
     <row r="5" spans="1:14" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="340"/>
-      <c r="B5" s="341"/>
-      <c r="C5" s="341"/>
-      <c r="D5" s="341"/>
-      <c r="E5" s="341"/>
-      <c r="F5" s="341"/>
-      <c r="G5" s="341"/>
-      <c r="H5" s="341"/>
-      <c r="I5" s="341"/>
-      <c r="J5" s="341"/>
-      <c r="K5" s="341"/>
-      <c r="L5" s="342"/>
+      <c r="A5" s="344"/>
+      <c r="B5" s="345"/>
+      <c r="C5" s="345"/>
+      <c r="D5" s="345"/>
+      <c r="E5" s="345"/>
+      <c r="F5" s="345"/>
+      <c r="G5" s="345"/>
+      <c r="H5" s="345"/>
+      <c r="I5" s="345"/>
+      <c r="J5" s="345"/>
+      <c r="K5" s="345"/>
+      <c r="L5" s="346"/>
       <c r="M5" s="240"/>
     </row>
     <row r="6" spans="1:14" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="340"/>
-      <c r="B6" s="341"/>
-      <c r="C6" s="341"/>
-      <c r="D6" s="341"/>
-      <c r="E6" s="341"/>
-      <c r="F6" s="341"/>
-      <c r="G6" s="341"/>
-      <c r="H6" s="341"/>
-      <c r="I6" s="341"/>
-      <c r="J6" s="341"/>
-      <c r="K6" s="341"/>
-      <c r="L6" s="342"/>
+      <c r="A6" s="344"/>
+      <c r="B6" s="345"/>
+      <c r="C6" s="345"/>
+      <c r="D6" s="345"/>
+      <c r="E6" s="345"/>
+      <c r="F6" s="345"/>
+      <c r="G6" s="345"/>
+      <c r="H6" s="345"/>
+      <c r="I6" s="345"/>
+      <c r="J6" s="345"/>
+      <c r="K6" s="345"/>
+      <c r="L6" s="346"/>
       <c r="M6" s="240"/>
     </row>
     <row r="7" spans="1:14" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="340"/>
-      <c r="B7" s="341"/>
-      <c r="C7" s="341"/>
-      <c r="D7" s="341"/>
-      <c r="E7" s="341"/>
-      <c r="F7" s="341"/>
-      <c r="G7" s="341"/>
-      <c r="H7" s="341"/>
-      <c r="I7" s="341"/>
-      <c r="J7" s="341"/>
-      <c r="K7" s="341"/>
-      <c r="L7" s="342"/>
+      <c r="A7" s="344"/>
+      <c r="B7" s="345"/>
+      <c r="C7" s="345"/>
+      <c r="D7" s="345"/>
+      <c r="E7" s="345"/>
+      <c r="F7" s="345"/>
+      <c r="G7" s="345"/>
+      <c r="H7" s="345"/>
+      <c r="I7" s="345"/>
+      <c r="J7" s="345"/>
+      <c r="K7" s="345"/>
+      <c r="L7" s="346"/>
       <c r="M7" s="240"/>
     </row>
     <row r="8" spans="1:14" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="343"/>
-      <c r="B8" s="344"/>
-      <c r="C8" s="344"/>
-      <c r="D8" s="344"/>
-      <c r="E8" s="344"/>
-      <c r="F8" s="344"/>
-      <c r="G8" s="344"/>
-      <c r="H8" s="344"/>
-      <c r="I8" s="344"/>
-      <c r="J8" s="344"/>
-      <c r="K8" s="344"/>
-      <c r="L8" s="345"/>
+      <c r="A8" s="347"/>
+      <c r="B8" s="348"/>
+      <c r="C8" s="348"/>
+      <c r="D8" s="348"/>
+      <c r="E8" s="348"/>
+      <c r="F8" s="348"/>
+      <c r="G8" s="348"/>
+      <c r="H8" s="348"/>
+      <c r="I8" s="348"/>
+      <c r="J8" s="348"/>
+      <c r="K8" s="348"/>
+      <c r="L8" s="349"/>
     </row>
     <row r="9" spans="1:14" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="351" t="s">
+      <c r="A9" s="357" t="s">
         <v>350</v>
       </c>
-      <c r="B9" s="352"/>
-      <c r="C9" s="352"/>
-      <c r="D9" s="352"/>
-      <c r="E9" s="352"/>
-      <c r="F9" s="352"/>
-      <c r="G9" s="352"/>
-      <c r="H9" s="352"/>
-      <c r="I9" s="352"/>
-      <c r="J9" s="352"/>
-      <c r="K9" s="352"/>
-      <c r="L9" s="353"/>
+      <c r="B9" s="358"/>
+      <c r="C9" s="358"/>
+      <c r="D9" s="358"/>
+      <c r="E9" s="358"/>
+      <c r="F9" s="358"/>
+      <c r="G9" s="358"/>
+      <c r="H9" s="358"/>
+      <c r="I9" s="358"/>
+      <c r="J9" s="358"/>
+      <c r="K9" s="358"/>
+      <c r="L9" s="359"/>
     </row>
     <row r="10" spans="1:14" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="354" t="s">
+      <c r="A10" s="360" t="s">
         <v>351</v>
       </c>
-      <c r="B10" s="355"/>
-      <c r="C10" s="355"/>
-      <c r="D10" s="355"/>
-      <c r="E10" s="355"/>
-      <c r="F10" s="355"/>
-      <c r="G10" s="355"/>
-      <c r="H10" s="355"/>
-      <c r="I10" s="355"/>
-      <c r="J10" s="355"/>
-      <c r="K10" s="355"/>
-      <c r="L10" s="356"/>
+      <c r="B10" s="361"/>
+      <c r="C10" s="361"/>
+      <c r="D10" s="361"/>
+      <c r="E10" s="361"/>
+      <c r="F10" s="361"/>
+      <c r="G10" s="361"/>
+      <c r="H10" s="361"/>
+      <c r="I10" s="361"/>
+      <c r="J10" s="361"/>
+      <c r="K10" s="361"/>
+      <c r="L10" s="362"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="346" t="s">
+      <c r="A11" s="350" t="s">
         <v>312</v>
       </c>
-      <c r="B11" s="346" t="s">
+      <c r="B11" s="350" t="s">
         <v>313</v>
       </c>
-      <c r="C11" s="346" t="s">
+      <c r="C11" s="350" t="s">
         <v>314</v>
       </c>
-      <c r="D11" s="346" t="s">
+      <c r="D11" s="350" t="s">
         <v>315</v>
       </c>
-      <c r="E11" s="329" t="s">
+      <c r="E11" s="353" t="s">
         <v>316</v>
       </c>
-      <c r="F11" s="346" t="s">
+      <c r="F11" s="350" t="s">
         <v>317</v>
       </c>
-      <c r="G11" s="349" t="s">
+      <c r="G11" s="355" t="s">
         <v>318</v>
       </c>
-      <c r="H11" s="329" t="s">
+      <c r="H11" s="353" t="s">
         <v>319</v>
       </c>
-      <c r="I11" s="329" t="s">
+      <c r="I11" s="353" t="s">
         <v>311</v>
       </c>
-      <c r="J11" s="331" t="s">
+      <c r="J11" s="364" t="s">
         <v>310</v>
       </c>
       <c r="K11" s="241" t="s">
         <v>320</v>
       </c>
-      <c r="L11" s="333" t="s">
+      <c r="L11" s="366" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="347"/>
-      <c r="B12" s="347"/>
-      <c r="C12" s="348"/>
-      <c r="D12" s="347"/>
-      <c r="E12" s="330"/>
-      <c r="F12" s="347"/>
-      <c r="G12" s="350"/>
-      <c r="H12" s="330"/>
-      <c r="I12" s="330"/>
-      <c r="J12" s="332"/>
+      <c r="A12" s="351"/>
+      <c r="B12" s="351"/>
+      <c r="C12" s="352"/>
+      <c r="D12" s="351"/>
+      <c r="E12" s="354"/>
+      <c r="F12" s="351"/>
+      <c r="G12" s="356"/>
+      <c r="H12" s="354"/>
+      <c r="I12" s="354"/>
+      <c r="J12" s="365"/>
       <c r="K12" s="242" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 16/02</v>
       </c>
-      <c r="L12" s="334"/>
+      <c r="L12" s="367"/>
     </row>
     <row r="13" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="243">
@@ -4848,7 +4883,7 @@
         <v>0.02</v>
       </c>
       <c r="N14" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -5411,22 +5446,20 @@
       </c>
     </row>
     <row r="27" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="243">
+      <c r="A27" s="379">
         <v>15</v>
       </c>
-      <c r="B27" s="243" t="s">
+      <c r="B27" s="379" t="s">
         <v>140</v>
       </c>
-      <c r="C27" s="251"/>
-      <c r="D27" s="244">
+      <c r="C27" s="380"/>
+      <c r="D27" s="381">
         <v>0.82</v>
       </c>
-      <c r="E27" s="245">
+      <c r="E27" s="382">
         <v>250932.15</v>
       </c>
-      <c r="F27" s="246">
-        <v>0</v>
-      </c>
+      <c r="F27" s="246"/>
       <c r="G27" s="247">
         <f t="shared" si="0"/>
         <v>250932.15</v>
@@ -7793,7 +7826,7 @@
       <c r="E77" s="245">
         <v>833728.65</v>
       </c>
-      <c r="F77" s="373">
+      <c r="F77" s="322">
         <v>99011.93</v>
       </c>
       <c r="G77" s="247">
@@ -7825,7 +7858,7 @@
         <v>0.65000000000000036</v>
       </c>
       <c r="N77" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
@@ -8064,7 +8097,7 @@
         <v>0.7000000000000004</v>
       </c>
       <c r="N82" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.25">
@@ -8587,7 +8620,7 @@
         <v>0.8100000000000005</v>
       </c>
       <c r="N93" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.25">
@@ -8639,18 +8672,18 @@
       </c>
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A95" s="252">
+      <c r="A95" s="323">
         <f t="shared" si="9"/>
         <v>83</v>
       </c>
-      <c r="B95" s="254" t="s">
+      <c r="B95" s="324" t="s">
         <v>207</v>
       </c>
-      <c r="C95" s="251"/>
-      <c r="D95" s="244">
+      <c r="C95" s="325"/>
+      <c r="D95" s="326">
         <v>1.35</v>
       </c>
-      <c r="E95" s="245">
+      <c r="E95" s="327">
         <v>413120.83</v>
       </c>
       <c r="F95" s="246">
@@ -8686,18 +8719,18 @@
       </c>
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A96" s="252">
+      <c r="A96" s="323">
         <f t="shared" si="9"/>
         <v>84</v>
       </c>
-      <c r="B96" s="254" t="s">
+      <c r="B96" s="324" t="s">
         <v>208</v>
       </c>
-      <c r="C96" s="251"/>
-      <c r="D96" s="244">
+      <c r="C96" s="325"/>
+      <c r="D96" s="326">
         <v>1.1200000000000001</v>
       </c>
-      <c r="E96" s="245">
+      <c r="E96" s="327">
         <v>342737.84</v>
       </c>
       <c r="F96" s="246">
@@ -8749,7 +8782,7 @@
         <v>123612.85</v>
       </c>
       <c r="F97" s="246">
-        <f t="shared" ref="F97:F113" si="22">E97</f>
+        <f t="shared" ref="F97:F112" si="22">E97</f>
         <v>123612.85</v>
       </c>
       <c r="G97" s="247">
@@ -9210,7 +9243,7 @@
         <v>95</v>
       </c>
       <c r="B107" s="254" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C107" s="251"/>
       <c r="D107" s="244">
@@ -9592,7 +9625,7 @@
         <v>103</v>
       </c>
       <c r="B115" s="254" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C115" s="251"/>
       <c r="D115" s="244">
@@ -9695,85 +9728,81 @@
     </row>
     <row r="119" spans="1:13" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="120" spans="1:13" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B120" s="335" t="s">
+      <c r="B120" s="368" t="s">
         <v>286</v>
       </c>
-      <c r="C120" s="335"/>
-      <c r="D120" s="335"/>
-      <c r="E120" s="335"/>
-      <c r="F120" s="335"/>
-      <c r="G120" s="335"/>
-      <c r="H120" s="335"/>
-      <c r="I120" s="335"/>
-      <c r="J120" s="335"/>
-      <c r="K120" s="335"/>
+      <c r="C120" s="368"/>
+      <c r="D120" s="368"/>
+      <c r="E120" s="368"/>
+      <c r="F120" s="368"/>
+      <c r="G120" s="368"/>
+      <c r="H120" s="368"/>
+      <c r="I120" s="368"/>
+      <c r="J120" s="368"/>
+      <c r="K120" s="368"/>
     </row>
     <row r="121" spans="1:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B121" s="335"/>
-      <c r="C121" s="335"/>
-      <c r="D121" s="335"/>
-      <c r="E121" s="335"/>
-      <c r="F121" s="335"/>
-      <c r="G121" s="335"/>
-      <c r="H121" s="335"/>
-      <c r="I121" s="335"/>
-      <c r="J121" s="335"/>
-      <c r="K121" s="335"/>
+      <c r="B121" s="368"/>
+      <c r="C121" s="368"/>
+      <c r="D121" s="368"/>
+      <c r="E121" s="368"/>
+      <c r="F121" s="368"/>
+      <c r="G121" s="368"/>
+      <c r="H121" s="368"/>
+      <c r="I121" s="368"/>
+      <c r="J121" s="368"/>
+      <c r="K121" s="368"/>
     </row>
     <row r="122" spans="1:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B122" s="335"/>
-      <c r="C122" s="335"/>
-      <c r="D122" s="335"/>
-      <c r="E122" s="335"/>
-      <c r="F122" s="335"/>
-      <c r="G122" s="335"/>
-      <c r="H122" s="335"/>
-      <c r="I122" s="335"/>
-      <c r="J122" s="335"/>
-      <c r="K122" s="335"/>
+      <c r="B122" s="368"/>
+      <c r="C122" s="368"/>
+      <c r="D122" s="368"/>
+      <c r="E122" s="368"/>
+      <c r="F122" s="368"/>
+      <c r="G122" s="368"/>
+      <c r="H122" s="368"/>
+      <c r="I122" s="368"/>
+      <c r="J122" s="368"/>
+      <c r="K122" s="368"/>
     </row>
     <row r="123" spans="1:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B123" s="335"/>
-      <c r="C123" s="335"/>
-      <c r="D123" s="335"/>
-      <c r="E123" s="335"/>
-      <c r="F123" s="335"/>
-      <c r="G123" s="335"/>
-      <c r="H123" s="335"/>
-      <c r="I123" s="335"/>
-      <c r="J123" s="335"/>
-      <c r="K123" s="335"/>
+      <c r="B123" s="368"/>
+      <c r="C123" s="368"/>
+      <c r="D123" s="368"/>
+      <c r="E123" s="368"/>
+      <c r="F123" s="368"/>
+      <c r="G123" s="368"/>
+      <c r="H123" s="368"/>
+      <c r="I123" s="368"/>
+      <c r="J123" s="368"/>
+      <c r="K123" s="368"/>
     </row>
     <row r="124" spans="1:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B124" s="335"/>
-      <c r="C124" s="335"/>
-      <c r="D124" s="335"/>
-      <c r="E124" s="335"/>
-      <c r="F124" s="335"/>
-      <c r="G124" s="335"/>
-      <c r="H124" s="335"/>
-      <c r="I124" s="335"/>
-      <c r="J124" s="335"/>
-      <c r="K124" s="335"/>
+      <c r="B124" s="368"/>
+      <c r="C124" s="368"/>
+      <c r="D124" s="368"/>
+      <c r="E124" s="368"/>
+      <c r="F124" s="368"/>
+      <c r="G124" s="368"/>
+      <c r="H124" s="368"/>
+      <c r="I124" s="368"/>
+      <c r="J124" s="368"/>
+      <c r="K124" s="368"/>
     </row>
     <row r="125" spans="1:13" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B125" s="335"/>
-      <c r="C125" s="335"/>
-      <c r="D125" s="335"/>
-      <c r="E125" s="335"/>
-      <c r="F125" s="335"/>
-      <c r="G125" s="335"/>
-      <c r="H125" s="335"/>
-      <c r="I125" s="335"/>
-      <c r="J125" s="335"/>
-      <c r="K125" s="335"/>
+      <c r="B125" s="368"/>
+      <c r="C125" s="368"/>
+      <c r="D125" s="368"/>
+      <c r="E125" s="368"/>
+      <c r="F125" s="368"/>
+      <c r="G125" s="368"/>
+      <c r="H125" s="368"/>
+      <c r="I125" s="368"/>
+      <c r="J125" s="368"/>
+      <c r="K125" s="368"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="L11:L12"/>
     <mergeCell ref="B120:K125"/>
     <mergeCell ref="D1:K1"/>
     <mergeCell ref="A4:L8"/>
@@ -9787,6 +9816,10 @@
     <mergeCell ref="H11:H12"/>
     <mergeCell ref="A9:L9"/>
     <mergeCell ref="A10:L10"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="L11:L12"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
@@ -9795,31 +9828,36 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56D35F41-74CB-4294-A7A2-EC3C67574818}">
-  <dimension ref="B4:M6"/>
+  <dimension ref="B4:M9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="6" spans="2:13" ht="183.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="358" t="s">
-        <v>408</v>
-      </c>
-      <c r="C6" s="358"/>
-      <c r="D6" s="358"/>
-      <c r="E6" s="358"/>
-      <c r="F6" s="358"/>
-      <c r="G6" s="358"/>
-      <c r="H6" s="358"/>
-      <c r="I6" s="358"/>
-      <c r="J6" s="358"/>
+    <row r="4" spans="2:13" ht="165" x14ac:dyDescent="0.25">
+      <c r="B4" s="226" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="369" t="s">
+        <v>415</v>
+      </c>
+      <c r="C6" s="369"/>
+      <c r="D6" s="369"/>
+      <c r="E6" s="369"/>
+      <c r="F6" s="369"/>
+      <c r="G6" s="369"/>
+      <c r="H6" s="369"/>
+      <c r="I6" s="369"/>
+      <c r="J6" s="369"/>
       <c r="L6" s="226" t="s">
+        <v>401</v>
+      </c>
+      <c r="M6" s="226" t="s">
         <v>402</v>
       </c>
-      <c r="M6" s="226" t="s">
-        <v>403</v>
+    </row>
+    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B9" s="383" t="s">
+        <v>416</v>
       </c>
     </row>
   </sheetData>
@@ -9849,11 +9887,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="359" t="s">
+      <c r="A1" s="370" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="359"/>
-      <c r="C1" s="359"/>
+      <c r="B1" s="370"/>
+      <c r="C1" s="370"/>
       <c r="I1" s="40"/>
       <c r="J1" s="40" t="s">
         <v>20</v>
@@ -9868,9 +9906,9 @@
       <c r="R1" s="40"/>
     </row>
     <row r="2" spans="1:18" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="359"/>
-      <c r="B2" s="359"/>
-      <c r="C2" s="359"/>
+      <c r="A2" s="370"/>
+      <c r="B2" s="370"/>
+      <c r="C2" s="370"/>
       <c r="J2" t="s">
         <v>20</v>
       </c>
@@ -9882,10 +9920,10 @@
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
       <c r="D3" s="1"/>
-      <c r="E3" s="360" t="s">
+      <c r="E3" s="371" t="s">
         <v>49</v>
       </c>
-      <c r="F3" s="361"/>
+      <c r="F3" s="372"/>
       <c r="G3" s="1"/>
       <c r="J3" t="s">
         <v>20</v>
@@ -12377,22 +12415,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="362" t="s">
+      <c r="B1" s="373" t="s">
         <v>124</v>
       </c>
-      <c r="C1" s="363"/>
-      <c r="D1" s="363"/>
-      <c r="E1" s="363"/>
-      <c r="F1" s="363"/>
-      <c r="G1" s="363"/>
-      <c r="H1" s="363"/>
-      <c r="I1" s="363"/>
-      <c r="J1" s="363"/>
-      <c r="K1" s="363"/>
-      <c r="L1" s="363"/>
-      <c r="M1" s="363"/>
-      <c r="N1" s="363"/>
-      <c r="O1" s="364"/>
+      <c r="C1" s="374"/>
+      <c r="D1" s="374"/>
+      <c r="E1" s="374"/>
+      <c r="F1" s="374"/>
+      <c r="G1" s="374"/>
+      <c r="H1" s="374"/>
+      <c r="I1" s="374"/>
+      <c r="J1" s="374"/>
+      <c r="K1" s="374"/>
+      <c r="L1" s="374"/>
+      <c r="M1" s="374"/>
+      <c r="N1" s="374"/>
+      <c r="O1" s="375"/>
       <c r="P1" t="s">
         <v>20</v>
       </c>
@@ -12409,15 +12447,15 @@
       </c>
     </row>
     <row r="3" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="365" t="s">
+      <c r="B3" s="376" t="s">
         <v>273</v>
       </c>
-      <c r="C3" s="366"/>
-      <c r="D3" s="366"/>
-      <c r="E3" s="366"/>
-      <c r="F3" s="366"/>
-      <c r="G3" s="366"/>
-      <c r="H3" s="366"/>
+      <c r="C3" s="377"/>
+      <c r="D3" s="377"/>
+      <c r="E3" s="377"/>
+      <c r="F3" s="377"/>
+      <c r="G3" s="377"/>
+      <c r="H3" s="377"/>
       <c r="I3" s="31">
         <v>6905337</v>
       </c>
@@ -17798,10 +17836,10 @@
       </c>
     </row>
     <row r="111" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C111" s="367" t="s">
-        <v>20</v>
-      </c>
-      <c r="D111" s="367"/>
+      <c r="C111" s="378" t="s">
+        <v>20</v>
+      </c>
+      <c r="D111" s="378"/>
       <c r="E111" s="99"/>
       <c r="G111" s="12" t="s">
         <v>20</v>

--- a/2026/ITALIA/ENERO/ENERO ITALIA.xlsx
+++ b/2026/ITALIA/ENERO/ENERO ITALIA.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\2026\ITALIA\ENERO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\ITALIA\ENERO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C8954D6-8AB1-4205-9F5C-FF1D34558C02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1BAA8A1-0C3E-4856-8A87-74B680801914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="4" r:id="rId1"/>
@@ -21,14 +21,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$L$125</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$124</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$123</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="423">
   <si>
     <t xml:space="preserve">                                                            GRAL. PAZ 83/85 Pº 2 "B" - AVELLANEDA -CP 1870</t>
   </si>
@@ -1108,9 +1108,6 @@
     <t xml:space="preserve">CAJA DE BANCOS </t>
   </si>
   <si>
-    <t>VTO 16/02</t>
-  </si>
-  <si>
     <t>PERÍODO: ENERO</t>
   </si>
   <si>
@@ -1241,12 +1238,6 @@
   </si>
   <si>
     <t>4 E COCHERA XHARDEZ MARIA EUGENIA</t>
-  </si>
-  <si>
-    <t>marcela65bossetti@gmail.com - 
-             lucas_lc1@icloud.com
-borromeo22@hotmail.com
-altgenug@gmail.com karinalanni16@gmail.com alejandraaalejo@yahoo.com.ar</t>
   </si>
   <si>
     <t>● alejandraaalejo@yahoo.com.ar para agregar a la cadena de italia
@@ -1302,7 +1293,34 @@
     <t>EL 12A Y 12 B TIENE GASTOS (QUE PAGARON ELLOS ) PENDIENTES QUE LES PONGAMOS COMO INGRESO DEL ASCENSOR. DEBEMOS AGREGARLE $272.252 A CADA UNO</t>
   </si>
   <si>
-    <t>El 2C habia abonado el mes anterior $250.932,15 - Lo pusimos impago - Debe abonar $123.612,15.</t>
+    <t>marcela65bossetti@gmail.com
+             lucas_lc1@icloud.com
+borromeo22@hotmail.com
+altgenug@gmail.com karinalanni16@gmail.com alejandraaalejo@yahoo.com.ar</t>
+  </si>
+  <si>
+    <t>VTO 18/02</t>
+  </si>
+  <si>
+    <t>El 8vo e junto con las cocheras G y J habia abonado el  mes anterior 239.116,53 como un boludo. Nosotros le pusimos ese pago a la UF 53. Hay que quitarselo. El VO e y sus socheras debe abonar:</t>
+  </si>
+  <si>
+    <t>8vo E</t>
+  </si>
+  <si>
+    <t>Cochcera G</t>
+  </si>
+  <si>
+    <t>Cochera J</t>
+  </si>
+  <si>
+    <t>El 2C habia abonado el mes anterior $250.932,15 - Lo pusimos impago - Debe abonar $123.612,15 y los abono</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El 8C deposito el 10/02 $120.000 </t>
+  </si>
+  <si>
+    <t>Macarena Crespo nueva inquilina</t>
   </si>
 </sst>
 </file>
@@ -1579,7 +1597,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1661,6 +1679,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2219,7 +2243,7 @@
     </xf>
     <xf numFmtId="44" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="384">
+  <cellXfs count="394">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2816,159 +2840,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="31" fillId="13" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="distributed"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="30" fillId="14" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="30" fillId="14" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2978,6 +2849,177 @@
     </xf>
     <xf numFmtId="44" fontId="31" fillId="14" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="31" fillId="4" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="44" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="30" fillId="15" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="15" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -3343,31 +3385,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E413A25D-5161-4141-BE0B-6E37A2A76CA5}">
   <dimension ref="A1:M124"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.5703125" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" customWidth="1"/>
-    <col min="6" max="6" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.5546875" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" customWidth="1"/>
+    <col min="6" max="6" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.7109375" customWidth="1"/>
+    <col min="10" max="10" width="22.6640625" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.28515625" customWidth="1"/>
+    <col min="12" max="12" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="143"/>
-      <c r="B1" s="338" t="s">
+      <c r="B1" s="347" t="s">
         <v>333</v>
       </c>
-      <c r="C1" s="338"/>
-      <c r="D1" s="338"/>
-      <c r="E1" s="339"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C1" s="347"/>
+      <c r="D1" s="347"/>
+      <c r="E1" s="348"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="144"/>
       <c r="B2" s="151" t="s">
         <v>336</v>
@@ -3376,16 +3418,16 @@
       <c r="D2" s="145"/>
       <c r="E2" s="146"/>
     </row>
-    <row r="3" spans="1:5" ht="51.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="51.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="144"/>
-      <c r="B3" s="334" t="s">
+      <c r="B3" s="349" t="s">
         <v>334</v>
       </c>
-      <c r="C3" s="334"/>
-      <c r="D3" s="334"/>
-      <c r="E3" s="335"/>
-    </row>
-    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C3" s="349"/>
+      <c r="D3" s="349"/>
+      <c r="E3" s="350"/>
+    </row>
+    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="147" t="s">
         <v>282</v>
       </c>
@@ -3396,12 +3438,12 @@
       <c r="D4" s="149"/>
       <c r="E4" s="150"/>
     </row>
-    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="144" t="s">
         <v>335</v>
       </c>
       <c r="B5" s="149" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C5" s="151"/>
       <c r="D5" s="145" t="s">
@@ -3409,7 +3451,7 @@
       </c>
       <c r="E5" s="152"/>
     </row>
-    <row r="6" spans="1:5" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="265" t="s">
         <v>322</v>
       </c>
@@ -3420,57 +3462,57 @@
       </c>
       <c r="E6" s="150"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="336" t="s">
-        <v>356</v>
-      </c>
-      <c r="C8" s="336"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="336"/>
-      <c r="C9" s="336"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="336"/>
-      <c r="C10" s="336"/>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="337" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="351" t="s">
+        <v>415</v>
+      </c>
+      <c r="C8" s="351"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B9" s="351"/>
+      <c r="C9" s="351"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="351"/>
+      <c r="C10" s="351"/>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="352" t="s">
         <v>286</v>
       </c>
-      <c r="B13" s="337"/>
-      <c r="C13" s="337"/>
-      <c r="D13" s="337"/>
-      <c r="E13" s="337"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="337"/>
-      <c r="B14" s="337"/>
-      <c r="C14" s="337"/>
-      <c r="D14" s="337"/>
-      <c r="E14" s="337"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="337"/>
-      <c r="B15" s="337"/>
-      <c r="C15" s="337"/>
-      <c r="D15" s="337"/>
-      <c r="E15" s="337"/>
-    </row>
-    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="337"/>
-      <c r="B16" s="337"/>
-      <c r="C16" s="337"/>
-      <c r="D16" s="337"/>
-      <c r="E16" s="337"/>
-    </row>
-    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="18" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="352"/>
+      <c r="C13" s="352"/>
+      <c r="D13" s="352"/>
+      <c r="E13" s="352"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="352"/>
+      <c r="B14" s="352"/>
+      <c r="C14" s="352"/>
+      <c r="D14" s="352"/>
+      <c r="E14" s="352"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="352"/>
+      <c r="B15" s="352"/>
+      <c r="C15" s="352"/>
+      <c r="D15" s="352"/>
+      <c r="E15" s="352"/>
+    </row>
+    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="352"/>
+      <c r="B16" s="352"/>
+      <c r="C16" s="352"/>
+      <c r="D16" s="352"/>
+      <c r="E16" s="352"/>
+    </row>
+    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="18" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="9"/>
     </row>
-    <row r="19" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="153" t="s">
         <v>287</v>
       </c>
@@ -3479,7 +3521,7 @@
       <c r="D20" s="156"/>
       <c r="E20" s="157"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="158" t="s">
         <v>323</v>
       </c>
@@ -3488,11 +3530,11 @@
       <c r="D21" s="159"/>
       <c r="E21" s="160"/>
     </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="332" t="s">
-        <v>358</v>
-      </c>
-      <c r="B22" s="333"/>
+    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="343" t="s">
+        <v>357</v>
+      </c>
+      <c r="B22" s="344"/>
       <c r="C22" s="163"/>
       <c r="D22" s="285">
         <v>2182238</v>
@@ -3500,11 +3542,11 @@
       <c r="E22" s="189"/>
       <c r="H22" s="164"/>
     </row>
-    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="332" t="s">
-        <v>359</v>
-      </c>
-      <c r="B23" s="333"/>
+    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="343" t="s">
+        <v>358</v>
+      </c>
+      <c r="B23" s="344"/>
       <c r="C23" s="163"/>
       <c r="D23" s="285">
         <v>-474636.76</v>
@@ -3512,11 +3554,11 @@
       <c r="E23" s="165"/>
       <c r="H23" s="164"/>
     </row>
-    <row r="24" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="332" t="s">
-        <v>413</v>
-      </c>
-      <c r="B24" s="333"/>
+    <row r="24" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="343" t="s">
+        <v>411</v>
+      </c>
+      <c r="B24" s="344"/>
       <c r="C24" s="163"/>
       <c r="D24" s="286">
         <v>1381383</v>
@@ -3524,11 +3566,11 @@
       <c r="E24" s="165"/>
       <c r="H24" s="164"/>
     </row>
-    <row r="25" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="332" t="s">
+    <row r="25" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="343" t="s">
         <v>54</v>
       </c>
-      <c r="B25" s="333"/>
+      <c r="B25" s="344"/>
       <c r="C25" s="163"/>
       <c r="D25" s="286">
         <v>0.76</v>
@@ -3536,7 +3578,7 @@
       <c r="E25" s="165"/>
       <c r="H25" s="164"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="166" t="s">
         <v>288</v>
       </c>
@@ -3548,18 +3590,18 @@
         <v>3088985</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="166" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B27" s="166"/>
       <c r="C27" s="166"/>
       <c r="D27" s="167"/>
       <c r="E27" s="266"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="163" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B28" s="163"/>
       <c r="C28" s="163"/>
@@ -3569,7 +3611,7 @@
       </c>
       <c r="E28" s="268"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="166" t="s">
         <v>288</v>
       </c>
@@ -3581,7 +3623,7 @@
         <v>511000</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="158" t="s">
         <v>324</v>
       </c>
@@ -3590,9 +3632,9 @@
       <c r="D30" s="167"/>
       <c r="E30" s="266"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="163" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B31" s="267"/>
       <c r="C31" s="267"/>
@@ -3600,10 +3642,10 @@
         <v>14015.68</v>
       </c>
       <c r="E31" s="278" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="163" t="s">
         <v>341</v>
       </c>
@@ -3613,10 +3655,10 @@
         <v>1235711.01</v>
       </c>
       <c r="E32" s="278" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="163" t="s">
         <v>326</v>
       </c>
@@ -3626,10 +3668,10 @@
         <v>225414.17</v>
       </c>
       <c r="E33" s="278" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="163" t="s">
         <v>328</v>
       </c>
@@ -3643,7 +3685,7 @@
         <v>Debito 16/01 Cred.</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="163" t="s">
         <v>327</v>
       </c>
@@ -3657,7 +3699,7 @@
         <v>Debito 16/01 Cred.</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="163" t="s">
         <v>342</v>
       </c>
@@ -3666,7 +3708,7 @@
       <c r="D36" s="187"/>
       <c r="E36" s="278"/>
     </row>
-    <row r="37" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="166" t="s">
         <v>325</v>
       </c>
@@ -3678,7 +3720,7 @@
         <v>1616063.91</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="158" t="s">
         <v>289</v>
       </c>
@@ -3687,33 +3729,33 @@
       <c r="D38" s="169"/>
       <c r="E38" s="170"/>
     </row>
-    <row r="39" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="329" t="s">
+    <row r="39" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="345" t="s">
         <v>329</v>
       </c>
-      <c r="B39" s="330"/>
+      <c r="B39" s="346"/>
       <c r="C39" s="173"/>
       <c r="D39" s="320">
         <v>313739</v>
       </c>
       <c r="E39" s="165" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="329" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="345" t="s">
         <v>330</v>
       </c>
-      <c r="B40" s="330"/>
+      <c r="B40" s="346"/>
       <c r="C40" s="173"/>
       <c r="D40" s="321">
         <v>5204</v>
       </c>
       <c r="E40" s="165" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="166" t="s">
         <v>290</v>
       </c>
@@ -3725,7 +3767,7 @@
         <v>318943</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="158" t="s">
         <v>291</v>
       </c>
@@ -3734,7 +3776,7 @@
       <c r="D42" s="176"/>
       <c r="E42" s="177"/>
     </row>
-    <row r="43" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="178" t="s">
         <v>292</v>
       </c>
@@ -3744,10 +3786,10 @@
         <v>29750.38</v>
       </c>
       <c r="E43" s="165" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="178" t="s">
         <v>292</v>
       </c>
@@ -3757,10 +3799,10 @@
         <v>15585.29</v>
       </c>
       <c r="E44" s="165" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="178" t="s">
         <v>292</v>
       </c>
@@ -3770,10 +3812,10 @@
         <v>578076.46</v>
       </c>
       <c r="E45" s="165" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="178" t="s">
         <v>292</v>
       </c>
@@ -3783,10 +3825,10 @@
         <v>312536.71999999997</v>
       </c>
       <c r="E46" s="165" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="178" t="s">
         <v>293</v>
       </c>
@@ -3796,10 +3838,10 @@
         <v>10562.67</v>
       </c>
       <c r="E47" s="165" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="178" t="s">
         <v>293</v>
       </c>
@@ -3808,20 +3850,20 @@
       <c r="D48" s="180"/>
       <c r="E48" s="165"/>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="329" t="s">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49" s="345" t="s">
         <v>294</v>
       </c>
-      <c r="B49" s="330"/>
+      <c r="B49" s="346"/>
       <c r="C49" s="178"/>
       <c r="D49" s="180">
         <v>3444706.16</v>
       </c>
       <c r="E49" s="278" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="182" t="s">
         <v>295</v>
       </c>
@@ -3830,7 +3872,7 @@
       <c r="D50" s="179"/>
       <c r="E50" s="165"/>
     </row>
-    <row r="51" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="166" t="s">
         <v>296</v>
       </c>
@@ -3842,53 +3884,53 @@
         <v>4391217.68</v>
       </c>
     </row>
-    <row r="52" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="158"/>
       <c r="B52" s="166"/>
       <c r="C52" s="166"/>
       <c r="D52" s="167"/>
       <c r="E52" s="185"/>
     </row>
-    <row r="53" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="332" t="s">
-        <v>368</v>
-      </c>
-      <c r="B53" s="333"/>
+    <row r="53" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="343" t="s">
+        <v>367</v>
+      </c>
+      <c r="B53" s="344"/>
       <c r="C53" s="178"/>
       <c r="D53" s="180">
         <v>0</v>
       </c>
       <c r="E53" s="186"/>
     </row>
-    <row r="54" spans="1:6" ht="156.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="332" t="s">
-        <v>410</v>
-      </c>
-      <c r="B54" s="333"/>
+    <row r="54" spans="1:6" ht="156.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="343" t="s">
+        <v>408</v>
+      </c>
+      <c r="B54" s="344"/>
       <c r="C54" s="178"/>
       <c r="D54" s="180">
         <v>570000</v>
       </c>
       <c r="E54" s="317" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" ht="96.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="332" t="s">
         <v>409</v>
       </c>
-      <c r="B55" s="333"/>
+    </row>
+    <row r="55" spans="1:6" ht="96.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="343" t="s">
+        <v>407</v>
+      </c>
+      <c r="B55" s="344"/>
       <c r="C55" s="178"/>
       <c r="D55" s="180">
         <v>950000</v>
       </c>
       <c r="E55" s="186" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="287" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B56" s="162"/>
       <c r="C56" s="178"/>
@@ -3897,68 +3939,68 @@
         <v>964820</v>
       </c>
       <c r="E56" s="186" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="332" t="s">
-        <v>412</v>
-      </c>
-      <c r="B57" s="333"/>
+        <v>366</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="343" t="s">
+        <v>410</v>
+      </c>
+      <c r="B57" s="344"/>
       <c r="C57" s="178"/>
       <c r="D57" s="180">
         <v>85000</v>
       </c>
       <c r="E57" s="186" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="F57" s="205"/>
     </row>
-    <row r="58" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="332" t="s">
-        <v>376</v>
-      </c>
-      <c r="B58" s="333"/>
+    <row r="58" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="343" t="s">
+        <v>375</v>
+      </c>
+      <c r="B58" s="344"/>
       <c r="C58" s="178"/>
       <c r="D58" s="180">
         <v>85000</v>
       </c>
       <c r="E58" s="189" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F58" s="205"/>
     </row>
-    <row r="59" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="332" t="s">
-        <v>378</v>
-      </c>
-      <c r="B59" s="333"/>
+    <row r="59" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="343" t="s">
+        <v>377</v>
+      </c>
+      <c r="B59" s="344"/>
       <c r="C59" s="178"/>
       <c r="D59" s="180">
         <v>150000</v>
       </c>
       <c r="E59" s="189" t="s">
+        <v>378</v>
+      </c>
+      <c r="F59" s="205"/>
+    </row>
+    <row r="60" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="343" t="s">
         <v>379</v>
       </c>
-      <c r="F59" s="205"/>
-    </row>
-    <row r="60" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="332" t="s">
-        <v>380</v>
-      </c>
-      <c r="B60" s="333"/>
+      <c r="B60" s="344"/>
       <c r="C60" s="178"/>
       <c r="D60" s="180">
         <v>250000</v>
       </c>
       <c r="E60" s="189" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F60" s="205"/>
     </row>
-    <row r="61" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="287" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B61" s="162"/>
       <c r="C61" s="178"/>
@@ -3970,9 +4012,9 @@
       </c>
       <c r="F61" s="205"/>
     </row>
-    <row r="62" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="287" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B62" s="162"/>
       <c r="C62" s="178"/>
@@ -3980,13 +4022,13 @@
         <v>1820000</v>
       </c>
       <c r="E62" s="189" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F62" s="205"/>
     </row>
-    <row r="63" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="287" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B63" s="162"/>
       <c r="C63" s="178"/>
@@ -3994,13 +4036,13 @@
         <v>3000000</v>
       </c>
       <c r="E63" s="189" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F63" s="205"/>
     </row>
-    <row r="64" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="287" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B64" s="162"/>
       <c r="C64" s="178"/>
@@ -4008,24 +4050,24 @@
         <v>256900</v>
       </c>
       <c r="E64" s="189" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F64" s="205"/>
     </row>
-    <row r="65" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="332" t="s">
-        <v>375</v>
-      </c>
-      <c r="B65" s="333"/>
+    <row r="65" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="343" t="s">
+        <v>374</v>
+      </c>
+      <c r="B65" s="344"/>
       <c r="C65" s="178"/>
       <c r="D65" s="180">
         <v>303033.69</v>
       </c>
       <c r="E65" s="189" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" s="166" t="s">
         <v>5</v>
       </c>
@@ -4037,7 +4079,7 @@
         <v>8559403.6899999995</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" s="158" t="s">
         <v>297</v>
       </c>
@@ -4046,31 +4088,31 @@
       <c r="D67" s="159"/>
       <c r="E67" s="160"/>
     </row>
-    <row r="68" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="332" t="s">
-        <v>386</v>
-      </c>
-      <c r="B68" s="333"/>
+    <row r="68" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="343" t="s">
+        <v>385</v>
+      </c>
+      <c r="B68" s="344"/>
       <c r="C68" s="163"/>
       <c r="D68" s="285">
         <v>650000</v>
       </c>
       <c r="E68" s="189"/>
     </row>
-    <row r="69" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="332" t="s">
-        <v>387</v>
-      </c>
-      <c r="B69" s="333"/>
+    <row r="69" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="343" t="s">
+        <v>386</v>
+      </c>
+      <c r="B69" s="344"/>
       <c r="C69" s="163"/>
       <c r="D69" s="285">
         <v>650000</v>
       </c>
       <c r="E69" s="189"/>
     </row>
-    <row r="70" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="161" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B70" s="162"/>
       <c r="C70" s="163"/>
@@ -4078,12 +4120,12 @@
         <v>95200</v>
       </c>
       <c r="E70" s="189" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="161" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B71" s="162"/>
       <c r="C71" s="163"/>
@@ -4091,12 +4133,12 @@
         <v>60000</v>
       </c>
       <c r="E71" s="189" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="161" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B72" s="162"/>
       <c r="C72" s="163"/>
@@ -4104,12 +4146,12 @@
         <v>42350</v>
       </c>
       <c r="E72" s="189" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="161" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B73" s="162"/>
       <c r="C73" s="163"/>
@@ -4117,12 +4159,12 @@
         <v>100000</v>
       </c>
       <c r="E73" s="189" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="287" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B74" s="162"/>
       <c r="C74" s="163"/>
@@ -4130,10 +4172,10 @@
         <v>70000</v>
       </c>
       <c r="E74" s="189" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" s="166" t="s">
         <v>288</v>
       </c>
@@ -4145,7 +4187,7 @@
         <v>1667550</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="158" t="s">
         <v>298</v>
       </c>
@@ -4154,7 +4196,7 @@
       <c r="D76" s="191"/>
       <c r="E76" s="174"/>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" s="178" t="s">
         <v>337</v>
       </c>
@@ -4165,7 +4207,7 @@
       </c>
       <c r="E77" s="192"/>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="178" t="s">
         <v>338</v>
       </c>
@@ -4176,7 +4218,7 @@
       </c>
       <c r="E78" s="193"/>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" s="178" t="s">
         <v>339</v>
       </c>
@@ -4187,7 +4229,7 @@
       </c>
       <c r="E79" s="193"/>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" s="178" t="s">
         <v>340</v>
       </c>
@@ -4199,7 +4241,7 @@
       </c>
       <c r="E80" s="193"/>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" s="194" t="s">
         <v>288</v>
       </c>
@@ -4211,14 +4253,14 @@
         <v>282278.22000000003</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="178"/>
       <c r="B82" s="178"/>
       <c r="C82" s="178"/>
       <c r="D82" s="197"/>
       <c r="E82" s="198"/>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" s="199" t="s">
         <v>299</v>
       </c>
@@ -4227,13 +4269,13 @@
       <c r="D83" s="200"/>
       <c r="E83" s="201"/>
     </row>
-    <row r="84" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" s="202"/>
       <c r="D84" s="203"/>
       <c r="E84" s="204"/>
       <c r="F84" s="205"/>
     </row>
-    <row r="85" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" s="206" t="s">
         <v>300</v>
       </c>
@@ -4247,16 +4289,16 @@
       <c r="F85" s="211"/>
       <c r="G85" s="205"/>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="D86" s="203"/>
       <c r="E86" s="203"/>
     </row>
-    <row r="87" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D87" s="203"/>
       <c r="E87" s="203"/>
       <c r="H87" s="212"/>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" s="153" t="s">
         <v>301</v>
       </c>
@@ -4265,32 +4307,32 @@
       <c r="D88" s="213"/>
       <c r="E88" s="214"/>
     </row>
-    <row r="89" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="171"/>
       <c r="B89" s="172"/>
       <c r="C89" s="178"/>
       <c r="D89" s="187"/>
       <c r="E89" s="215"/>
     </row>
-    <row r="90" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="332"/>
-      <c r="B90" s="333"/>
+    <row r="90" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="343"/>
+      <c r="B90" s="344"/>
       <c r="C90" s="178"/>
       <c r="D90" s="187"/>
       <c r="E90" s="215"/>
     </row>
-    <row r="91" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D91" s="178"/>
       <c r="E91" s="178"/>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" s="171"/>
       <c r="B92" s="216"/>
       <c r="C92" s="178"/>
       <c r="D92" s="187"/>
       <c r="E92" s="215"/>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" s="217" t="s">
         <v>332</v>
       </c>
@@ -4302,9 +4344,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" spans="1:8" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="95" spans="1:8" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" s="199" t="s">
         <v>302</v>
       </c>
@@ -4313,8 +4355,8 @@
       <c r="D96" s="220"/>
       <c r="E96" s="279"/>
     </row>
-    <row r="97" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="98" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="98" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A98" s="206" t="s">
         <v>303</v>
       </c>
@@ -4326,8 +4368,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="100" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="100" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A100" s="222" t="s">
         <v>304</v>
       </c>
@@ -4336,7 +4378,7 @@
         <v>20435441.5</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A101" s="222" t="s">
         <v>305</v>
       </c>
@@ -4345,7 +4387,7 @@
         <v>20435441.5</v>
       </c>
     </row>
-    <row r="102" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A102" s="222" t="s">
         <v>306</v>
       </c>
@@ -4354,7 +4396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A103" s="222" t="s">
         <v>307</v>
       </c>
@@ -4363,22 +4405,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A105" s="331" t="s">
-        <v>390</v>
-      </c>
-      <c r="B105" s="331"/>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A106" s="331"/>
-      <c r="B106" s="331"/>
-    </row>
-    <row r="107" spans="1:6" s="226" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A105" s="354" t="s">
+        <v>389</v>
+      </c>
+      <c r="B105" s="354"/>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A106" s="354"/>
+      <c r="B106" s="354"/>
+    </row>
+    <row r="107" spans="1:6" s="226" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A107"/>
       <c r="B107" s="224"/>
       <c r="C107" s="225"/>
     </row>
-    <row r="108" spans="1:6" s="226" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" s="226" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="283" t="s">
         <v>354</v>
       </c>
@@ -4389,7 +4431,7 @@
       <c r="D108" s="228"/>
       <c r="E108" s="228"/>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" s="173" t="s">
         <v>331</v>
       </c>
@@ -4398,7 +4440,7 @@
         <v>-20435441.5</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" s="173" t="s">
         <v>308</v>
       </c>
@@ -4408,89 +4450,89 @@
       </c>
       <c r="F110" s="224"/>
     </row>
-    <row r="111" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="173" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B111" s="304">
         <v>-123000</v>
       </c>
       <c r="F111" s="224"/>
     </row>
-    <row r="112" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="173" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B112" s="305">
         <v>-3689.2069499999998</v>
       </c>
       <c r="F112" s="224"/>
     </row>
-    <row r="113" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="173" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B113" s="305">
         <v>-130000</v>
       </c>
       <c r="F113" s="224"/>
     </row>
-    <row r="114" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="173" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B114" s="303">
         <v>-99011.93</v>
       </c>
       <c r="F114" s="224"/>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A115" s="173" t="s">
         <v>86</v>
       </c>
       <c r="B115" s="230">
         <f>PRORRATEO!F117</f>
-        <v>15176046.170695035</v>
+        <v>15206198.110695034</v>
       </c>
       <c r="F115" s="224"/>
     </row>
-    <row r="116" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A116" s="231" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B116" s="318">
         <v>122500</v>
       </c>
       <c r="F116" s="224"/>
     </row>
-    <row r="117" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A117" s="232" t="s">
         <v>355</v>
       </c>
       <c r="B117" s="233">
         <f>SUM(B108:C116)</f>
-        <v>10567217.803745035</v>
+        <v>10597369.743745035</v>
       </c>
       <c r="D117" s="224"/>
       <c r="E117" s="205"/>
       <c r="F117" s="205"/>
     </row>
-    <row r="118" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A119" s="328" t="s">
+    <row r="118" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A119" s="353" t="s">
         <v>309</v>
       </c>
-      <c r="B119" s="328"/>
-      <c r="C119" s="328"/>
-    </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A120" s="328"/>
-      <c r="B120" s="328"/>
-      <c r="C120" s="328"/>
-    </row>
-    <row r="121" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B119" s="353"/>
+      <c r="C119" s="353"/>
+    </row>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A120" s="353"/>
+      <c r="B120" s="353"/>
+      <c r="C120" s="353"/>
+    </row>
+    <row r="121" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="234" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B121" s="316">
         <v>3400</v>
@@ -4498,9 +4540,9 @@
       <c r="C121" s="235"/>
       <c r="E121" s="211"/>
     </row>
-    <row r="122" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="234" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B122" s="316">
         <v>110000</v>
@@ -4508,7 +4550,7 @@
       <c r="C122" s="235"/>
       <c r="D122" s="211"/>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A123" s="236" t="s">
         <v>5</v>
       </c>
@@ -4518,21 +4560,11 @@
       </c>
       <c r="C123" s="238"/>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
       <c r="M124" s="239"/>
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A68:B68"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B8:C10"/>
-    <mergeCell ref="A13:E16"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A119:C120"/>
     <mergeCell ref="A40:B40"/>
     <mergeCell ref="A105:B106"/>
@@ -4547,9 +4579,19 @@
     <mergeCell ref="A54:B54"/>
     <mergeCell ref="A69:B69"/>
     <mergeCell ref="A55:B55"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B8:C10"/>
+    <mergeCell ref="A13:E16"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A23:B23"/>
   </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="5" orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="5" scale="90" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -4557,50 +4599,50 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{533DB7A7-09F4-49CF-B824-70F15C1FF525}">
   <dimension ref="A1:N125"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" customWidth="1"/>
-    <col min="2" max="2" width="25.5703125" customWidth="1"/>
-    <col min="3" max="3" width="0.140625" customWidth="1"/>
-    <col min="4" max="4" width="8.42578125" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" customWidth="1"/>
-    <col min="6" max="6" width="12.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.5703125" customWidth="1"/>
-    <col min="8" max="8" width="9.5703125" customWidth="1"/>
-    <col min="9" max="9" width="12.42578125" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" customWidth="1"/>
-    <col min="13" max="13" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.33203125" customWidth="1"/>
+    <col min="2" max="2" width="25.5546875" customWidth="1"/>
+    <col min="3" max="3" width="0.109375" customWidth="1"/>
+    <col min="4" max="4" width="8.44140625" customWidth="1"/>
+    <col min="5" max="5" width="14.109375" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" customWidth="1"/>
+    <col min="7" max="7" width="10.5546875" customWidth="1"/>
+    <col min="8" max="8" width="9.5546875" customWidth="1"/>
+    <col min="9" max="9" width="12.44140625" customWidth="1"/>
+    <col min="10" max="10" width="14.44140625" customWidth="1"/>
+    <col min="11" max="11" width="14.6640625" customWidth="1"/>
+    <col min="12" max="12" width="14.33203125" customWidth="1"/>
+    <col min="13" max="13" width="7.33203125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="288"/>
       <c r="B1" s="289"/>
       <c r="C1" s="289"/>
-      <c r="D1" s="340"/>
-      <c r="E1" s="340"/>
-      <c r="F1" s="340"/>
-      <c r="G1" s="340"/>
-      <c r="H1" s="340"/>
-      <c r="I1" s="340"/>
-      <c r="J1" s="340"/>
-      <c r="K1" s="340"/>
+      <c r="D1" s="363"/>
+      <c r="E1" s="363"/>
+      <c r="F1" s="363"/>
+      <c r="G1" s="363"/>
+      <c r="H1" s="363"/>
+      <c r="I1" s="363"/>
+      <c r="J1" s="363"/>
+      <c r="K1" s="363"/>
       <c r="L1" s="290"/>
     </row>
-    <row r="2" spans="1:14" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="291"/>
       <c r="B2" s="292"/>
       <c r="C2" s="293"/>
       <c r="D2" s="293" t="s">
         <v>310</v>
       </c>
-      <c r="E2" s="363">
+      <c r="E2" s="355">
         <v>3000000</v>
       </c>
-      <c r="F2" s="363"/>
+      <c r="F2" s="355"/>
       <c r="G2" s="293"/>
       <c r="H2" s="293"/>
       <c r="I2" s="293" t="s">
@@ -4613,7 +4655,7 @@
       <c r="L2" s="296"/>
       <c r="M2" s="240"/>
     </row>
-    <row r="3" spans="1:14" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="297"/>
       <c r="B3" s="298"/>
       <c r="C3" s="298"/>
@@ -4628,170 +4670,170 @@
       <c r="L3" s="301"/>
       <c r="M3" s="240"/>
     </row>
-    <row r="4" spans="1:14" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="341" t="s">
+    <row r="4" spans="1:14" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="364" t="s">
         <v>352</v>
       </c>
-      <c r="B4" s="342"/>
-      <c r="C4" s="342"/>
-      <c r="D4" s="342"/>
-      <c r="E4" s="342"/>
-      <c r="F4" s="342"/>
-      <c r="G4" s="342"/>
-      <c r="H4" s="342"/>
-      <c r="I4" s="342"/>
-      <c r="J4" s="342"/>
-      <c r="K4" s="342"/>
-      <c r="L4" s="343"/>
+      <c r="B4" s="365"/>
+      <c r="C4" s="365"/>
+      <c r="D4" s="365"/>
+      <c r="E4" s="365"/>
+      <c r="F4" s="365"/>
+      <c r="G4" s="365"/>
+      <c r="H4" s="365"/>
+      <c r="I4" s="365"/>
+      <c r="J4" s="365"/>
+      <c r="K4" s="365"/>
+      <c r="L4" s="366"/>
       <c r="M4" s="240"/>
     </row>
-    <row r="5" spans="1:14" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="344"/>
-      <c r="B5" s="345"/>
-      <c r="C5" s="345"/>
-      <c r="D5" s="345"/>
-      <c r="E5" s="345"/>
-      <c r="F5" s="345"/>
-      <c r="G5" s="345"/>
-      <c r="H5" s="345"/>
-      <c r="I5" s="345"/>
-      <c r="J5" s="345"/>
-      <c r="K5" s="345"/>
-      <c r="L5" s="346"/>
+    <row r="5" spans="1:14" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="367"/>
+      <c r="B5" s="368"/>
+      <c r="C5" s="368"/>
+      <c r="D5" s="368"/>
+      <c r="E5" s="368"/>
+      <c r="F5" s="368"/>
+      <c r="G5" s="368"/>
+      <c r="H5" s="368"/>
+      <c r="I5" s="368"/>
+      <c r="J5" s="368"/>
+      <c r="K5" s="368"/>
+      <c r="L5" s="369"/>
       <c r="M5" s="240"/>
     </row>
-    <row r="6" spans="1:14" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="344"/>
-      <c r="B6" s="345"/>
-      <c r="C6" s="345"/>
-      <c r="D6" s="345"/>
-      <c r="E6" s="345"/>
-      <c r="F6" s="345"/>
-      <c r="G6" s="345"/>
-      <c r="H6" s="345"/>
-      <c r="I6" s="345"/>
-      <c r="J6" s="345"/>
-      <c r="K6" s="345"/>
-      <c r="L6" s="346"/>
+    <row r="6" spans="1:14" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="367"/>
+      <c r="B6" s="368"/>
+      <c r="C6" s="368"/>
+      <c r="D6" s="368"/>
+      <c r="E6" s="368"/>
+      <c r="F6" s="368"/>
+      <c r="G6" s="368"/>
+      <c r="H6" s="368"/>
+      <c r="I6" s="368"/>
+      <c r="J6" s="368"/>
+      <c r="K6" s="368"/>
+      <c r="L6" s="369"/>
       <c r="M6" s="240"/>
     </row>
-    <row r="7" spans="1:14" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="344"/>
-      <c r="B7" s="345"/>
-      <c r="C7" s="345"/>
-      <c r="D7" s="345"/>
-      <c r="E7" s="345"/>
-      <c r="F7" s="345"/>
-      <c r="G7" s="345"/>
-      <c r="H7" s="345"/>
-      <c r="I7" s="345"/>
-      <c r="J7" s="345"/>
-      <c r="K7" s="345"/>
-      <c r="L7" s="346"/>
+    <row r="7" spans="1:14" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="367"/>
+      <c r="B7" s="368"/>
+      <c r="C7" s="368"/>
+      <c r="D7" s="368"/>
+      <c r="E7" s="368"/>
+      <c r="F7" s="368"/>
+      <c r="G7" s="368"/>
+      <c r="H7" s="368"/>
+      <c r="I7" s="368"/>
+      <c r="J7" s="368"/>
+      <c r="K7" s="368"/>
+      <c r="L7" s="369"/>
       <c r="M7" s="240"/>
     </row>
-    <row r="8" spans="1:14" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="347"/>
-      <c r="B8" s="348"/>
-      <c r="C8" s="348"/>
-      <c r="D8" s="348"/>
-      <c r="E8" s="348"/>
-      <c r="F8" s="348"/>
-      <c r="G8" s="348"/>
-      <c r="H8" s="348"/>
-      <c r="I8" s="348"/>
-      <c r="J8" s="348"/>
-      <c r="K8" s="348"/>
-      <c r="L8" s="349"/>
-    </row>
-    <row r="9" spans="1:14" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="357" t="s">
+    <row r="8" spans="1:14" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="370"/>
+      <c r="B8" s="371"/>
+      <c r="C8" s="371"/>
+      <c r="D8" s="371"/>
+      <c r="E8" s="371"/>
+      <c r="F8" s="371"/>
+      <c r="G8" s="371"/>
+      <c r="H8" s="371"/>
+      <c r="I8" s="371"/>
+      <c r="J8" s="371"/>
+      <c r="K8" s="371"/>
+      <c r="L8" s="372"/>
+    </row>
+    <row r="9" spans="1:14" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="378" t="s">
         <v>350</v>
       </c>
-      <c r="B9" s="358"/>
-      <c r="C9" s="358"/>
-      <c r="D9" s="358"/>
-      <c r="E9" s="358"/>
-      <c r="F9" s="358"/>
-      <c r="G9" s="358"/>
-      <c r="H9" s="358"/>
-      <c r="I9" s="358"/>
-      <c r="J9" s="358"/>
-      <c r="K9" s="358"/>
-      <c r="L9" s="359"/>
-    </row>
-    <row r="10" spans="1:14" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="360" t="s">
+      <c r="B9" s="379"/>
+      <c r="C9" s="379"/>
+      <c r="D9" s="379"/>
+      <c r="E9" s="379"/>
+      <c r="F9" s="379"/>
+      <c r="G9" s="379"/>
+      <c r="H9" s="379"/>
+      <c r="I9" s="379"/>
+      <c r="J9" s="379"/>
+      <c r="K9" s="379"/>
+      <c r="L9" s="380"/>
+    </row>
+    <row r="10" spans="1:14" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="381" t="s">
         <v>351</v>
       </c>
-      <c r="B10" s="361"/>
-      <c r="C10" s="361"/>
-      <c r="D10" s="361"/>
-      <c r="E10" s="361"/>
-      <c r="F10" s="361"/>
-      <c r="G10" s="361"/>
-      <c r="H10" s="361"/>
-      <c r="I10" s="361"/>
-      <c r="J10" s="361"/>
-      <c r="K10" s="361"/>
-      <c r="L10" s="362"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="350" t="s">
+      <c r="B10" s="382"/>
+      <c r="C10" s="382"/>
+      <c r="D10" s="382"/>
+      <c r="E10" s="382"/>
+      <c r="F10" s="382"/>
+      <c r="G10" s="382"/>
+      <c r="H10" s="382"/>
+      <c r="I10" s="382"/>
+      <c r="J10" s="382"/>
+      <c r="K10" s="382"/>
+      <c r="L10" s="383"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A11" s="373" t="s">
         <v>312</v>
       </c>
-      <c r="B11" s="350" t="s">
+      <c r="B11" s="373" t="s">
         <v>313</v>
       </c>
-      <c r="C11" s="350" t="s">
+      <c r="C11" s="373" t="s">
         <v>314</v>
       </c>
-      <c r="D11" s="350" t="s">
+      <c r="D11" s="373" t="s">
         <v>315</v>
       </c>
-      <c r="E11" s="353" t="s">
+      <c r="E11" s="356" t="s">
         <v>316</v>
       </c>
-      <c r="F11" s="350" t="s">
+      <c r="F11" s="373" t="s">
         <v>317</v>
       </c>
-      <c r="G11" s="355" t="s">
+      <c r="G11" s="376" t="s">
         <v>318</v>
       </c>
-      <c r="H11" s="353" t="s">
+      <c r="H11" s="356" t="s">
         <v>319</v>
       </c>
-      <c r="I11" s="353" t="s">
+      <c r="I11" s="356" t="s">
         <v>311</v>
       </c>
-      <c r="J11" s="364" t="s">
+      <c r="J11" s="358" t="s">
         <v>310</v>
       </c>
       <c r="K11" s="241" t="s">
         <v>320</v>
       </c>
-      <c r="L11" s="366" t="s">
+      <c r="L11" s="360" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="351"/>
-      <c r="B12" s="351"/>
-      <c r="C12" s="352"/>
-      <c r="D12" s="351"/>
-      <c r="E12" s="354"/>
-      <c r="F12" s="351"/>
-      <c r="G12" s="356"/>
-      <c r="H12" s="354"/>
-      <c r="I12" s="354"/>
-      <c r="J12" s="365"/>
+    <row r="12" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="374"/>
+      <c r="B12" s="374"/>
+      <c r="C12" s="375"/>
+      <c r="D12" s="374"/>
+      <c r="E12" s="357"/>
+      <c r="F12" s="374"/>
+      <c r="G12" s="377"/>
+      <c r="H12" s="357"/>
+      <c r="I12" s="357"/>
+      <c r="J12" s="359"/>
       <c r="K12" s="242" t="str">
         <f>RESUMEN!B8</f>
-        <v>VTO 16/02</v>
-      </c>
-      <c r="L12" s="367"/>
-    </row>
-    <row r="13" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>VTO 18/02</v>
+      </c>
+      <c r="L12" s="361"/>
+    </row>
+    <row r="13" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="243">
         <v>1</v>
       </c>
@@ -4837,7 +4879,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="243">
         <v>2</v>
       </c>
@@ -4883,10 +4925,10 @@
         <v>0.02</v>
       </c>
       <c r="N14" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="243">
         <v>3</v>
       </c>
@@ -4933,7 +4975,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="243">
         <v>4</v>
       </c>
@@ -4979,7 +5021,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="243">
         <v>5</v>
       </c>
@@ -5025,7 +5067,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="243">
         <v>6</v>
       </c>
@@ -5072,7 +5114,7 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="243">
         <v>7</v>
       </c>
@@ -5119,7 +5161,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="243">
         <v>8</v>
       </c>
@@ -5166,7 +5208,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="243">
         <v>9</v>
       </c>
@@ -5212,7 +5254,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="243">
         <v>10</v>
       </c>
@@ -5259,7 +5301,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="243">
         <v>11</v>
       </c>
@@ -5306,7 +5348,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="243">
         <v>12</v>
       </c>
@@ -5352,7 +5394,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="243">
         <v>13</v>
       </c>
@@ -5398,7 +5440,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="243">
         <v>14</v>
       </c>
@@ -5445,18 +5487,18 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="379">
+    <row r="27" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="328">
         <v>15</v>
       </c>
-      <c r="B27" s="379" t="s">
+      <c r="B27" s="328" t="s">
         <v>140</v>
       </c>
-      <c r="C27" s="380"/>
-      <c r="D27" s="381">
+      <c r="C27" s="329"/>
+      <c r="D27" s="330">
         <v>0.82</v>
       </c>
-      <c r="E27" s="382">
+      <c r="E27" s="331">
         <v>250932.15</v>
       </c>
       <c r="F27" s="246"/>
@@ -5489,7 +5531,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="243">
         <v>16</v>
       </c>
@@ -5536,7 +5578,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="243">
         <v>17</v>
       </c>
@@ -5583,7 +5625,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="306">
         <v>18</v>
       </c>
@@ -5630,7 +5672,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="243">
         <v>19</v>
       </c>
@@ -5680,7 +5722,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="313">
         <v>20</v>
       </c>
@@ -5729,7 +5771,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="313">
         <v>21</v>
       </c>
@@ -5776,7 +5818,7 @@
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="252">
         <f>A33+1</f>
         <v>22</v>
@@ -5824,7 +5866,7 @@
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="252">
         <f t="shared" ref="A35:A98" si="9">A34+1</f>
         <v>23</v>
@@ -5871,7 +5913,7 @@
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="252">
         <f t="shared" si="9"/>
         <v>24</v>
@@ -5919,7 +5961,7 @@
         <v>0.24000000000000007</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="252">
         <f t="shared" si="9"/>
         <v>25</v>
@@ -5966,7 +6008,7 @@
         <v>0.25000000000000006</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="252">
         <f t="shared" si="9"/>
         <v>26</v>
@@ -6011,7 +6053,7 @@
         <v>0.26000000000000006</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="252">
         <f t="shared" si="9"/>
         <v>27</v>
@@ -6058,7 +6100,7 @@
         <v>0.27000000000000007</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="252">
         <f t="shared" si="9"/>
         <v>28</v>
@@ -6105,7 +6147,7 @@
         <v>0.28000000000000008</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="280">
         <f t="shared" si="9"/>
         <v>29</v>
@@ -6155,7 +6197,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="252">
         <f t="shared" si="9"/>
         <v>30</v>
@@ -6203,7 +6245,7 @@
         <v>0.3000000000000001</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="252">
         <f t="shared" si="9"/>
         <v>31</v>
@@ -6251,7 +6293,7 @@
         <v>0.31000000000000011</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="252">
         <f t="shared" si="9"/>
         <v>32</v>
@@ -6299,7 +6341,7 @@
         <v>0.32000000000000012</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="252">
         <f t="shared" si="9"/>
         <v>33</v>
@@ -6346,7 +6388,7 @@
         <v>0.33000000000000013</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="252">
         <f t="shared" si="9"/>
         <v>34</v>
@@ -6394,7 +6436,7 @@
         <v>0.34000000000000014</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" s="280">
         <f t="shared" si="9"/>
         <v>35</v>
@@ -6442,7 +6484,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="252">
         <f t="shared" si="9"/>
         <v>36</v>
@@ -6492,7 +6534,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" s="252">
         <f t="shared" si="9"/>
         <v>37</v>
@@ -6537,7 +6579,7 @@
         <v>0.37000000000000016</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" s="252">
         <f t="shared" si="9"/>
         <v>38</v>
@@ -6584,7 +6626,7 @@
         <v>0.38000000000000017</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" s="252">
         <f t="shared" si="9"/>
         <v>39</v>
@@ -6631,7 +6673,7 @@
         <v>0.39000000000000018</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" s="252">
         <f t="shared" si="9"/>
         <v>40</v>
@@ -6676,7 +6718,7 @@
         <v>0.40000000000000019</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" s="252">
         <f t="shared" si="9"/>
         <v>41</v>
@@ -6724,7 +6766,7 @@
         <v>0.4100000000000002</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" s="252">
         <f t="shared" si="9"/>
         <v>42</v>
@@ -6769,7 +6811,7 @@
         <v>0.42000000000000021</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" s="252">
         <f t="shared" si="9"/>
         <v>43</v>
@@ -6816,7 +6858,7 @@
         <v>0.43000000000000022</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" s="252">
         <f t="shared" si="9"/>
         <v>44</v>
@@ -6861,7 +6903,7 @@
         <v>0.44000000000000022</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" s="252">
         <f t="shared" si="9"/>
         <v>45</v>
@@ -6909,7 +6951,7 @@
         <v>0.45000000000000023</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58" s="252">
         <f t="shared" si="9"/>
         <v>46</v>
@@ -6959,7 +7001,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59" s="280">
         <f t="shared" si="9"/>
         <v>47</v>
@@ -7005,8 +7047,11 @@
         <f t="shared" si="7"/>
         <v>0.47000000000000025</v>
       </c>
-    </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N59" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" s="313">
         <f t="shared" si="9"/>
         <v>48</v>
@@ -7057,7 +7102,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61" s="252">
         <f t="shared" si="9"/>
         <v>49</v>
@@ -7104,7 +7149,7 @@
         <v>0.49000000000000027</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62" s="252">
         <f t="shared" si="9"/>
         <v>50</v>
@@ -7149,7 +7194,7 @@
         <v>0.50000000000000022</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A63" s="252">
         <f t="shared" si="9"/>
         <v>51</v>
@@ -7196,7 +7241,7 @@
         <v>0.51000000000000023</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A64" s="252">
         <f t="shared" si="9"/>
         <v>52</v>
@@ -7244,22 +7289,22 @@
         <v>0.52000000000000024</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A65" s="252">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A65" s="333">
         <f t="shared" si="9"/>
         <v>53</v>
       </c>
-      <c r="B65" s="254" t="s">
+      <c r="B65" s="334" t="s">
         <v>177</v>
       </c>
-      <c r="C65" s="251"/>
-      <c r="D65" s="244">
+      <c r="C65" s="335"/>
+      <c r="D65" s="336">
         <v>1.1200000000000001</v>
       </c>
-      <c r="E65" s="245">
+      <c r="E65" s="337">
         <v>168836.53</v>
       </c>
-      <c r="F65" s="246">
+      <c r="F65" s="337">
         <v>239116.53</v>
       </c>
       <c r="G65" s="247">
@@ -7291,7 +7336,7 @@
         <v>0.53000000000000025</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" s="252">
         <f t="shared" si="9"/>
         <v>54</v>
@@ -7338,7 +7383,7 @@
         <v>0.54000000000000026</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" s="252">
         <f t="shared" si="9"/>
         <v>55</v>
@@ -7385,7 +7430,7 @@
         <v>0.55000000000000027</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68" s="252">
         <f t="shared" si="9"/>
         <v>56</v>
@@ -7433,12 +7478,12 @@
         <v>0.56000000000000028</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A69" s="252">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A69" s="341">
         <f t="shared" si="9"/>
         <v>57</v>
       </c>
-      <c r="B69" s="254" t="s">
+      <c r="B69" s="342" t="s">
         <v>181</v>
       </c>
       <c r="C69" s="251"/>
@@ -7481,7 +7526,7 @@
         <v>0.57000000000000028</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" s="252">
         <f t="shared" si="9"/>
         <v>58</v>
@@ -7529,22 +7574,22 @@
         <v>0.58000000000000029</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A71" s="280">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A71" s="333">
         <f t="shared" si="9"/>
         <v>59</v>
       </c>
-      <c r="B71" s="281" t="s">
+      <c r="B71" s="334" t="s">
         <v>183</v>
       </c>
-      <c r="C71" s="282"/>
-      <c r="D71" s="273">
+      <c r="C71" s="335"/>
+      <c r="D71" s="336">
         <v>1.34</v>
       </c>
-      <c r="E71" s="274">
+      <c r="E71" s="337">
         <v>202000.59</v>
       </c>
-      <c r="F71" s="274"/>
+      <c r="F71" s="337"/>
       <c r="G71" s="275">
         <f t="shared" si="0"/>
         <v>202000.59</v>
@@ -7574,7 +7619,7 @@
         <v>0.5900000000000003</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" s="252">
         <f t="shared" si="9"/>
         <v>60</v>
@@ -7621,7 +7666,7 @@
         <v>0.60000000000000031</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" s="252">
         <f t="shared" si="9"/>
         <v>61</v>
@@ -7669,7 +7714,7 @@
         <v>0.61000000000000032</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74" s="252">
         <f t="shared" si="9"/>
         <v>62</v>
@@ -7716,7 +7761,7 @@
         <v>0.62000000000000033</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A75" s="252">
         <f t="shared" si="9"/>
         <v>63</v>
@@ -7764,7 +7809,7 @@
         <v>0.63000000000000034</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A76" s="252">
         <f t="shared" si="9"/>
         <v>64</v>
@@ -7811,7 +7856,7 @@
         <v>0.64000000000000035</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A77" s="252">
         <f t="shared" si="9"/>
         <v>65</v>
@@ -7858,10 +7903,10 @@
         <v>0.65000000000000036</v>
       </c>
       <c r="N77" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A78" s="252">
         <f t="shared" si="9"/>
         <v>66</v>
@@ -7908,7 +7953,7 @@
         <v>0.66000000000000036</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A79" s="252">
         <f t="shared" si="9"/>
         <v>67</v>
@@ -7955,7 +8000,7 @@
         <v>0.67000000000000037</v>
       </c>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A80" s="252">
         <f t="shared" si="9"/>
         <v>68</v>
@@ -8002,7 +8047,7 @@
         <v>0.68000000000000038</v>
       </c>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A81" s="252">
         <f t="shared" si="9"/>
         <v>69</v>
@@ -8049,7 +8094,7 @@
         <v>0.69000000000000039</v>
       </c>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A82" s="280">
         <f t="shared" si="9"/>
         <v>70</v>
@@ -8097,10 +8142,10 @@
         <v>0.7000000000000004</v>
       </c>
       <c r="N82" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A83" s="252">
         <f t="shared" si="9"/>
         <v>71</v>
@@ -8147,7 +8192,7 @@
         <v>0.71000000000000041</v>
       </c>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A84" s="252">
         <f t="shared" si="9"/>
         <v>72</v>
@@ -8195,7 +8240,7 @@
         <v>0.72000000000000042</v>
       </c>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A85" s="252">
         <f t="shared" si="9"/>
         <v>73</v>
@@ -8243,7 +8288,7 @@
         <v>0.73000000000000043</v>
       </c>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A86" s="252">
         <f t="shared" si="9"/>
         <v>74</v>
@@ -8290,7 +8335,7 @@
         <v>0.74000000000000044</v>
       </c>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A87" s="252">
         <f t="shared" si="9"/>
         <v>75</v>
@@ -8338,7 +8383,7 @@
         <v>0.75000000000000044</v>
       </c>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A88" s="252">
         <f t="shared" si="9"/>
         <v>76</v>
@@ -8386,7 +8431,7 @@
         <v>0.76000000000000045</v>
       </c>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A89" s="252">
         <f t="shared" si="9"/>
         <v>77</v>
@@ -8433,7 +8478,7 @@
         <v>0.77000000000000046</v>
       </c>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A90" s="252">
         <f t="shared" si="9"/>
         <v>78</v>
@@ -8480,7 +8525,7 @@
         <v>0.78000000000000047</v>
       </c>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A91" s="252">
         <f t="shared" si="9"/>
         <v>79</v>
@@ -8528,7 +8573,7 @@
         <v>0.79000000000000048</v>
       </c>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A92" s="252">
         <f t="shared" si="9"/>
         <v>80</v>
@@ -8573,7 +8618,7 @@
         <v>0.80000000000000049</v>
       </c>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A93" s="280">
         <f t="shared" si="9"/>
         <v>81</v>
@@ -8620,10 +8665,10 @@
         <v>0.8100000000000005</v>
       </c>
       <c r="N93" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A94" s="252">
         <f t="shared" si="9"/>
         <v>82</v>
@@ -8671,7 +8716,7 @@
         <v>0.82000000000000051</v>
       </c>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A95" s="323">
         <f t="shared" si="9"/>
         <v>83</v>
@@ -8718,7 +8763,7 @@
         <v>0.83000000000000052</v>
       </c>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A96" s="323">
         <f t="shared" si="9"/>
         <v>84</v>
@@ -8766,7 +8811,7 @@
         <v>0.84000000000000052</v>
       </c>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A97" s="252">
         <f t="shared" si="9"/>
         <v>85</v>
@@ -8814,7 +8859,7 @@
         <v>0.85000000000000053</v>
       </c>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A98" s="252">
         <f t="shared" si="9"/>
         <v>86</v>
@@ -8862,7 +8907,7 @@
         <v>0.86000000000000054</v>
       </c>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A99" s="252">
         <f t="shared" ref="A99:A115" si="24">A98+1</f>
         <v>87</v>
@@ -8909,7 +8954,7 @@
         <v>0.87000000000000055</v>
       </c>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A100" s="252">
         <f t="shared" si="24"/>
         <v>88</v>
@@ -8956,7 +9001,7 @@
         <v>0.88000000000000056</v>
       </c>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A101" s="252">
         <f t="shared" si="24"/>
         <v>89</v>
@@ -9004,7 +9049,7 @@
         <v>0.89000000000000057</v>
       </c>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A102" s="252">
         <f t="shared" si="24"/>
         <v>90</v>
@@ -9051,7 +9096,7 @@
         <v>0.90000000000000058</v>
       </c>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A103" s="252">
         <f t="shared" si="24"/>
         <v>91</v>
@@ -9096,7 +9141,7 @@
         <v>0.91000000000000059</v>
       </c>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A104" s="252">
         <f t="shared" si="24"/>
         <v>92</v>
@@ -9144,7 +9189,7 @@
         <v>0.9200000000000006</v>
       </c>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A105" s="280">
         <f t="shared" si="24"/>
         <v>93</v>
@@ -9159,14 +9204,17 @@
       <c r="E105" s="274">
         <v>15075.93</v>
       </c>
-      <c r="F105" s="274"/>
+      <c r="F105" s="274">
+        <f>E105</f>
+        <v>15075.93</v>
+      </c>
       <c r="G105" s="275">
         <f t="shared" si="16"/>
-        <v>15075.93</v>
+        <v>0</v>
       </c>
       <c r="H105" s="275">
         <f t="shared" si="20"/>
-        <v>452.27789999999999</v>
+        <v>0</v>
       </c>
       <c r="I105" s="271">
         <f t="shared" si="17"/>
@@ -9178,18 +9226,18 @@
       </c>
       <c r="K105" s="276">
         <f t="shared" si="19"/>
-        <v>30603.93</v>
+        <v>15075.93</v>
       </c>
       <c r="L105" s="277">
         <f t="shared" si="23"/>
-        <v>31521.93</v>
+        <v>15527.93</v>
       </c>
       <c r="M105" s="205">
         <f t="shared" si="21"/>
         <v>0.9300000000000006</v>
       </c>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A106" s="252">
         <f t="shared" si="24"/>
         <v>94</v>
@@ -9237,13 +9285,13 @@
         <v>0.94000000000000061</v>
       </c>
     </row>
-    <row r="107" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="252">
         <f t="shared" si="24"/>
         <v>95</v>
       </c>
       <c r="B107" s="254" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C107" s="251"/>
       <c r="D107" s="244">
@@ -9285,7 +9333,7 @@
         <v>0.95000000000000062</v>
       </c>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A108" s="252">
         <f t="shared" si="24"/>
         <v>96</v>
@@ -9336,7 +9384,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A109" s="252">
         <f t="shared" si="24"/>
         <v>97</v>
@@ -9384,7 +9432,7 @@
         <v>0.97000000000000064</v>
       </c>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A110" s="252">
         <f t="shared" si="24"/>
         <v>98</v>
@@ -9432,7 +9480,7 @@
         <v>0.98000000000000065</v>
       </c>
     </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A111" s="252">
         <f t="shared" si="24"/>
         <v>99</v>
@@ -9479,7 +9527,7 @@
         <v>0.99000000000000066</v>
       </c>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A112" s="252">
         <f t="shared" si="24"/>
         <v>100</v>
@@ -9527,7 +9575,7 @@
         <v>1.0000000000000007</v>
       </c>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A113" s="280">
         <f t="shared" si="24"/>
         <v>101</v>
@@ -9542,14 +9590,17 @@
       <c r="E113" s="274">
         <v>15076.01</v>
       </c>
-      <c r="F113" s="274"/>
+      <c r="F113" s="274">
+        <f>E113</f>
+        <v>15076.01</v>
+      </c>
       <c r="G113" s="275">
         <f t="shared" si="16"/>
-        <v>15076.01</v>
+        <v>0</v>
       </c>
       <c r="H113" s="275">
         <f t="shared" si="20"/>
-        <v>452.28030000000001</v>
+        <v>0</v>
       </c>
       <c r="I113" s="271">
         <f t="shared" si="25"/>
@@ -9561,18 +9612,18 @@
       </c>
       <c r="K113" s="276">
         <f t="shared" si="27"/>
-        <v>30604.01</v>
+        <v>15076.01</v>
       </c>
       <c r="L113" s="277">
         <f t="shared" si="23"/>
-        <v>31522.01</v>
+        <v>15528.01</v>
       </c>
       <c r="M113" s="205">
         <f t="shared" si="21"/>
         <v>1.0100000000000007</v>
       </c>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A114" s="252">
         <f t="shared" si="24"/>
         <v>102</v>
@@ -9619,13 +9670,13 @@
         <v>1.0200000000000007</v>
       </c>
     </row>
-    <row r="115" spans="1:13" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A115" s="252">
         <f t="shared" si="24"/>
         <v>103</v>
       </c>
       <c r="B115" s="254" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C115" s="251"/>
       <c r="D115" s="244">
@@ -9666,7 +9717,7 @@
         <v>1.0300000000000007</v>
       </c>
     </row>
-    <row r="116" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A116" s="252"/>
       <c r="B116" s="256"/>
       <c r="C116" s="251"/>
@@ -9681,7 +9732,7 @@
       <c r="L116" s="250"/>
       <c r="M116" s="205"/>
     </row>
-    <row r="117" spans="1:13" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:13" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A117" s="257"/>
       <c r="B117" s="258"/>
       <c r="C117" s="258"/>
@@ -9695,15 +9746,15 @@
       </c>
       <c r="F117" s="261">
         <f>SUM(F13:F116)</f>
-        <v>15176046.170695035</v>
+        <v>15206198.110695034</v>
       </c>
       <c r="G117" s="261">
         <f t="shared" si="28"/>
-        <v>19335408.389304973</v>
+        <v>19305256.449304972</v>
       </c>
       <c r="H117" s="261">
         <f t="shared" si="28"/>
-        <v>587960.43809999991</v>
+        <v>587055.87989999994</v>
       </c>
       <c r="I117" s="262">
         <f t="shared" si="28"/>
@@ -9715,95 +9766,94 @@
       </c>
       <c r="K117" s="263">
         <f t="shared" si="28"/>
-        <v>35022169.560000002</v>
+        <v>34991113.560000002</v>
       </c>
       <c r="L117" s="263">
         <f t="shared" si="28"/>
-        <v>36072824.560000002</v>
-      </c>
-    </row>
-    <row r="118" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>36040836.560000002</v>
+      </c>
+    </row>
+    <row r="118" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B118" s="264"/>
       <c r="C118" s="264"/>
     </row>
-    <row r="119" spans="1:13" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="120" spans="1:13" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B120" s="368" t="s">
+    <row r="119" spans="1:13" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="120" spans="1:13" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B120" s="362" t="s">
         <v>286</v>
       </c>
-      <c r="C120" s="368"/>
-      <c r="D120" s="368"/>
-      <c r="E120" s="368"/>
-      <c r="F120" s="368"/>
-      <c r="G120" s="368"/>
-      <c r="H120" s="368"/>
-      <c r="I120" s="368"/>
-      <c r="J120" s="368"/>
-      <c r="K120" s="368"/>
-    </row>
-    <row r="121" spans="1:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B121" s="368"/>
-      <c r="C121" s="368"/>
-      <c r="D121" s="368"/>
-      <c r="E121" s="368"/>
-      <c r="F121" s="368"/>
-      <c r="G121" s="368"/>
-      <c r="H121" s="368"/>
-      <c r="I121" s="368"/>
-      <c r="J121" s="368"/>
-      <c r="K121" s="368"/>
-    </row>
-    <row r="122" spans="1:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B122" s="368"/>
-      <c r="C122" s="368"/>
-      <c r="D122" s="368"/>
-      <c r="E122" s="368"/>
-      <c r="F122" s="368"/>
-      <c r="G122" s="368"/>
-      <c r="H122" s="368"/>
-      <c r="I122" s="368"/>
-      <c r="J122" s="368"/>
-      <c r="K122" s="368"/>
-    </row>
-    <row r="123" spans="1:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B123" s="368"/>
-      <c r="C123" s="368"/>
-      <c r="D123" s="368"/>
-      <c r="E123" s="368"/>
-      <c r="F123" s="368"/>
-      <c r="G123" s="368"/>
-      <c r="H123" s="368"/>
-      <c r="I123" s="368"/>
-      <c r="J123" s="368"/>
-      <c r="K123" s="368"/>
-    </row>
-    <row r="124" spans="1:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B124" s="368"/>
-      <c r="C124" s="368"/>
-      <c r="D124" s="368"/>
-      <c r="E124" s="368"/>
-      <c r="F124" s="368"/>
-      <c r="G124" s="368"/>
-      <c r="H124" s="368"/>
-      <c r="I124" s="368"/>
-      <c r="J124" s="368"/>
-      <c r="K124" s="368"/>
-    </row>
-    <row r="125" spans="1:13" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B125" s="368"/>
-      <c r="C125" s="368"/>
-      <c r="D125" s="368"/>
-      <c r="E125" s="368"/>
-      <c r="F125" s="368"/>
-      <c r="G125" s="368"/>
-      <c r="H125" s="368"/>
-      <c r="I125" s="368"/>
-      <c r="J125" s="368"/>
-      <c r="K125" s="368"/>
+      <c r="C120" s="362"/>
+      <c r="D120" s="362"/>
+      <c r="E120" s="362"/>
+      <c r="F120" s="362"/>
+      <c r="G120" s="362"/>
+      <c r="H120" s="362"/>
+      <c r="I120" s="362"/>
+      <c r="J120" s="362"/>
+      <c r="K120" s="362"/>
+    </row>
+    <row r="121" spans="1:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B121" s="362"/>
+      <c r="C121" s="362"/>
+      <c r="D121" s="362"/>
+      <c r="E121" s="362"/>
+      <c r="F121" s="362"/>
+      <c r="G121" s="362"/>
+      <c r="H121" s="362"/>
+      <c r="I121" s="362"/>
+      <c r="J121" s="362"/>
+      <c r="K121" s="362"/>
+    </row>
+    <row r="122" spans="1:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B122" s="362"/>
+      <c r="C122" s="362"/>
+      <c r="D122" s="362"/>
+      <c r="E122" s="362"/>
+      <c r="F122" s="362"/>
+      <c r="G122" s="362"/>
+      <c r="H122" s="362"/>
+      <c r="I122" s="362"/>
+      <c r="J122" s="362"/>
+      <c r="K122" s="362"/>
+    </row>
+    <row r="123" spans="1:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B123" s="362"/>
+      <c r="C123" s="362"/>
+      <c r="D123" s="362"/>
+      <c r="E123" s="362"/>
+      <c r="F123" s="362"/>
+      <c r="G123" s="362"/>
+      <c r="H123" s="362"/>
+      <c r="I123" s="362"/>
+      <c r="J123" s="362"/>
+      <c r="K123" s="362"/>
+    </row>
+    <row r="124" spans="1:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B124" s="362"/>
+      <c r="C124" s="362"/>
+      <c r="D124" s="362"/>
+      <c r="E124" s="362"/>
+      <c r="F124" s="362"/>
+      <c r="G124" s="362"/>
+      <c r="H124" s="362"/>
+      <c r="I124" s="362"/>
+      <c r="J124" s="362"/>
+      <c r="K124" s="362"/>
+    </row>
+    <row r="125" spans="1:13" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B125" s="362"/>
+      <c r="C125" s="362"/>
+      <c r="D125" s="362"/>
+      <c r="E125" s="362"/>
+      <c r="F125" s="362"/>
+      <c r="G125" s="362"/>
+      <c r="H125" s="362"/>
+      <c r="I125" s="362"/>
+      <c r="J125" s="362"/>
+      <c r="K125" s="362"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B120:K125"/>
     <mergeCell ref="D1:K1"/>
     <mergeCell ref="A4:L8"/>
     <mergeCell ref="A11:A12"/>
@@ -9820,44 +9870,142 @@
     <mergeCell ref="I11:I12"/>
     <mergeCell ref="J11:J12"/>
     <mergeCell ref="L11:L12"/>
+    <mergeCell ref="B120:K125"/>
   </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
+  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="3" scale="85" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56D35F41-74CB-4294-A7A2-EC3C67574818}">
-  <dimension ref="B4:M9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B4:N20"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="12.77734375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="4" spans="2:13" ht="165" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:14" ht="144" x14ac:dyDescent="0.3">
       <c r="B4" s="226" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="384" t="s">
+        <v>413</v>
+      </c>
+      <c r="C6" s="384"/>
+      <c r="D6" s="384"/>
+      <c r="E6" s="384"/>
+      <c r="F6" s="384"/>
+      <c r="G6" s="384"/>
+      <c r="H6" s="384"/>
+      <c r="I6" s="384"/>
+      <c r="J6" s="384"/>
+      <c r="L6" s="226" t="s">
         <v>414</v>
       </c>
-    </row>
-    <row r="6" spans="2:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="369" t="s">
-        <v>415</v>
-      </c>
-      <c r="C6" s="369"/>
-      <c r="D6" s="369"/>
-      <c r="E6" s="369"/>
-      <c r="F6" s="369"/>
-      <c r="G6" s="369"/>
-      <c r="H6" s="369"/>
-      <c r="I6" s="369"/>
-      <c r="J6" s="369"/>
-      <c r="L6" s="226" t="s">
-        <v>401</v>
-      </c>
       <c r="M6" s="226" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B9" s="383" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B9" s="332" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B13" s="338" t="s">
         <v>416</v>
+      </c>
+      <c r="C13" s="338"/>
+      <c r="D13" s="338"/>
+      <c r="E13" s="338"/>
+      <c r="F13" s="338"/>
+      <c r="G13" s="338"/>
+      <c r="H13" s="338"/>
+      <c r="I13" s="338"/>
+      <c r="J13" s="338"/>
+      <c r="K13" s="338"/>
+      <c r="L13" s="338"/>
+      <c r="M13" s="338"/>
+      <c r="N13" s="338"/>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B14" s="338" t="s">
+        <v>417</v>
+      </c>
+      <c r="C14" s="339">
+        <v>194996.59</v>
+      </c>
+      <c r="D14" s="338"/>
+      <c r="E14" s="338"/>
+      <c r="F14" s="338"/>
+      <c r="G14" s="338"/>
+      <c r="H14" s="338"/>
+      <c r="I14" s="338"/>
+      <c r="J14" s="338"/>
+      <c r="K14" s="338"/>
+      <c r="L14" s="338"/>
+      <c r="M14" s="338"/>
+      <c r="N14" s="338"/>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B15" s="338" t="s">
+        <v>418</v>
+      </c>
+      <c r="C15" s="339">
+        <v>15075.93</v>
+      </c>
+      <c r="D15" s="338"/>
+      <c r="E15" s="338"/>
+      <c r="F15" s="338"/>
+      <c r="G15" s="338"/>
+      <c r="H15" s="338"/>
+      <c r="I15" s="338"/>
+      <c r="J15" s="338"/>
+      <c r="K15" s="338"/>
+      <c r="L15" s="338"/>
+      <c r="M15" s="338"/>
+      <c r="N15" s="338"/>
+    </row>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B16" s="338" t="s">
+        <v>419</v>
+      </c>
+      <c r="C16" s="339">
+        <v>15076.01</v>
+      </c>
+      <c r="D16" s="338"/>
+      <c r="E16" s="338"/>
+      <c r="F16" s="338"/>
+      <c r="G16" s="338"/>
+      <c r="H16" s="338"/>
+      <c r="I16" s="338"/>
+      <c r="J16" s="338"/>
+      <c r="K16" s="338"/>
+      <c r="L16" s="338"/>
+      <c r="M16" s="338"/>
+      <c r="N16" s="338"/>
+    </row>
+    <row r="17" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B17" s="338"/>
+      <c r="C17" s="338"/>
+      <c r="D17" s="338"/>
+      <c r="E17" s="338"/>
+      <c r="F17" s="338"/>
+      <c r="G17" s="338"/>
+      <c r="H17" s="338"/>
+      <c r="I17" s="338"/>
+      <c r="J17" s="338"/>
+      <c r="K17" s="338"/>
+      <c r="L17" s="338"/>
+      <c r="M17" s="338"/>
+      <c r="N17" s="338"/>
+    </row>
+    <row r="20" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B20" s="340" t="s">
+        <v>421</v>
       </c>
     </row>
   </sheetData>
@@ -9871,27 +10019,27 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R198"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" style="9" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="62.7109375" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="12" customWidth="1"/>
-    <col min="8" max="8" width="4.5703125" customWidth="1"/>
-    <col min="9" max="9" width="35.85546875" customWidth="1"/>
-    <col min="10" max="10" width="12.28515625" customWidth="1"/>
-    <col min="11" max="11" width="9.28515625" customWidth="1"/>
-    <col min="12" max="12" width="11.140625" customWidth="1"/>
+    <col min="2" max="2" width="5.88671875" style="9" customWidth="1"/>
+    <col min="3" max="3" width="11.44140625" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="62.6640625" customWidth="1"/>
+    <col min="5" max="5" width="14.5546875" customWidth="1"/>
+    <col min="6" max="6" width="14.5546875" style="12" customWidth="1"/>
+    <col min="8" max="8" width="4.5546875" customWidth="1"/>
+    <col min="9" max="9" width="35.88671875" customWidth="1"/>
+    <col min="10" max="10" width="12.33203125" customWidth="1"/>
+    <col min="11" max="11" width="9.33203125" customWidth="1"/>
+    <col min="12" max="12" width="11.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="370" t="s">
+    <row r="1" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="385" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="370"/>
-      <c r="C1" s="370"/>
+      <c r="B1" s="385"/>
+      <c r="C1" s="385"/>
       <c r="I1" s="40"/>
       <c r="J1" s="40" t="s">
         <v>20</v>
@@ -9905,31 +10053,31 @@
       <c r="Q1" s="40"/>
       <c r="R1" s="40"/>
     </row>
-    <row r="2" spans="1:18" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="370"/>
-      <c r="B2" s="370"/>
-      <c r="C2" s="370"/>
+    <row r="2" spans="1:18" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="385"/>
+      <c r="B2" s="385"/>
+      <c r="C2" s="385"/>
       <c r="J2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" ht="15.6" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="30" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
       <c r="D3" s="1"/>
-      <c r="E3" s="371" t="s">
+      <c r="E3" s="386" t="s">
         <v>49</v>
       </c>
-      <c r="F3" s="372"/>
+      <c r="F3" s="387"/>
       <c r="G3" s="1"/>
       <c r="J3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B4" s="8" t="s">
         <v>6</v>
       </c>
@@ -9948,7 +10096,7 @@
       <c r="N4" s="9"/>
       <c r="O4" s="36"/>
     </row>
-    <row r="5" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="8" t="s">
         <v>0</v>
       </c>
@@ -9961,7 +10109,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="8" t="s">
         <v>40</v>
       </c>
@@ -9988,7 +10136,7 @@
       <c r="Q6" s="32"/>
       <c r="R6" s="32"/>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
       <c r="D7" s="8" t="s">
@@ -10008,7 +10156,7 @@
       <c r="P7"/>
       <c r="Q7"/>
     </row>
-    <row r="8" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B8" s="8" t="s">
         <v>7</v>
       </c>
@@ -10031,7 +10179,7 @@
       <c r="Q8" s="35"/>
       <c r="R8" s="35"/>
     </row>
-    <row r="9" spans="1:18" s="3" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="3" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B9" s="4">
         <v>1</v>
       </c>
@@ -10058,7 +10206,7 @@
       <c r="Q9" s="35"/>
       <c r="R9" s="35"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B10" s="7"/>
       <c r="D10" t="s">
         <v>248</v>
@@ -10084,7 +10232,7 @@
       <c r="Q10" s="35"/>
       <c r="R10" s="35"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B11" s="7"/>
       <c r="D11" t="s">
         <v>50</v>
@@ -10105,7 +10253,7 @@
       <c r="Q11" s="35"/>
       <c r="R11" s="35"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B12" s="7"/>
       <c r="D12" t="s">
         <v>51</v>
@@ -10131,7 +10279,7 @@
       <c r="Q12" s="35"/>
       <c r="R12" s="35"/>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B13" s="7"/>
       <c r="D13" t="s">
         <v>52</v>
@@ -10152,7 +10300,7 @@
       <c r="Q13" s="35"/>
       <c r="R13" s="35"/>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B14" s="7"/>
       <c r="D14" t="s">
         <v>53</v>
@@ -10173,7 +10321,7 @@
       <c r="Q14" s="35"/>
       <c r="R14" s="35"/>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B15" s="7"/>
       <c r="D15" t="s">
         <v>255</v>
@@ -10194,7 +10342,7 @@
       <c r="Q15" s="35"/>
       <c r="R15" s="35"/>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B16" s="7"/>
       <c r="D16" t="s">
         <v>256</v>
@@ -10215,7 +10363,7 @@
       <c r="Q16" s="35"/>
       <c r="R16" s="35"/>
     </row>
-    <row r="17" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B17" s="7"/>
       <c r="D17" t="s">
         <v>55</v>
@@ -10237,7 +10385,7 @@
       <c r="O17" s="35"/>
       <c r="P17" s="35"/>
     </row>
-    <row r="18" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B18" s="7"/>
       <c r="D18" t="s">
         <v>56</v>
@@ -10263,7 +10411,7 @@
       <c r="O18" s="35"/>
       <c r="P18" s="35"/>
     </row>
-    <row r="19" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B19" s="7"/>
       <c r="D19" t="s">
         <v>57</v>
@@ -10285,7 +10433,7 @@
       <c r="O19" s="35"/>
       <c r="P19" s="35"/>
     </row>
-    <row r="20" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B20" s="7"/>
       <c r="D20" t="s">
         <v>58</v>
@@ -10304,7 +10452,7 @@
       <c r="O20" s="35"/>
       <c r="P20" s="35"/>
     </row>
-    <row r="21" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B21" s="7"/>
       <c r="D21" t="s">
         <v>59</v>
@@ -10326,7 +10474,7 @@
       <c r="O21" s="35"/>
       <c r="P21" s="35"/>
     </row>
-    <row r="22" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B22" s="7"/>
       <c r="D22" t="s">
         <v>60</v>
@@ -10345,7 +10493,7 @@
       <c r="O22" s="35"/>
       <c r="P22" s="35"/>
     </row>
-    <row r="23" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B23" s="7"/>
       <c r="D23" t="s">
         <v>61</v>
@@ -10364,7 +10512,7 @@
       <c r="O23" s="35"/>
       <c r="P23" s="35"/>
     </row>
-    <row r="24" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B24" s="7"/>
       <c r="D24" t="s">
         <v>62</v>
@@ -10390,7 +10538,7 @@
       <c r="O24" s="35"/>
       <c r="P24" s="35"/>
     </row>
-    <row r="25" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B25" s="7"/>
       <c r="D25" t="s">
         <v>54</v>
@@ -10417,7 +10565,7 @@
       <c r="O25" s="35"/>
       <c r="P25" s="35"/>
     </row>
-    <row r="26" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B26" s="7"/>
       <c r="D26" t="s">
         <v>262</v>
@@ -10438,7 +10586,7 @@
       <c r="O26" s="35"/>
       <c r="P26" s="35"/>
     </row>
-    <row r="27" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B27" s="7">
         <v>2</v>
       </c>
@@ -10461,7 +10609,7 @@
       <c r="O27" s="35"/>
       <c r="P27" s="35"/>
     </row>
-    <row r="28" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B28" s="7"/>
       <c r="D28" t="s">
         <v>63</v>
@@ -10485,7 +10633,7 @@
       <c r="O28" s="35"/>
       <c r="P28" s="35"/>
     </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B29" s="7"/>
       <c r="D29" t="s">
         <v>64</v>
@@ -10507,7 +10655,7 @@
       <c r="O29" s="35"/>
       <c r="P29" s="35"/>
     </row>
-    <row r="30" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B30" s="7"/>
       <c r="D30" t="s">
         <v>65</v>
@@ -10529,7 +10677,7 @@
       <c r="O30" s="35"/>
       <c r="P30" s="35"/>
     </row>
-    <row r="31" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B31" s="7"/>
       <c r="D31" t="s">
         <v>66</v>
@@ -10548,7 +10696,7 @@
       <c r="O31" s="35"/>
       <c r="P31" s="35"/>
     </row>
-    <row r="32" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B32" s="7"/>
       <c r="D32" t="s">
         <v>67</v>
@@ -10567,7 +10715,7 @@
       <c r="O32" s="35"/>
       <c r="P32" s="35"/>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B33" s="7"/>
       <c r="D33" t="s">
         <v>68</v>
@@ -10586,7 +10734,7 @@
       <c r="O33" s="35"/>
       <c r="P33" s="35"/>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B34" s="7"/>
       <c r="D34" t="s">
         <v>259</v>
@@ -10608,7 +10756,7 @@
       <c r="O34" s="35"/>
       <c r="P34" s="35"/>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B35" s="7"/>
       <c r="D35" t="s">
         <v>260</v>
@@ -10630,7 +10778,7 @@
       <c r="O35" s="35"/>
       <c r="P35" s="35"/>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B36" s="7"/>
       <c r="D36" t="s">
         <v>261</v>
@@ -10652,7 +10800,7 @@
       <c r="O36" s="35"/>
       <c r="P36" s="35"/>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B37" s="7"/>
       <c r="D37" t="s">
         <v>257</v>
@@ -10674,7 +10822,7 @@
       <c r="O37" s="35"/>
       <c r="P37" s="35"/>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B38" s="7"/>
       <c r="D38" t="s">
         <v>258</v>
@@ -10696,7 +10844,7 @@
       <c r="O38" s="35"/>
       <c r="P38" s="35"/>
     </row>
-    <row r="39" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B39" s="7"/>
       <c r="D39" t="s">
         <v>20</v>
@@ -10723,7 +10871,7 @@
       <c r="O39" s="35"/>
       <c r="P39" s="35"/>
     </row>
-    <row r="40" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B40" s="7">
         <v>3</v>
       </c>
@@ -10746,7 +10894,7 @@
       <c r="O40" s="35"/>
       <c r="P40" s="35"/>
     </row>
-    <row r="41" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B41" s="7">
         <v>4</v>
       </c>
@@ -10769,7 +10917,7 @@
       <c r="Q41" s="35"/>
       <c r="R41" s="35"/>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B42" s="7"/>
       <c r="D42" s="96" t="s">
         <v>263</v>
@@ -10792,7 +10940,7 @@
       <c r="Q42" s="35"/>
       <c r="R42" s="35"/>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B43" s="7"/>
       <c r="D43" s="97" t="s">
         <v>264</v>
@@ -10820,7 +10968,7 @@
       <c r="Q43" s="12"/>
       <c r="R43" s="35"/>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B44" s="7"/>
       <c r="D44" s="97" t="s">
         <v>265</v>
@@ -10836,7 +10984,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B45" s="7"/>
       <c r="D45" s="97" t="s">
         <v>266</v>
@@ -10850,7 +10998,7 @@
       </c>
       <c r="J45" s="34"/>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B46" s="7"/>
       <c r="D46" s="97" t="s">
         <v>267</v>
@@ -10863,7 +11011,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="47" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B47" s="7"/>
       <c r="D47" s="58" t="s">
         <v>20</v>
@@ -10882,7 +11030,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="48" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="2"/>
       <c r="B48" s="7">
         <v>5</v>
@@ -10900,7 +11048,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="49" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B49" s="7"/>
       <c r="D49" t="s">
         <v>268</v>
@@ -10915,7 +11063,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="50" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B50" s="7"/>
       <c r="D50" t="s">
         <v>269</v>
@@ -10928,7 +11076,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="51" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B51" s="7"/>
       <c r="D51" t="s">
         <v>71</v>
@@ -10939,7 +11087,7 @@
       <c r="F51" s="56"/>
       <c r="G51" s="33"/>
     </row>
-    <row r="52" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B52" s="7"/>
       <c r="D52" t="s">
         <v>270</v>
@@ -10955,7 +11103,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="53" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B53" s="7">
         <v>6</v>
       </c>
@@ -10970,7 +11118,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="54" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B54" s="7"/>
       <c r="D54" s="63" t="s">
         <v>271</v>
@@ -10983,7 +11131,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="55" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B55" s="7"/>
       <c r="D55" t="s">
         <v>20</v>
@@ -10999,7 +11147,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="56" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B56" s="7">
         <v>7</v>
       </c>
@@ -11014,7 +11162,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="57" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B57" s="7"/>
       <c r="D57" s="63" t="s">
         <v>272</v>
@@ -11027,7 +11175,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="58" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B58" s="7"/>
       <c r="D58" s="63" t="s">
         <v>74</v>
@@ -11040,7 +11188,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="59" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B59" s="7"/>
       <c r="D59" s="63" t="s">
         <v>70</v>
@@ -11050,7 +11198,7 @@
       </c>
       <c r="F59" s="10"/>
     </row>
-    <row r="60" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B60" s="7"/>
       <c r="D60" s="63" t="s">
         <v>75</v>
@@ -11063,7 +11211,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="61" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B61" s="7"/>
       <c r="D61" s="63" t="s">
         <v>231</v>
@@ -11082,7 +11230,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="62" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B62" s="7"/>
       <c r="D62" s="63" t="s">
         <v>232</v>
@@ -11095,7 +11243,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="63" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B63" s="7"/>
       <c r="D63" s="63" t="s">
         <v>233</v>
@@ -11110,7 +11258,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="64" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B64" s="7"/>
       <c r="D64" s="63" t="s">
         <v>230</v>
@@ -11123,7 +11271,7 @@
         <v>3822364.73</v>
       </c>
     </row>
-    <row r="65" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B65" s="7">
         <v>8</v>
       </c>
@@ -11135,7 +11283,7 @@
       </c>
       <c r="F65" s="10"/>
     </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B66" s="7"/>
       <c r="D66" s="63" t="s">
         <v>229</v>
@@ -11148,7 +11296,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="67" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B67" s="7"/>
       <c r="D67" t="s">
         <v>16</v>
@@ -11170,7 +11318,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="68" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B68" s="7">
         <v>9</v>
       </c>
@@ -11192,7 +11340,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B69" s="7"/>
       <c r="D69" s="63" t="s">
         <v>78</v>
@@ -11214,7 +11362,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="70" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B70" s="7"/>
       <c r="D70" s="63" t="s">
         <v>79</v>
@@ -11239,7 +11387,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="71" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B71" s="7">
         <v>10</v>
       </c>
@@ -11259,7 +11407,7 @@
       </c>
       <c r="L71" s="9"/>
     </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B72" s="7"/>
       <c r="D72" s="101" t="s">
         <v>80</v>
@@ -11281,7 +11429,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B73" s="7"/>
       <c r="D73" s="63" t="s">
         <v>81</v>
@@ -11303,7 +11451,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B74" s="7"/>
       <c r="D74" s="2" t="s">
         <v>82</v>
@@ -11322,7 +11470,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="75" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B75" s="7"/>
       <c r="D75" s="63" t="s">
         <v>83</v>
@@ -11341,7 +11489,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="76" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B76" s="7"/>
       <c r="D76" s="6" t="s">
         <v>17</v>
@@ -11359,7 +11507,7 @@
       <c r="J76" s="9"/>
       <c r="K76" s="9"/>
     </row>
-    <row r="77" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B77" s="7"/>
       <c r="D77" s="6" t="s">
         <v>84</v>
@@ -11371,7 +11519,7 @@
       <c r="J77" s="9"/>
       <c r="K77" s="9"/>
     </row>
-    <row r="78" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B78" s="7"/>
       <c r="D78" s="6" t="s">
         <v>39</v>
@@ -11383,7 +11531,7 @@
       <c r="J78" s="9"/>
       <c r="K78" s="9"/>
     </row>
-    <row r="79" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B79" s="7"/>
       <c r="D79" s="81" t="s">
         <v>20</v>
@@ -11397,7 +11545,7 @@
       <c r="J79" s="9"/>
       <c r="K79" s="9"/>
     </row>
-    <row r="80" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B80" s="7" t="s">
         <v>20</v>
       </c>
@@ -11413,7 +11561,7 @@
       <c r="J80" s="9"/>
       <c r="K80" s="9"/>
     </row>
-    <row r="81" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B81" s="7"/>
       <c r="D81" s="97"/>
       <c r="E81" s="14">
@@ -11425,7 +11573,7 @@
       <c r="J81" s="9"/>
       <c r="K81" s="9"/>
     </row>
-    <row r="82" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B82" s="7" t="s">
         <v>20</v>
       </c>
@@ -11440,7 +11588,7 @@
       <c r="J82" s="9"/>
       <c r="K82" s="9"/>
     </row>
-    <row r="83" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B83" s="7"/>
       <c r="D83" s="106" t="s">
         <v>85</v>
@@ -11454,7 +11602,7 @@
       <c r="J83" s="9"/>
       <c r="K83" s="9"/>
     </row>
-    <row r="84" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B84" s="7"/>
       <c r="D84" s="58" t="s">
         <v>88</v>
@@ -11469,7 +11617,7 @@
       <c r="J84" s="9"/>
       <c r="K84" s="9"/>
     </row>
-    <row r="85" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B85" s="7"/>
       <c r="D85" s="58" t="s">
         <v>89</v>
@@ -11483,7 +11631,7 @@
       </c>
       <c r="K85" s="9"/>
     </row>
-    <row r="86" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B86" s="7"/>
       <c r="D86" s="58" t="s">
         <v>274</v>
@@ -11497,7 +11645,7 @@
       </c>
       <c r="K86" s="9"/>
     </row>
-    <row r="87" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B87" s="7"/>
       <c r="D87" s="58" t="s">
         <v>90</v>
@@ -11511,7 +11659,7 @@
       </c>
       <c r="K87" s="9"/>
     </row>
-    <row r="88" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B88" s="7"/>
       <c r="D88" s="58" t="s">
         <v>91</v>
@@ -11530,7 +11678,7 @@
       </c>
       <c r="K88" s="9"/>
     </row>
-    <row r="89" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B89" s="7"/>
       <c r="D89" s="106" t="s">
         <v>78</v>
@@ -11542,7 +11690,7 @@
       </c>
       <c r="K89" s="9"/>
     </row>
-    <row r="90" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B90" s="7"/>
       <c r="D90" s="58" t="s">
         <v>92</v>
@@ -11556,7 +11704,7 @@
       </c>
       <c r="K90" s="9"/>
     </row>
-    <row r="91" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B91" s="7"/>
       <c r="D91" s="58" t="s">
         <v>93</v>
@@ -11570,7 +11718,7 @@
       </c>
       <c r="K91" s="9"/>
     </row>
-    <row r="92" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B92" s="7"/>
       <c r="D92" s="58" t="s">
         <v>94</v>
@@ -11586,7 +11734,7 @@
       </c>
       <c r="K92" s="9"/>
     </row>
-    <row r="93" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B93" s="7"/>
       <c r="D93" s="58" t="s">
         <v>95</v>
@@ -11600,7 +11748,7 @@
       </c>
       <c r="K93" s="9"/>
     </row>
-    <row r="94" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B94" s="7"/>
       <c r="D94" s="58" t="s">
         <v>91</v>
@@ -11622,7 +11770,7 @@
       </c>
       <c r="K94" s="9"/>
     </row>
-    <row r="95" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B95" s="7" t="s">
         <v>20</v>
       </c>
@@ -11638,7 +11786,7 @@
       </c>
       <c r="K95" s="9"/>
     </row>
-    <row r="96" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B96" s="7"/>
       <c r="D96" s="96" t="s">
         <v>88</v>
@@ -11652,7 +11800,7 @@
       </c>
       <c r="K96" s="9"/>
     </row>
-    <row r="97" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B97" s="7"/>
       <c r="D97" s="96" t="s">
         <v>93</v>
@@ -11666,7 +11814,7 @@
       </c>
       <c r="K97" s="9"/>
     </row>
-    <row r="98" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B98" s="7"/>
       <c r="D98" s="96" t="s">
         <v>94</v>
@@ -11680,7 +11828,7 @@
       </c>
       <c r="K98" s="9"/>
     </row>
-    <row r="99" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B99" s="7"/>
       <c r="D99" s="96" t="s">
         <v>95</v>
@@ -11695,7 +11843,7 @@
       <c r="J99" s="9"/>
       <c r="K99" s="9"/>
     </row>
-    <row r="100" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B100" s="7"/>
       <c r="D100" s="96" t="s">
         <v>275</v>
@@ -11707,7 +11855,7 @@
       <c r="J100" s="9"/>
       <c r="K100" s="9"/>
     </row>
-    <row r="101" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B101" s="7"/>
       <c r="D101" s="96" t="s">
         <v>91</v>
@@ -11725,7 +11873,7 @@
       <c r="J101" s="9"/>
       <c r="K101" s="9"/>
     </row>
-    <row r="102" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B102" s="7"/>
       <c r="D102" s="4" t="s">
         <v>96</v>
@@ -11743,7 +11891,7 @@
       <c r="J102" s="9"/>
       <c r="K102" s="9"/>
     </row>
-    <row r="103" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B103" s="7"/>
       <c r="D103" s="113" t="s">
         <v>97</v>
@@ -11755,7 +11903,7 @@
       <c r="J103" s="9"/>
       <c r="K103" s="9"/>
     </row>
-    <row r="104" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B104" s="7"/>
       <c r="D104" s="113" t="s">
         <v>86</v>
@@ -11772,7 +11920,7 @@
       <c r="J104" s="9"/>
       <c r="K104" s="9"/>
     </row>
-    <row r="105" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B105" s="7"/>
       <c r="D105" s="113" t="s">
         <v>98</v>
@@ -11784,7 +11932,7 @@
       <c r="J105" s="9"/>
       <c r="K105" s="9"/>
     </row>
-    <row r="106" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B106" s="7"/>
       <c r="D106" s="113" t="s">
         <v>91</v>
@@ -11799,7 +11947,7 @@
       <c r="J106" s="9"/>
       <c r="K106" s="9"/>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B107"/>
       <c r="F107"/>
       <c r="G107" s="12" t="s">
@@ -11808,7 +11956,7 @@
       <c r="J107" s="9"/>
       <c r="K107" s="9"/>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>99</v>
       </c>
@@ -11820,7 +11968,7 @@
       <c r="J108" s="9"/>
       <c r="K108" s="9"/>
     </row>
-    <row r="109" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:11" ht="18" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>100</v>
       </c>
@@ -11833,7 +11981,7 @@
       <c r="J109" s="9"/>
       <c r="K109" s="9"/>
     </row>
-    <row r="110" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:11" ht="18" x14ac:dyDescent="0.35">
       <c r="B110" s="3"/>
       <c r="D110" s="40"/>
       <c r="E110" s="12"/>
@@ -11843,7 +11991,7 @@
       <c r="J110" s="9"/>
       <c r="K110" s="9"/>
     </row>
-    <row r="111" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:11" ht="18" x14ac:dyDescent="0.35">
       <c r="A111" s="115" t="s">
         <v>101</v>
       </c>
@@ -11856,7 +12004,7 @@
       <c r="J111" s="9"/>
       <c r="K111" s="9"/>
     </row>
-    <row r="112" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:11" ht="18" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>102</v>
       </c>
@@ -11869,7 +12017,7 @@
       <c r="J112" s="9"/>
       <c r="K112" s="9"/>
     </row>
-    <row r="113" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:11" ht="18" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>103</v>
       </c>
@@ -11883,7 +12031,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="114" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:11" ht="18" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>241</v>
       </c>
@@ -11897,7 +12045,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="115" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:11" ht="18" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>104</v>
       </c>
@@ -11913,7 +12061,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="116" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:11" ht="18" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>105</v>
       </c>
@@ -11924,7 +12072,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="117" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:11" ht="18" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>106</v>
       </c>
@@ -11932,7 +12080,7 @@
       <c r="D117" s="40"/>
       <c r="E117" s="12"/>
     </row>
-    <row r="118" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:11" ht="18" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>243</v>
       </c>
@@ -11940,7 +12088,7 @@
       <c r="D118" s="40"/>
       <c r="E118" s="12"/>
     </row>
-    <row r="119" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:11" ht="18" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>242</v>
       </c>
@@ -11948,7 +12096,7 @@
       <c r="D119" s="40"/>
       <c r="E119" s="12"/>
     </row>
-    <row r="120" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:11" ht="18" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>24</v>
       </c>
@@ -11958,7 +12106,7 @@
       </c>
       <c r="E120" s="12"/>
     </row>
-    <row r="121" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A121" t="s">
         <v>105</v>
       </c>
@@ -11966,14 +12114,14 @@
       <c r="D121" s="40"/>
       <c r="E121" s="12"/>
     </row>
-    <row r="122" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B122" s="3"/>
       <c r="D122" s="117" t="s">
         <v>107</v>
       </c>
       <c r="E122" s="12"/>
     </row>
-    <row r="123" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:11" ht="18" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>108</v>
       </c>
@@ -11981,7 +12129,7 @@
       <c r="D123" s="116"/>
       <c r="E123" s="12"/>
     </row>
-    <row r="124" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:11" ht="18" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>109</v>
       </c>
@@ -11989,7 +12137,7 @@
       <c r="D124" s="116"/>
       <c r="E124" s="12"/>
     </row>
-    <row r="125" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:11" ht="18" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>110</v>
       </c>
@@ -11997,7 +12145,7 @@
       <c r="D125" s="116"/>
       <c r="E125" s="12"/>
     </row>
-    <row r="126" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:11" ht="18" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>111</v>
       </c>
@@ -12005,12 +12153,12 @@
       <c r="D126" s="116"/>
       <c r="E126" s="12"/>
     </row>
-    <row r="127" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B127" s="3"/>
       <c r="D127" s="116"/>
       <c r="E127" s="12"/>
     </row>
-    <row r="128" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A128" s="121" t="s">
         <v>112</v>
       </c>
@@ -12020,7 +12168,7 @@
       <c r="E128" s="124"/>
       <c r="F128" s="125"/>
     </row>
-    <row r="129" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:6" ht="18" x14ac:dyDescent="0.3">
       <c r="A129" s="118" t="s">
         <v>113</v>
       </c>
@@ -12030,7 +12178,7 @@
       <c r="E129" s="120"/>
       <c r="F129" s="120"/>
     </row>
-    <row r="130" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:6" ht="18" x14ac:dyDescent="0.3">
       <c r="A130" s="118" t="s">
         <v>114</v>
       </c>
@@ -12040,7 +12188,7 @@
       <c r="E130" s="120"/>
       <c r="F130" s="120"/>
     </row>
-    <row r="131" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:6" ht="18" x14ac:dyDescent="0.3">
       <c r="A131" s="118" t="s">
         <v>115</v>
       </c>
@@ -12050,7 +12198,7 @@
       <c r="E131" s="120"/>
       <c r="F131" s="120"/>
     </row>
-    <row r="132" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:6" ht="18" x14ac:dyDescent="0.3">
       <c r="A132" s="118" t="s">
         <v>116</v>
       </c>
@@ -12060,7 +12208,7 @@
       <c r="E132" s="120"/>
       <c r="F132" s="120"/>
     </row>
-    <row r="133" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:6" ht="18" x14ac:dyDescent="0.3">
       <c r="A133" s="118" t="s">
         <v>117</v>
       </c>
@@ -12070,7 +12218,7 @@
       <c r="E133" s="120"/>
       <c r="F133" s="120"/>
     </row>
-    <row r="134" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:6" ht="18" x14ac:dyDescent="0.3">
       <c r="A134" s="118" t="s">
         <v>118</v>
       </c>
@@ -12080,7 +12228,7 @@
       <c r="E134" s="120"/>
       <c r="F134" s="120"/>
     </row>
-    <row r="135" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:6" ht="18" x14ac:dyDescent="0.3">
       <c r="A135" s="118" t="s">
         <v>119</v>
       </c>
@@ -12090,7 +12238,7 @@
       <c r="E135" s="120"/>
       <c r="F135" s="120"/>
     </row>
-    <row r="136" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:6" ht="18" x14ac:dyDescent="0.3">
       <c r="A136" s="118" t="s">
         <v>120</v>
       </c>
@@ -12100,7 +12248,7 @@
       <c r="E136" s="120"/>
       <c r="F136" s="120"/>
     </row>
-    <row r="137" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:6" ht="18" x14ac:dyDescent="0.3">
       <c r="A137" s="118" t="s">
         <v>254</v>
       </c>
@@ -12110,7 +12258,7 @@
       <c r="E137" s="120"/>
       <c r="F137" s="120"/>
     </row>
-    <row r="138" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:6" ht="18" x14ac:dyDescent="0.3">
       <c r="A138" s="118" t="s">
         <v>121</v>
       </c>
@@ -12120,7 +12268,7 @@
       <c r="E138" s="120"/>
       <c r="F138" s="120"/>
     </row>
-    <row r="139" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:6" ht="18" x14ac:dyDescent="0.3">
       <c r="A139" s="118" t="s">
         <v>122</v>
       </c>
@@ -12130,7 +12278,7 @@
       <c r="E139" s="120"/>
       <c r="F139" s="120"/>
     </row>
-    <row r="140" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:6" ht="18" x14ac:dyDescent="0.3">
       <c r="A140" s="118" t="s">
         <v>123</v>
       </c>
@@ -12140,7 +12288,7 @@
       <c r="E140" s="120"/>
       <c r="F140" s="120"/>
     </row>
-    <row r="141" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:6" ht="18" x14ac:dyDescent="0.3">
       <c r="A141" s="118"/>
       <c r="B141" s="118"/>
       <c r="C141" s="118"/>
@@ -12148,63 +12296,63 @@
       <c r="E141" s="120"/>
       <c r="F141" s="120"/>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>45</v>
       </c>
       <c r="B142" s="3"/>
       <c r="F142"/>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>30</v>
       </c>
       <c r="B143" s="3"/>
       <c r="F143"/>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>31</v>
       </c>
       <c r="B144" s="3"/>
       <c r="F144"/>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>32</v>
       </c>
       <c r="B145" s="3"/>
       <c r="F145"/>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>33</v>
       </c>
       <c r="B146" s="3"/>
       <c r="F146"/>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>34</v>
       </c>
       <c r="B147" s="3"/>
       <c r="F147"/>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>35</v>
       </c>
       <c r="B148" s="3"/>
       <c r="F148"/>
     </row>
-    <row r="149" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>36</v>
       </c>
       <c r="B149" s="3"/>
       <c r="F149"/>
     </row>
-    <row r="150" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A150" s="59" t="s">
         <v>47</v>
       </c>
@@ -12214,7 +12362,7 @@
       <c r="E150" s="90"/>
       <c r="F150" s="91"/>
     </row>
-    <row r="151" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A151" s="59" t="s">
         <v>48</v>
       </c>
@@ -12224,11 +12372,11 @@
       <c r="E151" s="90"/>
       <c r="F151" s="91"/>
     </row>
-    <row r="152" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B152"/>
       <c r="F152"/>
     </row>
-    <row r="153" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A153" s="136" t="s">
         <v>278</v>
       </c>
@@ -12238,7 +12386,7 @@
       <c r="E153" s="137"/>
       <c r="F153" s="138"/>
     </row>
-    <row r="154" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A154" s="136" t="s">
         <v>276</v>
       </c>
@@ -12248,7 +12396,7 @@
       <c r="E154" s="137"/>
       <c r="F154" s="138"/>
     </row>
-    <row r="155" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A155" s="139" t="s">
         <v>277</v>
       </c>
@@ -12258,126 +12406,126 @@
       <c r="E155" s="9"/>
       <c r="F155" s="9"/>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B156"/>
       <c r="F156"/>
     </row>
-    <row r="157" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B157"/>
       <c r="F157"/>
     </row>
-    <row r="158" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B158"/>
       <c r="D158" s="142" t="s">
         <v>279</v>
       </c>
       <c r="F158"/>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B159"/>
       <c r="F159"/>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B160"/>
       <c r="F160"/>
     </row>
-    <row r="161" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="161" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B161"/>
       <c r="F161"/>
     </row>
-    <row r="162" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="162" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B162"/>
       <c r="F162"/>
     </row>
-    <row r="163" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="163" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B163"/>
       <c r="F163"/>
     </row>
-    <row r="164" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="164" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B164"/>
       <c r="F164"/>
     </row>
-    <row r="165" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="165" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B165"/>
       <c r="F165"/>
     </row>
-    <row r="166" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="166" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B166"/>
       <c r="F166"/>
     </row>
-    <row r="167" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="167" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B167"/>
       <c r="F167"/>
     </row>
-    <row r="168" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="168" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B168"/>
       <c r="F168"/>
     </row>
-    <row r="169" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="169" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B169"/>
       <c r="F169"/>
     </row>
-    <row r="170" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="170" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B170"/>
       <c r="F170"/>
     </row>
-    <row r="171" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="171" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B171"/>
       <c r="F171"/>
     </row>
-    <row r="172" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="172" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B172"/>
       <c r="F172"/>
     </row>
-    <row r="180" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="180" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E180" s="93"/>
     </row>
-    <row r="181" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="181" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E181" s="93"/>
     </row>
-    <row r="182" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="182" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E182" s="93"/>
     </row>
-    <row r="183" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="183" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E183" s="93"/>
     </row>
-    <row r="184" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="184" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E184" s="93"/>
     </row>
-    <row r="185" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="185" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E185" s="93"/>
     </row>
-    <row r="186" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="186" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E186" s="93"/>
     </row>
-    <row r="187" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="187" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E187" s="93"/>
     </row>
-    <row r="188" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="188" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E188" s="93"/>
     </row>
-    <row r="189" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="189" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E189" s="93"/>
     </row>
-    <row r="190" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="190" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E190" s="93"/>
     </row>
-    <row r="191" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="191" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E191" s="93"/>
     </row>
-    <row r="192" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="192" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E192" s="93"/>
     </row>
-    <row r="193" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="193" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E193" s="93"/>
     </row>
-    <row r="194" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="194" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E194" s="93"/>
     </row>
-    <row r="195" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="195" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E195" s="93"/>
     </row>
-    <row r="198" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="198" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E198" s="93"/>
     </row>
   </sheetData>
@@ -12396,46 +12544,46 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q121"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.85546875" customWidth="1"/>
-    <col min="2" max="2" width="34.140625" customWidth="1"/>
-    <col min="3" max="3" width="5.7109375" customWidth="1"/>
+    <col min="1" max="1" width="5.88671875" customWidth="1"/>
+    <col min="2" max="2" width="34.109375" customWidth="1"/>
+    <col min="3" max="3" width="5.6640625" customWidth="1"/>
     <col min="4" max="4" width="9" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="5.7109375" customWidth="1"/>
-    <col min="6" max="6" width="12.7109375" customWidth="1"/>
+    <col min="5" max="5" width="5.6640625" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
-    <col min="8" max="8" width="12.5703125" customWidth="1"/>
-    <col min="9" max="9" width="13.140625" customWidth="1"/>
-    <col min="10" max="10" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.28515625" customWidth="1"/>
-    <col min="12" max="12" width="13.7109375" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.85546875" customWidth="1"/>
+    <col min="8" max="8" width="12.5546875" customWidth="1"/>
+    <col min="9" max="9" width="13.109375" customWidth="1"/>
+    <col min="10" max="10" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.33203125" customWidth="1"/>
+    <col min="12" max="12" width="13.6640625" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="373" t="s">
+    <row r="1" spans="1:17" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B1" s="388" t="s">
         <v>124</v>
       </c>
-      <c r="C1" s="374"/>
-      <c r="D1" s="374"/>
-      <c r="E1" s="374"/>
-      <c r="F1" s="374"/>
-      <c r="G1" s="374"/>
-      <c r="H1" s="374"/>
-      <c r="I1" s="374"/>
-      <c r="J1" s="374"/>
-      <c r="K1" s="374"/>
-      <c r="L1" s="374"/>
-      <c r="M1" s="374"/>
-      <c r="N1" s="374"/>
-      <c r="O1" s="375"/>
+      <c r="C1" s="389"/>
+      <c r="D1" s="389"/>
+      <c r="E1" s="389"/>
+      <c r="F1" s="389"/>
+      <c r="G1" s="389"/>
+      <c r="H1" s="389"/>
+      <c r="I1" s="389"/>
+      <c r="J1" s="389"/>
+      <c r="K1" s="389"/>
+      <c r="L1" s="389"/>
+      <c r="M1" s="389"/>
+      <c r="N1" s="389"/>
+      <c r="O1" s="390"/>
       <c r="P1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="I2" t="s">
         <v>18</v>
       </c>
@@ -12446,16 +12594,16 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="376" t="s">
+    <row r="3" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="391" t="s">
         <v>273</v>
       </c>
-      <c r="C3" s="377"/>
-      <c r="D3" s="377"/>
-      <c r="E3" s="377"/>
-      <c r="F3" s="377"/>
-      <c r="G3" s="377"/>
-      <c r="H3" s="377"/>
+      <c r="C3" s="392"/>
+      <c r="D3" s="392"/>
+      <c r="E3" s="392"/>
+      <c r="F3" s="392"/>
+      <c r="G3" s="392"/>
+      <c r="H3" s="392"/>
       <c r="I3" s="31">
         <v>6905337</v>
       </c>
@@ -12469,8 +12617,8 @@
         <v>4000000</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="5" spans="1:17" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="5" spans="1:17" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="19" t="s">
         <v>10</v>
       </c>
@@ -12517,7 +12665,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="7"/>
       <c r="B6" s="46"/>
       <c r="C6" s="46"/>
@@ -12534,7 +12682,7 @@
       <c r="N6" s="46"/>
       <c r="O6" s="47"/>
     </row>
-    <row r="7" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="48">
         <v>1</v>
       </c>
@@ -12589,7 +12737,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="20">
         <v>2</v>
       </c>
@@ -12638,7 +12786,7 @@
       </c>
       <c r="P8" s="65"/>
     </row>
-    <row r="9" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="20">
         <v>3</v>
       </c>
@@ -12690,7 +12838,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="20">
         <v>4</v>
       </c>
@@ -12742,7 +12890,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="20">
         <v>5</v>
       </c>
@@ -12794,7 +12942,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="20">
         <v>6</v>
       </c>
@@ -12849,7 +12997,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="20">
         <v>7</v>
       </c>
@@ -12904,7 +13052,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="20">
         <v>8</v>
       </c>
@@ -12959,7 +13107,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="20">
         <v>9</v>
       </c>
@@ -13011,7 +13159,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="20">
         <v>10</v>
       </c>
@@ -13063,7 +13211,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="20">
         <v>11</v>
       </c>
@@ -13115,7 +13263,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="20">
         <v>12</v>
       </c>
@@ -13166,7 +13314,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="20">
         <v>13</v>
       </c>
@@ -13218,7 +13366,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="20">
         <v>14</v>
       </c>
@@ -13270,7 +13418,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="20">
         <v>15</v>
       </c>
@@ -13322,7 +13470,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="20">
         <v>16</v>
       </c>
@@ -13373,7 +13521,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="20">
         <v>17</v>
       </c>
@@ -13425,7 +13573,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="20">
         <v>18</v>
       </c>
@@ -13477,7 +13625,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="20">
         <v>19</v>
       </c>
@@ -13528,7 +13676,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="20">
         <v>20</v>
       </c>
@@ -13582,7 +13730,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="20">
         <v>21</v>
       </c>
@@ -13634,7 +13782,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="20">
         <v>22</v>
       </c>
@@ -13686,7 +13834,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="20">
         <v>23</v>
       </c>
@@ -13738,7 +13886,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="20">
         <v>24</v>
       </c>
@@ -13792,7 +13940,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="20">
         <v>25</v>
       </c>
@@ -13844,7 +13992,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="20">
         <v>26</v>
       </c>
@@ -13895,7 +14043,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="20">
         <v>27</v>
       </c>
@@ -13947,7 +14095,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="20">
         <v>28</v>
       </c>
@@ -14001,7 +14149,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="66">
         <v>29</v>
       </c>
@@ -14052,7 +14200,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="71">
         <v>30</v>
       </c>
@@ -14102,7 +14250,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="37" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="71">
         <v>31</v>
       </c>
@@ -14152,7 +14300,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="71">
         <v>32</v>
       </c>
@@ -14202,7 +14350,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="71">
         <v>33</v>
       </c>
@@ -14252,7 +14400,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="71">
         <v>34</v>
       </c>
@@ -14302,7 +14450,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="71">
         <v>35</v>
       </c>
@@ -14355,7 +14503,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="42" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="71">
         <v>36</v>
       </c>
@@ -14404,7 +14552,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="43" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="71">
         <v>37</v>
       </c>
@@ -14454,7 +14602,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="71">
         <v>38</v>
       </c>
@@ -14504,7 +14652,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="71">
         <v>39</v>
       </c>
@@ -14554,7 +14702,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="46" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="71">
         <v>40</v>
       </c>
@@ -14604,7 +14752,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="47" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="71">
         <v>41</v>
       </c>
@@ -14654,7 +14802,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="71">
         <v>42</v>
       </c>
@@ -14706,7 +14854,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="71">
         <v>43</v>
       </c>
@@ -14755,7 +14903,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="71">
         <v>44</v>
       </c>
@@ -14804,7 +14952,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="71">
         <v>45</v>
       </c>
@@ -14854,7 +15002,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="52" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="71">
         <v>46</v>
       </c>
@@ -14904,7 +15052,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="53" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="71">
         <v>47</v>
       </c>
@@ -14953,7 +15101,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="54" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="71">
         <v>48</v>
       </c>
@@ -15003,7 +15151,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="55" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="71">
         <v>49</v>
       </c>
@@ -15053,7 +15201,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="71">
         <v>50</v>
       </c>
@@ -15103,7 +15251,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="57" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="71">
         <v>51</v>
       </c>
@@ -15153,7 +15301,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="71">
         <v>52</v>
       </c>
@@ -15203,7 +15351,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="71">
         <v>53</v>
       </c>
@@ -15256,7 +15404,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="71">
         <v>54</v>
       </c>
@@ -15306,7 +15454,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="71">
         <v>55</v>
       </c>
@@ -15356,7 +15504,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="71">
         <v>56</v>
       </c>
@@ -15406,7 +15554,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="71">
         <v>57</v>
       </c>
@@ -15459,7 +15607,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="71">
         <v>58</v>
       </c>
@@ -15509,7 +15657,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="65" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="71">
         <v>59</v>
       </c>
@@ -15562,7 +15710,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="71">
         <v>60</v>
       </c>
@@ -15615,7 +15763,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="67" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" s="71">
         <v>61</v>
       </c>
@@ -15665,7 +15813,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="68" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="71">
         <v>62</v>
       </c>
@@ -15715,7 +15863,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="69" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="71">
         <v>63</v>
       </c>
@@ -15765,7 +15913,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="70" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="126">
         <v>64</v>
       </c>
@@ -15815,7 +15963,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="71" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="71">
         <v>65</v>
       </c>
@@ -15863,7 +16011,7 @@
       </c>
       <c r="P71" s="65"/>
     </row>
-    <row r="72" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="71">
         <v>66</v>
       </c>
@@ -15913,7 +16061,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="73" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A73" s="71">
         <v>67</v>
       </c>
@@ -15963,7 +16111,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="71">
         <v>68</v>
       </c>
@@ -16010,7 +16158,7 @@
       </c>
       <c r="P74" s="65"/>
     </row>
-    <row r="75" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="71">
         <v>69</v>
       </c>
@@ -16060,7 +16208,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="71">
         <v>70</v>
       </c>
@@ -16107,7 +16255,7 @@
       </c>
       <c r="P76" s="65"/>
     </row>
-    <row r="77" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="71">
         <v>71</v>
       </c>
@@ -16157,7 +16305,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="71">
         <v>72</v>
       </c>
@@ -16206,7 +16354,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="71">
         <v>73</v>
       </c>
@@ -16256,7 +16404,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="71">
         <v>74</v>
       </c>
@@ -16303,7 +16451,7 @@
       </c>
       <c r="P80" s="65"/>
     </row>
-    <row r="81" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A81" s="71">
         <v>75</v>
       </c>
@@ -16353,7 +16501,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="82" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="71">
         <v>76</v>
       </c>
@@ -16403,7 +16551,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="83" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="71">
         <v>77</v>
       </c>
@@ -16453,7 +16601,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="84" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" s="71">
         <v>78</v>
       </c>
@@ -16501,7 +16649,7 @@
       </c>
       <c r="P84" s="65"/>
     </row>
-    <row r="85" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" s="71">
         <v>79</v>
       </c>
@@ -16551,7 +16699,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="86" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="71">
         <v>80</v>
       </c>
@@ -16601,7 +16749,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="87" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A87" s="71">
         <v>81</v>
       </c>
@@ -16651,7 +16799,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="88" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A88" s="71">
         <v>82</v>
       </c>
@@ -16701,7 +16849,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="89" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A89" s="71">
         <v>83</v>
       </c>
@@ -16751,7 +16899,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="90" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A90" s="71">
         <v>84</v>
       </c>
@@ -16801,7 +16949,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="91" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A91" s="71">
         <v>85</v>
       </c>
@@ -16851,7 +16999,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="92" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A92" s="71">
         <v>86</v>
       </c>
@@ -16901,7 +17049,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="93" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A93" s="71">
         <v>87</v>
       </c>
@@ -16951,7 +17099,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="94" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A94" s="71">
         <v>88</v>
       </c>
@@ -17001,7 +17149,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="95" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A95" s="71">
         <v>89</v>
       </c>
@@ -17051,7 +17199,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="96" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A96" s="71">
         <v>90</v>
       </c>
@@ -17102,7 +17250,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="97" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A97" s="71">
         <v>91</v>
       </c>
@@ -17154,7 +17302,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="98" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A98" s="71">
         <v>92</v>
       </c>
@@ -17206,7 +17354,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="99" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A99" s="71">
         <v>93</v>
       </c>
@@ -17258,7 +17406,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="100" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A100" s="71">
         <v>94</v>
       </c>
@@ -17310,7 +17458,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="101" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A101" s="71">
         <v>95</v>
       </c>
@@ -17362,7 +17510,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="102" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A102" s="71">
         <v>96</v>
       </c>
@@ -17414,7 +17562,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="103" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A103" s="71">
         <v>97</v>
       </c>
@@ -17466,7 +17614,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="104" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A104" s="71">
         <v>98</v>
       </c>
@@ -17518,7 +17666,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="105" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A105" s="71">
         <v>99</v>
       </c>
@@ -17570,7 +17718,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="106" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A106" s="71">
         <v>100</v>
       </c>
@@ -17619,7 +17767,7 @@
       </c>
       <c r="P106" s="65"/>
     </row>
-    <row r="107" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A107" s="71">
         <v>101</v>
       </c>
@@ -17671,7 +17819,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A108" s="71">
         <v>102</v>
       </c>
@@ -17723,7 +17871,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="109" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A109" s="71">
         <v>103</v>
       </c>
@@ -17775,7 +17923,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="110" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
         <v>20</v>
       </c>
@@ -17835,17 +17983,17 @@
         <v>20</v>
       </c>
     </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C111" s="378" t="s">
-        <v>20</v>
-      </c>
-      <c r="D111" s="378"/>
+    <row r="111" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C111" s="393" t="s">
+        <v>20</v>
+      </c>
+      <c r="D111" s="393"/>
       <c r="E111" s="99"/>
       <c r="G111" s="12" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="112" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:16" ht="18" x14ac:dyDescent="0.35">
       <c r="C112" s="3"/>
       <c r="D112" s="3"/>
       <c r="E112" s="3"/>
@@ -17855,7 +18003,7 @@
       <c r="K112" s="40"/>
       <c r="L112" s="40"/>
     </row>
-    <row r="113" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:16" ht="18" x14ac:dyDescent="0.35">
       <c r="A113" s="40" t="s">
         <v>22</v>
       </c>
@@ -17879,7 +18027,7 @@
       <c r="N113" s="40"/>
       <c r="O113" s="40"/>
     </row>
-    <row r="114" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:16" ht="18" x14ac:dyDescent="0.35">
       <c r="A114" s="78" t="s">
         <v>23</v>
       </c>
@@ -17910,7 +18058,7 @@
       </c>
       <c r="O114" s="9"/>
     </row>
-    <row r="115" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:16" ht="18" x14ac:dyDescent="0.35">
       <c r="A115" s="78" t="s">
         <v>24</v>
       </c>
@@ -17931,7 +18079,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="116" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:16" ht="18" x14ac:dyDescent="0.35">
       <c r="A116" s="78" t="s">
         <v>25</v>
       </c>
@@ -17953,7 +18101,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="117" spans="1:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:16" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A117" s="78" t="s">
         <v>46</v>
       </c>
@@ -17978,7 +18126,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="118" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D118" s="29"/>
       <c r="E118" s="29"/>
       <c r="J118" s="131">
@@ -17997,7 +18145,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:16" x14ac:dyDescent="0.3">
       <c r="J119" s="131">
         <v>45707</v>
       </c>
@@ -18008,7 +18156,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:16" x14ac:dyDescent="0.3">
       <c r="J120" s="131" t="s">
         <v>20</v>
       </c>
@@ -18019,7 +18167,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B121" s="3"/>
       <c r="C121" s="3"/>
       <c r="D121" s="3"/>

--- a/2026/ITALIA/ENERO/ENERO ITALIA.xlsx
+++ b/2026/ITALIA/ENERO/ENERO ITALIA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\ITALIA\ENERO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1BAA8A1-0C3E-4856-8A87-74B680801914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C94DB049-7C8B-4EA6-AD31-A7E118BF8363}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="4" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="856" uniqueCount="425">
   <si>
     <t xml:space="preserve">                                                            GRAL. PAZ 83/85 Pº 2 "B" - AVELLANEDA -CP 1870</t>
   </si>
@@ -1321,6 +1321,15 @@
   </si>
   <si>
     <t>Macarena Crespo nueva inquilina</t>
+  </si>
+  <si>
+    <t>4D Transfirio $125.000 el 16/02</t>
+  </si>
+  <si>
+    <t>Buenos días, si, el pago no registrado corresponde a las expensas del mes de octubre 2025 cuya liquidación se recibió por mail el 2/11/2025 y fue enviado por la administración anterior. El 4-11-2025 se realizó el pago por $119452.71 que es el comprobante que les envié. Como el pago no se imputó, desde diciembre estoy recibiendo las expensas con esa deuda que no existe. Por favor le pido realizar la corrección correspondiente. En otro mail les voy a reenviar el mail de la liquidación en cuestión que me envió la administración anterior para que puedan corroborar el monto y la fecha que menciono. 
+Aguardo sus comentarios, 
+Saludos, 
+Julieta Nani</t>
   </si>
 </sst>
 </file>
@@ -1597,7 +1606,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1685,6 +1694,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2243,7 +2258,7 @@
     </xf>
     <xf numFmtId="44" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="394">
+  <cellXfs count="398">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2867,6 +2882,11 @@
     <xf numFmtId="0" fontId="30" fillId="15" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="30" fillId="16" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="16" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2903,15 +2923,81 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="168" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="29" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2924,72 +3010,6 @@
     <xf numFmtId="0" fontId="27" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -3019,6 +3039,9 @@
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3402,12 +3425,12 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="143"/>
-      <c r="B1" s="347" t="s">
+      <c r="B1" s="350" t="s">
         <v>333</v>
       </c>
-      <c r="C1" s="347"/>
-      <c r="D1" s="347"/>
-      <c r="E1" s="348"/>
+      <c r="C1" s="350"/>
+      <c r="D1" s="350"/>
+      <c r="E1" s="351"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="144"/>
@@ -3420,12 +3443,12 @@
     </row>
     <row r="3" spans="1:5" ht="51.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="144"/>
-      <c r="B3" s="349" t="s">
+      <c r="B3" s="352" t="s">
         <v>334</v>
       </c>
-      <c r="C3" s="349"/>
-      <c r="D3" s="349"/>
-      <c r="E3" s="350"/>
+      <c r="C3" s="352"/>
+      <c r="D3" s="352"/>
+      <c r="E3" s="353"/>
     </row>
     <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="147" t="s">
@@ -3463,49 +3486,49 @@
       <c r="E6" s="150"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="351" t="s">
+      <c r="B8" s="354" t="s">
         <v>415</v>
       </c>
-      <c r="C8" s="351"/>
+      <c r="C8" s="354"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="351"/>
-      <c r="C9" s="351"/>
+      <c r="B9" s="354"/>
+      <c r="C9" s="354"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="351"/>
-      <c r="C10" s="351"/>
+      <c r="B10" s="354"/>
+      <c r="C10" s="354"/>
     </row>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="352" t="s">
+      <c r="A13" s="355" t="s">
         <v>286</v>
       </c>
-      <c r="B13" s="352"/>
-      <c r="C13" s="352"/>
-      <c r="D13" s="352"/>
-      <c r="E13" s="352"/>
+      <c r="B13" s="355"/>
+      <c r="C13" s="355"/>
+      <c r="D13" s="355"/>
+      <c r="E13" s="355"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="352"/>
-      <c r="B14" s="352"/>
-      <c r="C14" s="352"/>
-      <c r="D14" s="352"/>
-      <c r="E14" s="352"/>
+      <c r="A14" s="355"/>
+      <c r="B14" s="355"/>
+      <c r="C14" s="355"/>
+      <c r="D14" s="355"/>
+      <c r="E14" s="355"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="352"/>
-      <c r="B15" s="352"/>
-      <c r="C15" s="352"/>
-      <c r="D15" s="352"/>
-      <c r="E15" s="352"/>
+      <c r="A15" s="355"/>
+      <c r="B15" s="355"/>
+      <c r="C15" s="355"/>
+      <c r="D15" s="355"/>
+      <c r="E15" s="355"/>
     </row>
     <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="352"/>
-      <c r="B16" s="352"/>
-      <c r="C16" s="352"/>
-      <c r="D16" s="352"/>
-      <c r="E16" s="352"/>
+      <c r="A16" s="355"/>
+      <c r="B16" s="355"/>
+      <c r="C16" s="355"/>
+      <c r="D16" s="355"/>
+      <c r="E16" s="355"/>
     </row>
     <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="18" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -3531,10 +3554,10 @@
       <c r="E21" s="160"/>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="343" t="s">
+      <c r="A22" s="346" t="s">
         <v>357</v>
       </c>
-      <c r="B22" s="344"/>
+      <c r="B22" s="347"/>
       <c r="C22" s="163"/>
       <c r="D22" s="285">
         <v>2182238</v>
@@ -3543,10 +3566,10 @@
       <c r="H22" s="164"/>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="343" t="s">
+      <c r="A23" s="346" t="s">
         <v>358</v>
       </c>
-      <c r="B23" s="344"/>
+      <c r="B23" s="347"/>
       <c r="C23" s="163"/>
       <c r="D23" s="285">
         <v>-474636.76</v>
@@ -3555,10 +3578,10 @@
       <c r="H23" s="164"/>
     </row>
     <row r="24" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="343" t="s">
+      <c r="A24" s="346" t="s">
         <v>411</v>
       </c>
-      <c r="B24" s="344"/>
+      <c r="B24" s="347"/>
       <c r="C24" s="163"/>
       <c r="D24" s="286">
         <v>1381383</v>
@@ -3567,10 +3590,10 @@
       <c r="H24" s="164"/>
     </row>
     <row r="25" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="343" t="s">
+      <c r="A25" s="346" t="s">
         <v>54</v>
       </c>
-      <c r="B25" s="344"/>
+      <c r="B25" s="347"/>
       <c r="C25" s="163"/>
       <c r="D25" s="286">
         <v>0.76</v>
@@ -3730,10 +3753,10 @@
       <c r="E38" s="170"/>
     </row>
     <row r="39" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="345" t="s">
+      <c r="A39" s="348" t="s">
         <v>329</v>
       </c>
-      <c r="B39" s="346"/>
+      <c r="B39" s="349"/>
       <c r="C39" s="173"/>
       <c r="D39" s="320">
         <v>313739</v>
@@ -3743,10 +3766,10 @@
       </c>
     </row>
     <row r="40" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="345" t="s">
+      <c r="A40" s="348" t="s">
         <v>330</v>
       </c>
-      <c r="B40" s="346"/>
+      <c r="B40" s="349"/>
       <c r="C40" s="173"/>
       <c r="D40" s="321">
         <v>5204</v>
@@ -3851,10 +3874,10 @@
       <c r="E48" s="165"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="345" t="s">
+      <c r="A49" s="348" t="s">
         <v>294</v>
       </c>
-      <c r="B49" s="346"/>
+      <c r="B49" s="349"/>
       <c r="C49" s="178"/>
       <c r="D49" s="180">
         <v>3444706.16</v>
@@ -3892,10 +3915,10 @@
       <c r="E52" s="185"/>
     </row>
     <row r="53" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="343" t="s">
+      <c r="A53" s="346" t="s">
         <v>367</v>
       </c>
-      <c r="B53" s="344"/>
+      <c r="B53" s="347"/>
       <c r="C53" s="178"/>
       <c r="D53" s="180">
         <v>0</v>
@@ -3903,10 +3926,10 @@
       <c r="E53" s="186"/>
     </row>
     <row r="54" spans="1:6" ht="156.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="343" t="s">
+      <c r="A54" s="346" t="s">
         <v>408</v>
       </c>
-      <c r="B54" s="344"/>
+      <c r="B54" s="347"/>
       <c r="C54" s="178"/>
       <c r="D54" s="180">
         <v>570000</v>
@@ -3916,10 +3939,10 @@
       </c>
     </row>
     <row r="55" spans="1:6" ht="96.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="343" t="s">
+      <c r="A55" s="346" t="s">
         <v>407</v>
       </c>
-      <c r="B55" s="344"/>
+      <c r="B55" s="347"/>
       <c r="C55" s="178"/>
       <c r="D55" s="180">
         <v>950000</v>
@@ -3943,10 +3966,10 @@
       </c>
     </row>
     <row r="57" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="343" t="s">
+      <c r="A57" s="346" t="s">
         <v>410</v>
       </c>
-      <c r="B57" s="344"/>
+      <c r="B57" s="347"/>
       <c r="C57" s="178"/>
       <c r="D57" s="180">
         <v>85000</v>
@@ -3957,10 +3980,10 @@
       <c r="F57" s="205"/>
     </row>
     <row r="58" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="343" t="s">
+      <c r="A58" s="346" t="s">
         <v>375</v>
       </c>
-      <c r="B58" s="344"/>
+      <c r="B58" s="347"/>
       <c r="C58" s="178"/>
       <c r="D58" s="180">
         <v>85000</v>
@@ -3971,10 +3994,10 @@
       <c r="F58" s="205"/>
     </row>
     <row r="59" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="343" t="s">
+      <c r="A59" s="346" t="s">
         <v>377</v>
       </c>
-      <c r="B59" s="344"/>
+      <c r="B59" s="347"/>
       <c r="C59" s="178"/>
       <c r="D59" s="180">
         <v>150000</v>
@@ -3985,10 +4008,10 @@
       <c r="F59" s="205"/>
     </row>
     <row r="60" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="343" t="s">
+      <c r="A60" s="346" t="s">
         <v>379</v>
       </c>
-      <c r="B60" s="344"/>
+      <c r="B60" s="347"/>
       <c r="C60" s="178"/>
       <c r="D60" s="180">
         <v>250000</v>
@@ -4055,10 +4078,10 @@
       <c r="F64" s="205"/>
     </row>
     <row r="65" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="343" t="s">
+      <c r="A65" s="346" t="s">
         <v>374</v>
       </c>
-      <c r="B65" s="344"/>
+      <c r="B65" s="347"/>
       <c r="C65" s="178"/>
       <c r="D65" s="180">
         <v>303033.69</v>
@@ -4089,10 +4112,10 @@
       <c r="E67" s="160"/>
     </row>
     <row r="68" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="343" t="s">
+      <c r="A68" s="346" t="s">
         <v>385</v>
       </c>
-      <c r="B68" s="344"/>
+      <c r="B68" s="347"/>
       <c r="C68" s="163"/>
       <c r="D68" s="285">
         <v>650000</v>
@@ -4100,10 +4123,10 @@
       <c r="E68" s="189"/>
     </row>
     <row r="69" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="343" t="s">
+      <c r="A69" s="346" t="s">
         <v>386</v>
       </c>
-      <c r="B69" s="344"/>
+      <c r="B69" s="347"/>
       <c r="C69" s="163"/>
       <c r="D69" s="285">
         <v>650000</v>
@@ -4315,8 +4338,8 @@
       <c r="E89" s="215"/>
     </row>
     <row r="90" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="343"/>
-      <c r="B90" s="344"/>
+      <c r="A90" s="346"/>
+      <c r="B90" s="347"/>
       <c r="C90" s="178"/>
       <c r="D90" s="187"/>
       <c r="E90" s="215"/>
@@ -4406,14 +4429,14 @@
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" s="354" t="s">
+      <c r="A105" s="357" t="s">
         <v>389</v>
       </c>
-      <c r="B105" s="354"/>
+      <c r="B105" s="357"/>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" s="354"/>
-      <c r="B106" s="354"/>
+      <c r="A106" s="357"/>
+      <c r="B106" s="357"/>
     </row>
     <row r="107" spans="1:6" s="226" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A107"/>
@@ -4519,16 +4542,16 @@
     </row>
     <row r="118" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="119" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A119" s="353" t="s">
+      <c r="A119" s="356" t="s">
         <v>309</v>
       </c>
-      <c r="B119" s="353"/>
-      <c r="C119" s="353"/>
+      <c r="B119" s="356"/>
+      <c r="C119" s="356"/>
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A120" s="353"/>
-      <c r="B120" s="353"/>
-      <c r="C120" s="353"/>
+      <c r="A120" s="356"/>
+      <c r="B120" s="356"/>
+      <c r="C120" s="356"/>
     </row>
     <row r="121" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="234" t="s">
@@ -4622,14 +4645,14 @@
       <c r="A1" s="288"/>
       <c r="B1" s="289"/>
       <c r="C1" s="289"/>
-      <c r="D1" s="363"/>
-      <c r="E1" s="363"/>
-      <c r="F1" s="363"/>
-      <c r="G1" s="363"/>
-      <c r="H1" s="363"/>
-      <c r="I1" s="363"/>
-      <c r="J1" s="363"/>
-      <c r="K1" s="363"/>
+      <c r="D1" s="359"/>
+      <c r="E1" s="359"/>
+      <c r="F1" s="359"/>
+      <c r="G1" s="359"/>
+      <c r="H1" s="359"/>
+      <c r="I1" s="359"/>
+      <c r="J1" s="359"/>
+      <c r="K1" s="359"/>
       <c r="L1" s="290"/>
     </row>
     <row r="2" spans="1:14" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -4639,10 +4662,10 @@
       <c r="D2" s="293" t="s">
         <v>310</v>
       </c>
-      <c r="E2" s="355">
+      <c r="E2" s="382">
         <v>3000000</v>
       </c>
-      <c r="F2" s="355"/>
+      <c r="F2" s="382"/>
       <c r="G2" s="293"/>
       <c r="H2" s="293"/>
       <c r="I2" s="293" t="s">
@@ -4671,167 +4694,167 @@
       <c r="M3" s="240"/>
     </row>
     <row r="4" spans="1:14" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="364" t="s">
+      <c r="A4" s="360" t="s">
         <v>352</v>
       </c>
-      <c r="B4" s="365"/>
-      <c r="C4" s="365"/>
-      <c r="D4" s="365"/>
-      <c r="E4" s="365"/>
-      <c r="F4" s="365"/>
-      <c r="G4" s="365"/>
-      <c r="H4" s="365"/>
-      <c r="I4" s="365"/>
-      <c r="J4" s="365"/>
-      <c r="K4" s="365"/>
-      <c r="L4" s="366"/>
+      <c r="B4" s="361"/>
+      <c r="C4" s="361"/>
+      <c r="D4" s="361"/>
+      <c r="E4" s="361"/>
+      <c r="F4" s="361"/>
+      <c r="G4" s="361"/>
+      <c r="H4" s="361"/>
+      <c r="I4" s="361"/>
+      <c r="J4" s="361"/>
+      <c r="K4" s="361"/>
+      <c r="L4" s="362"/>
       <c r="M4" s="240"/>
     </row>
     <row r="5" spans="1:14" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="367"/>
-      <c r="B5" s="368"/>
-      <c r="C5" s="368"/>
-      <c r="D5" s="368"/>
-      <c r="E5" s="368"/>
-      <c r="F5" s="368"/>
-      <c r="G5" s="368"/>
-      <c r="H5" s="368"/>
-      <c r="I5" s="368"/>
-      <c r="J5" s="368"/>
-      <c r="K5" s="368"/>
-      <c r="L5" s="369"/>
+      <c r="A5" s="363"/>
+      <c r="B5" s="364"/>
+      <c r="C5" s="364"/>
+      <c r="D5" s="364"/>
+      <c r="E5" s="364"/>
+      <c r="F5" s="364"/>
+      <c r="G5" s="364"/>
+      <c r="H5" s="364"/>
+      <c r="I5" s="364"/>
+      <c r="J5" s="364"/>
+      <c r="K5" s="364"/>
+      <c r="L5" s="365"/>
       <c r="M5" s="240"/>
     </row>
     <row r="6" spans="1:14" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="367"/>
-      <c r="B6" s="368"/>
-      <c r="C6" s="368"/>
-      <c r="D6" s="368"/>
-      <c r="E6" s="368"/>
-      <c r="F6" s="368"/>
-      <c r="G6" s="368"/>
-      <c r="H6" s="368"/>
-      <c r="I6" s="368"/>
-      <c r="J6" s="368"/>
-      <c r="K6" s="368"/>
-      <c r="L6" s="369"/>
+      <c r="A6" s="363"/>
+      <c r="B6" s="364"/>
+      <c r="C6" s="364"/>
+      <c r="D6" s="364"/>
+      <c r="E6" s="364"/>
+      <c r="F6" s="364"/>
+      <c r="G6" s="364"/>
+      <c r="H6" s="364"/>
+      <c r="I6" s="364"/>
+      <c r="J6" s="364"/>
+      <c r="K6" s="364"/>
+      <c r="L6" s="365"/>
       <c r="M6" s="240"/>
     </row>
     <row r="7" spans="1:14" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="367"/>
-      <c r="B7" s="368"/>
-      <c r="C7" s="368"/>
-      <c r="D7" s="368"/>
-      <c r="E7" s="368"/>
-      <c r="F7" s="368"/>
-      <c r="G7" s="368"/>
-      <c r="H7" s="368"/>
-      <c r="I7" s="368"/>
-      <c r="J7" s="368"/>
-      <c r="K7" s="368"/>
-      <c r="L7" s="369"/>
+      <c r="A7" s="363"/>
+      <c r="B7" s="364"/>
+      <c r="C7" s="364"/>
+      <c r="D7" s="364"/>
+      <c r="E7" s="364"/>
+      <c r="F7" s="364"/>
+      <c r="G7" s="364"/>
+      <c r="H7" s="364"/>
+      <c r="I7" s="364"/>
+      <c r="J7" s="364"/>
+      <c r="K7" s="364"/>
+      <c r="L7" s="365"/>
       <c r="M7" s="240"/>
     </row>
     <row r="8" spans="1:14" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="370"/>
-      <c r="B8" s="371"/>
-      <c r="C8" s="371"/>
-      <c r="D8" s="371"/>
-      <c r="E8" s="371"/>
-      <c r="F8" s="371"/>
-      <c r="G8" s="371"/>
-      <c r="H8" s="371"/>
-      <c r="I8" s="371"/>
-      <c r="J8" s="371"/>
-      <c r="K8" s="371"/>
-      <c r="L8" s="372"/>
+      <c r="A8" s="366"/>
+      <c r="B8" s="367"/>
+      <c r="C8" s="367"/>
+      <c r="D8" s="367"/>
+      <c r="E8" s="367"/>
+      <c r="F8" s="367"/>
+      <c r="G8" s="367"/>
+      <c r="H8" s="367"/>
+      <c r="I8" s="367"/>
+      <c r="J8" s="367"/>
+      <c r="K8" s="367"/>
+      <c r="L8" s="368"/>
     </row>
     <row r="9" spans="1:14" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="378" t="s">
+      <c r="A9" s="376" t="s">
         <v>350</v>
       </c>
-      <c r="B9" s="379"/>
-      <c r="C9" s="379"/>
-      <c r="D9" s="379"/>
-      <c r="E9" s="379"/>
-      <c r="F9" s="379"/>
-      <c r="G9" s="379"/>
-      <c r="H9" s="379"/>
-      <c r="I9" s="379"/>
-      <c r="J9" s="379"/>
-      <c r="K9" s="379"/>
-      <c r="L9" s="380"/>
+      <c r="B9" s="377"/>
+      <c r="C9" s="377"/>
+      <c r="D9" s="377"/>
+      <c r="E9" s="377"/>
+      <c r="F9" s="377"/>
+      <c r="G9" s="377"/>
+      <c r="H9" s="377"/>
+      <c r="I9" s="377"/>
+      <c r="J9" s="377"/>
+      <c r="K9" s="377"/>
+      <c r="L9" s="378"/>
     </row>
     <row r="10" spans="1:14" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="381" t="s">
+      <c r="A10" s="379" t="s">
         <v>351</v>
       </c>
-      <c r="B10" s="382"/>
-      <c r="C10" s="382"/>
-      <c r="D10" s="382"/>
-      <c r="E10" s="382"/>
-      <c r="F10" s="382"/>
-      <c r="G10" s="382"/>
-      <c r="H10" s="382"/>
-      <c r="I10" s="382"/>
-      <c r="J10" s="382"/>
-      <c r="K10" s="382"/>
-      <c r="L10" s="383"/>
+      <c r="B10" s="380"/>
+      <c r="C10" s="380"/>
+      <c r="D10" s="380"/>
+      <c r="E10" s="380"/>
+      <c r="F10" s="380"/>
+      <c r="G10" s="380"/>
+      <c r="H10" s="380"/>
+      <c r="I10" s="380"/>
+      <c r="J10" s="380"/>
+      <c r="K10" s="380"/>
+      <c r="L10" s="381"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="373" t="s">
+      <c r="A11" s="369" t="s">
         <v>312</v>
       </c>
-      <c r="B11" s="373" t="s">
+      <c r="B11" s="369" t="s">
         <v>313</v>
       </c>
-      <c r="C11" s="373" t="s">
+      <c r="C11" s="369" t="s">
         <v>314</v>
       </c>
-      <c r="D11" s="373" t="s">
+      <c r="D11" s="369" t="s">
         <v>315</v>
       </c>
-      <c r="E11" s="356" t="s">
+      <c r="E11" s="372" t="s">
         <v>316</v>
       </c>
-      <c r="F11" s="373" t="s">
+      <c r="F11" s="369" t="s">
         <v>317</v>
       </c>
-      <c r="G11" s="376" t="s">
+      <c r="G11" s="374" t="s">
         <v>318</v>
       </c>
-      <c r="H11" s="356" t="s">
+      <c r="H11" s="372" t="s">
         <v>319</v>
       </c>
-      <c r="I11" s="356" t="s">
+      <c r="I11" s="372" t="s">
         <v>311</v>
       </c>
-      <c r="J11" s="358" t="s">
+      <c r="J11" s="383" t="s">
         <v>310</v>
       </c>
       <c r="K11" s="241" t="s">
         <v>320</v>
       </c>
-      <c r="L11" s="360" t="s">
+      <c r="L11" s="385" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="374"/>
-      <c r="B12" s="374"/>
-      <c r="C12" s="375"/>
-      <c r="D12" s="374"/>
-      <c r="E12" s="357"/>
-      <c r="F12" s="374"/>
-      <c r="G12" s="377"/>
-      <c r="H12" s="357"/>
-      <c r="I12" s="357"/>
-      <c r="J12" s="359"/>
+      <c r="A12" s="370"/>
+      <c r="B12" s="370"/>
+      <c r="C12" s="371"/>
+      <c r="D12" s="370"/>
+      <c r="E12" s="373"/>
+      <c r="F12" s="370"/>
+      <c r="G12" s="375"/>
+      <c r="H12" s="373"/>
+      <c r="I12" s="373"/>
+      <c r="J12" s="384"/>
       <c r="K12" s="242" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 18/02</v>
       </c>
-      <c r="L12" s="361"/>
+      <c r="L12" s="386"/>
     </row>
     <row r="13" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="243">
@@ -6198,11 +6221,11 @@
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="252">
+      <c r="A42" s="344">
         <f t="shared" si="9"/>
         <v>30</v>
       </c>
-      <c r="B42" s="254" t="s">
+      <c r="B42" s="345" t="s">
         <v>155</v>
       </c>
       <c r="C42" s="251"/>
@@ -9779,81 +9802,83 @@
     </row>
     <row r="119" spans="1:13" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="120" spans="1:13" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B120" s="362" t="s">
+      <c r="B120" s="358" t="s">
         <v>286</v>
       </c>
-      <c r="C120" s="362"/>
-      <c r="D120" s="362"/>
-      <c r="E120" s="362"/>
-      <c r="F120" s="362"/>
-      <c r="G120" s="362"/>
-      <c r="H120" s="362"/>
-      <c r="I120" s="362"/>
-      <c r="J120" s="362"/>
-      <c r="K120" s="362"/>
+      <c r="C120" s="358"/>
+      <c r="D120" s="358"/>
+      <c r="E120" s="358"/>
+      <c r="F120" s="358"/>
+      <c r="G120" s="358"/>
+      <c r="H120" s="358"/>
+      <c r="I120" s="358"/>
+      <c r="J120" s="358"/>
+      <c r="K120" s="358"/>
     </row>
     <row r="121" spans="1:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B121" s="362"/>
-      <c r="C121" s="362"/>
-      <c r="D121" s="362"/>
-      <c r="E121" s="362"/>
-      <c r="F121" s="362"/>
-      <c r="G121" s="362"/>
-      <c r="H121" s="362"/>
-      <c r="I121" s="362"/>
-      <c r="J121" s="362"/>
-      <c r="K121" s="362"/>
+      <c r="B121" s="358"/>
+      <c r="C121" s="358"/>
+      <c r="D121" s="358"/>
+      <c r="E121" s="358"/>
+      <c r="F121" s="358"/>
+      <c r="G121" s="358"/>
+      <c r="H121" s="358"/>
+      <c r="I121" s="358"/>
+      <c r="J121" s="358"/>
+      <c r="K121" s="358"/>
     </row>
     <row r="122" spans="1:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B122" s="362"/>
-      <c r="C122" s="362"/>
-      <c r="D122" s="362"/>
-      <c r="E122" s="362"/>
-      <c r="F122" s="362"/>
-      <c r="G122" s="362"/>
-      <c r="H122" s="362"/>
-      <c r="I122" s="362"/>
-      <c r="J122" s="362"/>
-      <c r="K122" s="362"/>
+      <c r="B122" s="358"/>
+      <c r="C122" s="358"/>
+      <c r="D122" s="358"/>
+      <c r="E122" s="358"/>
+      <c r="F122" s="358"/>
+      <c r="G122" s="358"/>
+      <c r="H122" s="358"/>
+      <c r="I122" s="358"/>
+      <c r="J122" s="358"/>
+      <c r="K122" s="358"/>
     </row>
     <row r="123" spans="1:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B123" s="362"/>
-      <c r="C123" s="362"/>
-      <c r="D123" s="362"/>
-      <c r="E123" s="362"/>
-      <c r="F123" s="362"/>
-      <c r="G123" s="362"/>
-      <c r="H123" s="362"/>
-      <c r="I123" s="362"/>
-      <c r="J123" s="362"/>
-      <c r="K123" s="362"/>
+      <c r="B123" s="358"/>
+      <c r="C123" s="358"/>
+      <c r="D123" s="358"/>
+      <c r="E123" s="358"/>
+      <c r="F123" s="358"/>
+      <c r="G123" s="358"/>
+      <c r="H123" s="358"/>
+      <c r="I123" s="358"/>
+      <c r="J123" s="358"/>
+      <c r="K123" s="358"/>
     </row>
     <row r="124" spans="1:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B124" s="362"/>
-      <c r="C124" s="362"/>
-      <c r="D124" s="362"/>
-      <c r="E124" s="362"/>
-      <c r="F124" s="362"/>
-      <c r="G124" s="362"/>
-      <c r="H124" s="362"/>
-      <c r="I124" s="362"/>
-      <c r="J124" s="362"/>
-      <c r="K124" s="362"/>
+      <c r="B124" s="358"/>
+      <c r="C124" s="358"/>
+      <c r="D124" s="358"/>
+      <c r="E124" s="358"/>
+      <c r="F124" s="358"/>
+      <c r="G124" s="358"/>
+      <c r="H124" s="358"/>
+      <c r="I124" s="358"/>
+      <c r="J124" s="358"/>
+      <c r="K124" s="358"/>
     </row>
     <row r="125" spans="1:13" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B125" s="362"/>
-      <c r="C125" s="362"/>
-      <c r="D125" s="362"/>
-      <c r="E125" s="362"/>
-      <c r="F125" s="362"/>
-      <c r="G125" s="362"/>
-      <c r="H125" s="362"/>
-      <c r="I125" s="362"/>
-      <c r="J125" s="362"/>
-      <c r="K125" s="362"/>
+      <c r="B125" s="358"/>
+      <c r="C125" s="358"/>
+      <c r="D125" s="358"/>
+      <c r="E125" s="358"/>
+      <c r="F125" s="358"/>
+      <c r="G125" s="358"/>
+      <c r="H125" s="358"/>
+      <c r="I125" s="358"/>
+      <c r="J125" s="358"/>
+      <c r="K125" s="358"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="B120:K125"/>
     <mergeCell ref="D1:K1"/>
     <mergeCell ref="A4:L8"/>
     <mergeCell ref="A11:A12"/>
@@ -9869,8 +9894,6 @@
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="I11:I12"/>
     <mergeCell ref="J11:J12"/>
-    <mergeCell ref="L11:L12"/>
-    <mergeCell ref="B120:K125"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="3" scale="85" orientation="portrait" r:id="rId1"/>
@@ -9879,7 +9902,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56D35F41-74CB-4294-A7A2-EC3C67574818}">
-  <dimension ref="B4:N20"/>
+  <dimension ref="B4:Q26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="12.77734375" bestFit="1" customWidth="1"/>
@@ -9891,17 +9914,17 @@
       </c>
     </row>
     <row r="6" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="384" t="s">
+      <c r="B6" s="387" t="s">
         <v>413</v>
       </c>
-      <c r="C6" s="384"/>
-      <c r="D6" s="384"/>
-      <c r="E6" s="384"/>
-      <c r="F6" s="384"/>
-      <c r="G6" s="384"/>
-      <c r="H6" s="384"/>
-      <c r="I6" s="384"/>
-      <c r="J6" s="384"/>
+      <c r="C6" s="387"/>
+      <c r="D6" s="387"/>
+      <c r="E6" s="387"/>
+      <c r="F6" s="387"/>
+      <c r="G6" s="387"/>
+      <c r="H6" s="387"/>
+      <c r="I6" s="387"/>
+      <c r="J6" s="387"/>
       <c r="L6" s="226" t="s">
         <v>414</v>
       </c>
@@ -9988,7 +10011,7 @@
       <c r="M16" s="338"/>
       <c r="N16" s="338"/>
     </row>
-    <row r="17" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B17" s="338"/>
       <c r="C17" s="338"/>
       <c r="D17" s="338"/>
@@ -10003,14 +10026,41 @@
       <c r="M17" s="338"/>
       <c r="N17" s="338"/>
     </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B20" s="340" t="s">
         <v>421</v>
       </c>
     </row>
+    <row r="23" spans="2:17" x14ac:dyDescent="0.3">
+      <c r="B23" s="343" t="s">
+        <v>423</v>
+      </c>
+      <c r="C23" s="343"/>
+    </row>
+    <row r="26" spans="2:17" ht="117" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="397" t="s">
+        <v>424</v>
+      </c>
+      <c r="C26" s="397"/>
+      <c r="D26" s="397"/>
+      <c r="E26" s="397"/>
+      <c r="F26" s="397"/>
+      <c r="G26" s="397"/>
+      <c r="H26" s="397"/>
+      <c r="I26" s="397"/>
+      <c r="J26" s="397"/>
+      <c r="K26" s="397"/>
+      <c r="L26" s="397"/>
+      <c r="M26" s="397"/>
+      <c r="N26" s="397"/>
+      <c r="O26" s="397"/>
+      <c r="P26" s="397"/>
+      <c r="Q26" s="397"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="B6:J6"/>
+    <mergeCell ref="B26:Q26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10035,11 +10085,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="385" t="s">
+      <c r="A1" s="388" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="385"/>
-      <c r="C1" s="385"/>
+      <c r="B1" s="388"/>
+      <c r="C1" s="388"/>
       <c r="I1" s="40"/>
       <c r="J1" s="40" t="s">
         <v>20</v>
@@ -10054,9 +10104,9 @@
       <c r="R1" s="40"/>
     </row>
     <row r="2" spans="1:18" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="385"/>
-      <c r="B2" s="385"/>
-      <c r="C2" s="385"/>
+      <c r="A2" s="388"/>
+      <c r="B2" s="388"/>
+      <c r="C2" s="388"/>
       <c r="J2" t="s">
         <v>20</v>
       </c>
@@ -10068,10 +10118,10 @@
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
       <c r="D3" s="1"/>
-      <c r="E3" s="386" t="s">
+      <c r="E3" s="389" t="s">
         <v>49</v>
       </c>
-      <c r="F3" s="387"/>
+      <c r="F3" s="390"/>
       <c r="G3" s="1"/>
       <c r="J3" t="s">
         <v>20</v>
@@ -12563,22 +12613,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="388" t="s">
+      <c r="B1" s="391" t="s">
         <v>124</v>
       </c>
-      <c r="C1" s="389"/>
-      <c r="D1" s="389"/>
-      <c r="E1" s="389"/>
-      <c r="F1" s="389"/>
-      <c r="G1" s="389"/>
-      <c r="H1" s="389"/>
-      <c r="I1" s="389"/>
-      <c r="J1" s="389"/>
-      <c r="K1" s="389"/>
-      <c r="L1" s="389"/>
-      <c r="M1" s="389"/>
-      <c r="N1" s="389"/>
-      <c r="O1" s="390"/>
+      <c r="C1" s="392"/>
+      <c r="D1" s="392"/>
+      <c r="E1" s="392"/>
+      <c r="F1" s="392"/>
+      <c r="G1" s="392"/>
+      <c r="H1" s="392"/>
+      <c r="I1" s="392"/>
+      <c r="J1" s="392"/>
+      <c r="K1" s="392"/>
+      <c r="L1" s="392"/>
+      <c r="M1" s="392"/>
+      <c r="N1" s="392"/>
+      <c r="O1" s="393"/>
       <c r="P1" t="s">
         <v>20</v>
       </c>
@@ -12595,15 +12645,15 @@
       </c>
     </row>
     <row r="3" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="391" t="s">
+      <c r="B3" s="394" t="s">
         <v>273</v>
       </c>
-      <c r="C3" s="392"/>
-      <c r="D3" s="392"/>
-      <c r="E3" s="392"/>
-      <c r="F3" s="392"/>
-      <c r="G3" s="392"/>
-      <c r="H3" s="392"/>
+      <c r="C3" s="395"/>
+      <c r="D3" s="395"/>
+      <c r="E3" s="395"/>
+      <c r="F3" s="395"/>
+      <c r="G3" s="395"/>
+      <c r="H3" s="395"/>
       <c r="I3" s="31">
         <v>6905337</v>
       </c>
@@ -17984,10 +18034,10 @@
       </c>
     </row>
     <row r="111" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C111" s="393" t="s">
-        <v>20</v>
-      </c>
-      <c r="D111" s="393"/>
+      <c r="C111" s="396" t="s">
+        <v>20</v>
+      </c>
+      <c r="D111" s="396"/>
       <c r="E111" s="99"/>
       <c r="G111" s="12" t="s">
         <v>20</v>

--- a/2026/ITALIA/ENERO/ENERO ITALIA.xlsx
+++ b/2026/ITALIA/ENERO/ENERO ITALIA.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\ITALIA\ENERO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\2026\ITALIA\ENERO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C94DB049-7C8B-4EA6-AD31-A7E118BF8363}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F89375DB-AD4E-4B4E-A7EB-B3F1087EC256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="4" r:id="rId1"/>
@@ -2887,18 +2887,24 @@
     <xf numFmtId="0" fontId="30" fillId="16" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -2917,11 +2923,11 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3004,15 +3010,12 @@
     <xf numFmtId="0" fontId="29" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="distributed"/>
     </xf>
@@ -3039,9 +3042,6 @@
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3408,31 +3408,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E413A25D-5161-4141-BE0B-6E37A2A76CA5}">
   <dimension ref="A1:M124"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="16.6640625" customWidth="1"/>
-    <col min="6" max="6" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.6640625" customWidth="1"/>
+    <col min="10" max="10" width="22.7109375" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" customWidth="1"/>
+    <col min="12" max="12" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="143"/>
-      <c r="B1" s="350" t="s">
+      <c r="B1" s="352" t="s">
         <v>333</v>
       </c>
-      <c r="C1" s="350"/>
-      <c r="D1" s="350"/>
-      <c r="E1" s="351"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C1" s="352"/>
+      <c r="D1" s="352"/>
+      <c r="E1" s="353"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="144"/>
       <c r="B2" s="151" t="s">
         <v>336</v>
@@ -3441,16 +3441,16 @@
       <c r="D2" s="145"/>
       <c r="E2" s="146"/>
     </row>
-    <row r="3" spans="1:5" ht="51.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="51.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="144"/>
-      <c r="B3" s="352" t="s">
+      <c r="B3" s="354" t="s">
         <v>334</v>
       </c>
-      <c r="C3" s="352"/>
-      <c r="D3" s="352"/>
-      <c r="E3" s="353"/>
-    </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C3" s="354"/>
+      <c r="D3" s="354"/>
+      <c r="E3" s="355"/>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="147" t="s">
         <v>282</v>
       </c>
@@ -3461,7 +3461,7 @@
       <c r="D4" s="149"/>
       <c r="E4" s="150"/>
     </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="144" t="s">
         <v>335</v>
       </c>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="E5" s="152"/>
     </row>
-    <row r="6" spans="1:5" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="265" t="s">
         <v>322</v>
       </c>
@@ -3485,57 +3485,57 @@
       </c>
       <c r="E6" s="150"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="354" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B8" s="356" t="s">
         <v>415</v>
       </c>
-      <c r="C8" s="354"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="354"/>
-      <c r="C9" s="354"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="354"/>
-      <c r="C10" s="354"/>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="355" t="s">
+      <c r="C8" s="356"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="356"/>
+      <c r="C9" s="356"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B10" s="356"/>
+      <c r="C10" s="356"/>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="357" t="s">
         <v>286</v>
       </c>
-      <c r="B13" s="355"/>
-      <c r="C13" s="355"/>
-      <c r="D13" s="355"/>
-      <c r="E13" s="355"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="355"/>
-      <c r="B14" s="355"/>
-      <c r="C14" s="355"/>
-      <c r="D14" s="355"/>
-      <c r="E14" s="355"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="355"/>
-      <c r="B15" s="355"/>
-      <c r="C15" s="355"/>
-      <c r="D15" s="355"/>
-      <c r="E15" s="355"/>
-    </row>
-    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="355"/>
-      <c r="B16" s="355"/>
-      <c r="C16" s="355"/>
-      <c r="D16" s="355"/>
-      <c r="E16" s="355"/>
-    </row>
-    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="18" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="357"/>
+      <c r="C13" s="357"/>
+      <c r="D13" s="357"/>
+      <c r="E13" s="357"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="357"/>
+      <c r="B14" s="357"/>
+      <c r="C14" s="357"/>
+      <c r="D14" s="357"/>
+      <c r="E14" s="357"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="357"/>
+      <c r="B15" s="357"/>
+      <c r="C15" s="357"/>
+      <c r="D15" s="357"/>
+      <c r="E15" s="357"/>
+    </row>
+    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="357"/>
+      <c r="B16" s="357"/>
+      <c r="C16" s="357"/>
+      <c r="D16" s="357"/>
+      <c r="E16" s="357"/>
+    </row>
+    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="9"/>
     </row>
-    <row r="19" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="153" t="s">
         <v>287</v>
       </c>
@@ -3544,7 +3544,7 @@
       <c r="D20" s="156"/>
       <c r="E20" s="157"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="158" t="s">
         <v>323</v>
       </c>
@@ -3553,11 +3553,11 @@
       <c r="D21" s="159"/>
       <c r="E21" s="160"/>
     </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="346" t="s">
+    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="350" t="s">
         <v>357</v>
       </c>
-      <c r="B22" s="347"/>
+      <c r="B22" s="351"/>
       <c r="C22" s="163"/>
       <c r="D22" s="285">
         <v>2182238</v>
@@ -3565,11 +3565,11 @@
       <c r="E22" s="189"/>
       <c r="H22" s="164"/>
     </row>
-    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="346" t="s">
+    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="350" t="s">
         <v>358</v>
       </c>
-      <c r="B23" s="347"/>
+      <c r="B23" s="351"/>
       <c r="C23" s="163"/>
       <c r="D23" s="285">
         <v>-474636.76</v>
@@ -3577,11 +3577,11 @@
       <c r="E23" s="165"/>
       <c r="H23" s="164"/>
     </row>
-    <row r="24" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="346" t="s">
+    <row r="24" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="350" t="s">
         <v>411</v>
       </c>
-      <c r="B24" s="347"/>
+      <c r="B24" s="351"/>
       <c r="C24" s="163"/>
       <c r="D24" s="286">
         <v>1381383</v>
@@ -3589,11 +3589,11 @@
       <c r="E24" s="165"/>
       <c r="H24" s="164"/>
     </row>
-    <row r="25" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="346" t="s">
+    <row r="25" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="350" t="s">
         <v>54</v>
       </c>
-      <c r="B25" s="347"/>
+      <c r="B25" s="351"/>
       <c r="C25" s="163"/>
       <c r="D25" s="286">
         <v>0.76</v>
@@ -3601,7 +3601,7 @@
       <c r="E25" s="165"/>
       <c r="H25" s="164"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="166" t="s">
         <v>288</v>
       </c>
@@ -3613,7 +3613,7 @@
         <v>3088985</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="166" t="s">
         <v>382</v>
       </c>
@@ -3622,7 +3622,7 @@
       <c r="D27" s="167"/>
       <c r="E27" s="266"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="163" t="s">
         <v>383</v>
       </c>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="E28" s="268"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="166" t="s">
         <v>288</v>
       </c>
@@ -3646,7 +3646,7 @@
         <v>511000</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="158" t="s">
         <v>324</v>
       </c>
@@ -3655,7 +3655,7 @@
       <c r="D30" s="167"/>
       <c r="E30" s="266"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="163" t="s">
         <v>384</v>
       </c>
@@ -3668,7 +3668,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="163" t="s">
         <v>341</v>
       </c>
@@ -3681,7 +3681,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="163" t="s">
         <v>326</v>
       </c>
@@ -3694,7 +3694,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="163" t="s">
         <v>328</v>
       </c>
@@ -3708,7 +3708,7 @@
         <v>Debito 16/01 Cred.</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="163" t="s">
         <v>327</v>
       </c>
@@ -3722,7 +3722,7 @@
         <v>Debito 16/01 Cred.</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="163" t="s">
         <v>342</v>
       </c>
@@ -3731,7 +3731,7 @@
       <c r="D36" s="187"/>
       <c r="E36" s="278"/>
     </row>
-    <row r="37" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="166" t="s">
         <v>325</v>
       </c>
@@ -3743,7 +3743,7 @@
         <v>1616063.91</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="158" t="s">
         <v>289</v>
       </c>
@@ -3752,11 +3752,11 @@
       <c r="D38" s="169"/>
       <c r="E38" s="170"/>
     </row>
-    <row r="39" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="348" t="s">
+    <row r="39" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="347" t="s">
         <v>329</v>
       </c>
-      <c r="B39" s="349"/>
+      <c r="B39" s="348"/>
       <c r="C39" s="173"/>
       <c r="D39" s="320">
         <v>313739</v>
@@ -3765,11 +3765,11 @@
         <v>392</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="348" t="s">
+    <row r="40" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="347" t="s">
         <v>330</v>
       </c>
-      <c r="B40" s="349"/>
+      <c r="B40" s="348"/>
       <c r="C40" s="173"/>
       <c r="D40" s="321">
         <v>5204</v>
@@ -3778,7 +3778,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="166" t="s">
         <v>290</v>
       </c>
@@ -3790,7 +3790,7 @@
         <v>318943</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="158" t="s">
         <v>291</v>
       </c>
@@ -3799,7 +3799,7 @@
       <c r="D42" s="176"/>
       <c r="E42" s="177"/>
     </row>
-    <row r="43" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="178" t="s">
         <v>292</v>
       </c>
@@ -3812,7 +3812,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="178" t="s">
         <v>292</v>
       </c>
@@ -3825,7 +3825,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="178" t="s">
         <v>292</v>
       </c>
@@ -3838,7 +3838,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="178" t="s">
         <v>292</v>
       </c>
@@ -3851,7 +3851,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="178" t="s">
         <v>293</v>
       </c>
@@ -3864,7 +3864,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="178" t="s">
         <v>293</v>
       </c>
@@ -3873,11 +3873,11 @@
       <c r="D48" s="180"/>
       <c r="E48" s="165"/>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="348" t="s">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="347" t="s">
         <v>294</v>
       </c>
-      <c r="B49" s="349"/>
+      <c r="B49" s="348"/>
       <c r="C49" s="178"/>
       <c r="D49" s="180">
         <v>3444706.16</v>
@@ -3886,7 +3886,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="182" t="s">
         <v>295</v>
       </c>
@@ -3895,7 +3895,7 @@
       <c r="D50" s="179"/>
       <c r="E50" s="165"/>
     </row>
-    <row r="51" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="166" t="s">
         <v>296</v>
       </c>
@@ -3907,29 +3907,29 @@
         <v>4391217.68</v>
       </c>
     </row>
-    <row r="52" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="158"/>
       <c r="B52" s="166"/>
       <c r="C52" s="166"/>
       <c r="D52" s="167"/>
       <c r="E52" s="185"/>
     </row>
-    <row r="53" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="346" t="s">
+    <row r="53" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="350" t="s">
         <v>367</v>
       </c>
-      <c r="B53" s="347"/>
+      <c r="B53" s="351"/>
       <c r="C53" s="178"/>
       <c r="D53" s="180">
         <v>0</v>
       </c>
       <c r="E53" s="186"/>
     </row>
-    <row r="54" spans="1:6" ht="156.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="346" t="s">
+    <row r="54" spans="1:6" ht="156.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="350" t="s">
         <v>408</v>
       </c>
-      <c r="B54" s="347"/>
+      <c r="B54" s="351"/>
       <c r="C54" s="178"/>
       <c r="D54" s="180">
         <v>570000</v>
@@ -3938,11 +3938,11 @@
         <v>409</v>
       </c>
     </row>
-    <row r="55" spans="1:6" ht="96.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="346" t="s">
+    <row r="55" spans="1:6" ht="96.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="350" t="s">
         <v>407</v>
       </c>
-      <c r="B55" s="347"/>
+      <c r="B55" s="351"/>
       <c r="C55" s="178"/>
       <c r="D55" s="180">
         <v>950000</v>
@@ -3951,7 +3951,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="287" t="s">
         <v>365</v>
       </c>
@@ -3965,11 +3965,11 @@
         <v>366</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="346" t="s">
+    <row r="57" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="350" t="s">
         <v>410</v>
       </c>
-      <c r="B57" s="347"/>
+      <c r="B57" s="351"/>
       <c r="C57" s="178"/>
       <c r="D57" s="180">
         <v>85000</v>
@@ -3979,11 +3979,11 @@
       </c>
       <c r="F57" s="205"/>
     </row>
-    <row r="58" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="346" t="s">
+    <row r="58" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="350" t="s">
         <v>375</v>
       </c>
-      <c r="B58" s="347"/>
+      <c r="B58" s="351"/>
       <c r="C58" s="178"/>
       <c r="D58" s="180">
         <v>85000</v>
@@ -3993,11 +3993,11 @@
       </c>
       <c r="F58" s="205"/>
     </row>
-    <row r="59" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="346" t="s">
+    <row r="59" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="350" t="s">
         <v>377</v>
       </c>
-      <c r="B59" s="347"/>
+      <c r="B59" s="351"/>
       <c r="C59" s="178"/>
       <c r="D59" s="180">
         <v>150000</v>
@@ -4007,11 +4007,11 @@
       </c>
       <c r="F59" s="205"/>
     </row>
-    <row r="60" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="346" t="s">
+    <row r="60" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="350" t="s">
         <v>379</v>
       </c>
-      <c r="B60" s="347"/>
+      <c r="B60" s="351"/>
       <c r="C60" s="178"/>
       <c r="D60" s="180">
         <v>250000</v>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="F60" s="205"/>
     </row>
-    <row r="61" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="287" t="s">
         <v>369</v>
       </c>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="F61" s="205"/>
     </row>
-    <row r="62" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="287" t="s">
         <v>370</v>
       </c>
@@ -4049,7 +4049,7 @@
       </c>
       <c r="F62" s="205"/>
     </row>
-    <row r="63" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="287" t="s">
         <v>387</v>
       </c>
@@ -4063,7 +4063,7 @@
       </c>
       <c r="F63" s="205"/>
     </row>
-    <row r="64" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="287" t="s">
         <v>376</v>
       </c>
@@ -4077,11 +4077,11 @@
       </c>
       <c r="F64" s="205"/>
     </row>
-    <row r="65" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="346" t="s">
+    <row r="65" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="350" t="s">
         <v>374</v>
       </c>
-      <c r="B65" s="347"/>
+      <c r="B65" s="351"/>
       <c r="C65" s="178"/>
       <c r="D65" s="180">
         <v>303033.69</v>
@@ -4090,7 +4090,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="166" t="s">
         <v>5</v>
       </c>
@@ -4102,7 +4102,7 @@
         <v>8559403.6899999995</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="158" t="s">
         <v>297</v>
       </c>
@@ -4111,29 +4111,29 @@
       <c r="D67" s="159"/>
       <c r="E67" s="160"/>
     </row>
-    <row r="68" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="346" t="s">
+    <row r="68" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="350" t="s">
         <v>385</v>
       </c>
-      <c r="B68" s="347"/>
+      <c r="B68" s="351"/>
       <c r="C68" s="163"/>
       <c r="D68" s="285">
         <v>650000</v>
       </c>
       <c r="E68" s="189"/>
     </row>
-    <row r="69" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="346" t="s">
+    <row r="69" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="350" t="s">
         <v>386</v>
       </c>
-      <c r="B69" s="347"/>
+      <c r="B69" s="351"/>
       <c r="C69" s="163"/>
       <c r="D69" s="285">
         <v>650000</v>
       </c>
       <c r="E69" s="189"/>
     </row>
-    <row r="70" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="161" t="s">
         <v>360</v>
       </c>
@@ -4146,7 +4146,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="161" t="s">
         <v>371</v>
       </c>
@@ -4159,7 +4159,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="161" t="s">
         <v>364</v>
       </c>
@@ -4172,7 +4172,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="161" t="s">
         <v>368</v>
       </c>
@@ -4185,7 +4185,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="287" t="s">
         <v>363</v>
       </c>
@@ -4198,7 +4198,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="166" t="s">
         <v>288</v>
       </c>
@@ -4210,7 +4210,7 @@
         <v>1667550</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="158" t="s">
         <v>298</v>
       </c>
@@ -4219,7 +4219,7 @@
       <c r="D76" s="191"/>
       <c r="E76" s="174"/>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="178" t="s">
         <v>337</v>
       </c>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="E77" s="192"/>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="178" t="s">
         <v>338</v>
       </c>
@@ -4241,7 +4241,7 @@
       </c>
       <c r="E78" s="193"/>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="178" t="s">
         <v>339</v>
       </c>
@@ -4252,7 +4252,7 @@
       </c>
       <c r="E79" s="193"/>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="178" t="s">
         <v>340</v>
       </c>
@@ -4264,7 +4264,7 @@
       </c>
       <c r="E80" s="193"/>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="194" t="s">
         <v>288</v>
       </c>
@@ -4276,14 +4276,14 @@
         <v>282278.22000000003</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="178"/>
       <c r="B82" s="178"/>
       <c r="C82" s="178"/>
       <c r="D82" s="197"/>
       <c r="E82" s="198"/>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="199" t="s">
         <v>299</v>
       </c>
@@ -4292,13 +4292,13 @@
       <c r="D83" s="200"/>
       <c r="E83" s="201"/>
     </row>
-    <row r="84" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="202"/>
       <c r="D84" s="203"/>
       <c r="E84" s="204"/>
       <c r="F84" s="205"/>
     </row>
-    <row r="85" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="206" t="s">
         <v>300</v>
       </c>
@@ -4312,16 +4312,16 @@
       <c r="F85" s="211"/>
       <c r="G85" s="205"/>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D86" s="203"/>
       <c r="E86" s="203"/>
     </row>
-    <row r="87" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D87" s="203"/>
       <c r="E87" s="203"/>
       <c r="H87" s="212"/>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="153" t="s">
         <v>301</v>
       </c>
@@ -4330,32 +4330,32 @@
       <c r="D88" s="213"/>
       <c r="E88" s="214"/>
     </row>
-    <row r="89" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="171"/>
       <c r="B89" s="172"/>
       <c r="C89" s="178"/>
       <c r="D89" s="187"/>
       <c r="E89" s="215"/>
     </row>
-    <row r="90" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="346"/>
-      <c r="B90" s="347"/>
+    <row r="90" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="350"/>
+      <c r="B90" s="351"/>
       <c r="C90" s="178"/>
       <c r="D90" s="187"/>
       <c r="E90" s="215"/>
     </row>
-    <row r="91" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D91" s="178"/>
       <c r="E91" s="178"/>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="171"/>
       <c r="B92" s="216"/>
       <c r="C92" s="178"/>
       <c r="D92" s="187"/>
       <c r="E92" s="215"/>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="217" t="s">
         <v>332</v>
       </c>
@@ -4367,9 +4367,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="95" spans="1:8" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" spans="1:8" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="199" t="s">
         <v>302</v>
       </c>
@@ -4378,8 +4378,8 @@
       <c r="D96" s="220"/>
       <c r="E96" s="279"/>
     </row>
-    <row r="97" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="98" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="98" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="206" t="s">
         <v>303</v>
       </c>
@@ -4391,8 +4391,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="100" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="100" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="222" t="s">
         <v>304</v>
       </c>
@@ -4401,7 +4401,7 @@
         <v>20435441.5</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" s="222" t="s">
         <v>305</v>
       </c>
@@ -4410,7 +4410,7 @@
         <v>20435441.5</v>
       </c>
     </row>
-    <row r="102" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="222" t="s">
         <v>306</v>
       </c>
@@ -4419,7 +4419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="222" t="s">
         <v>307</v>
       </c>
@@ -4428,22 +4428,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" s="357" t="s">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A105" s="349" t="s">
         <v>389</v>
       </c>
-      <c r="B105" s="357"/>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" s="357"/>
-      <c r="B106" s="357"/>
-    </row>
-    <row r="107" spans="1:6" s="226" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B105" s="349"/>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A106" s="349"/>
+      <c r="B106" s="349"/>
+    </row>
+    <row r="107" spans="1:6" s="226" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107"/>
       <c r="B107" s="224"/>
       <c r="C107" s="225"/>
     </row>
-    <row r="108" spans="1:6" s="226" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6" s="226" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="283" t="s">
         <v>354</v>
       </c>
@@ -4454,7 +4454,7 @@
       <c r="D108" s="228"/>
       <c r="E108" s="228"/>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="173" t="s">
         <v>331</v>
       </c>
@@ -4463,7 +4463,7 @@
         <v>-20435441.5</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="173" t="s">
         <v>308</v>
       </c>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="F110" s="224"/>
     </row>
-    <row r="111" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="173" t="s">
         <v>396</v>
       </c>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="F111" s="224"/>
     </row>
-    <row r="112" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="173" t="s">
         <v>397</v>
       </c>
@@ -4491,7 +4491,7 @@
       </c>
       <c r="F112" s="224"/>
     </row>
-    <row r="113" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="173" t="s">
         <v>402</v>
       </c>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="F113" s="224"/>
     </row>
-    <row r="114" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="173" t="s">
         <v>406</v>
       </c>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="F114" s="224"/>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A115" s="173" t="s">
         <v>86</v>
       </c>
@@ -4519,7 +4519,7 @@
       </c>
       <c r="F115" s="224"/>
     </row>
-    <row r="116" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A116" s="231" t="s">
         <v>362</v>
       </c>
@@ -4528,7 +4528,7 @@
       </c>
       <c r="F116" s="224"/>
     </row>
-    <row r="117" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A117" s="232" t="s">
         <v>355</v>
       </c>
@@ -4540,20 +4540,20 @@
       <c r="E117" s="205"/>
       <c r="F117" s="205"/>
     </row>
-    <row r="118" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A119" s="356" t="s">
+    <row r="118" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A119" s="346" t="s">
         <v>309</v>
       </c>
-      <c r="B119" s="356"/>
-      <c r="C119" s="356"/>
-    </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A120" s="356"/>
-      <c r="B120" s="356"/>
-      <c r="C120" s="356"/>
-    </row>
-    <row r="121" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B119" s="346"/>
+      <c r="C119" s="346"/>
+    </row>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A120" s="346"/>
+      <c r="B120" s="346"/>
+      <c r="C120" s="346"/>
+    </row>
+    <row r="121" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="234" t="s">
         <v>395</v>
       </c>
@@ -4563,7 +4563,7 @@
       <c r="C121" s="235"/>
       <c r="E121" s="211"/>
     </row>
-    <row r="122" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="234" t="s">
         <v>398</v>
       </c>
@@ -4573,7 +4573,7 @@
       <c r="C122" s="235"/>
       <c r="D122" s="211"/>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A123" s="236" t="s">
         <v>5</v>
       </c>
@@ -4583,11 +4583,21 @@
       </c>
       <c r="C123" s="238"/>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
       <c r="M124" s="239"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B8:C10"/>
+    <mergeCell ref="A13:E16"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A119:C120"/>
     <mergeCell ref="A40:B40"/>
     <mergeCell ref="A105:B106"/>
@@ -4602,16 +4612,6 @@
     <mergeCell ref="A54:B54"/>
     <mergeCell ref="A69:B69"/>
     <mergeCell ref="A55:B55"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A68:B68"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B8:C10"/>
-    <mergeCell ref="A13:E16"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A23:B23"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" scale="90" orientation="portrait" r:id="rId1"/>
@@ -4622,50 +4622,50 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{533DB7A7-09F4-49CF-B824-70F15C1FF525}">
   <dimension ref="A1:N125"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.33203125" customWidth="1"/>
-    <col min="2" max="2" width="25.5546875" customWidth="1"/>
-    <col min="3" max="3" width="0.109375" customWidth="1"/>
-    <col min="4" max="4" width="8.44140625" customWidth="1"/>
-    <col min="5" max="5" width="14.109375" customWidth="1"/>
-    <col min="6" max="6" width="12.33203125" customWidth="1"/>
-    <col min="7" max="7" width="10.5546875" customWidth="1"/>
-    <col min="8" max="8" width="9.5546875" customWidth="1"/>
-    <col min="9" max="9" width="12.44140625" customWidth="1"/>
-    <col min="10" max="10" width="14.44140625" customWidth="1"/>
-    <col min="11" max="11" width="14.6640625" customWidth="1"/>
-    <col min="12" max="12" width="14.33203125" customWidth="1"/>
-    <col min="13" max="13" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.28515625" customWidth="1"/>
+    <col min="2" max="2" width="25.5703125" customWidth="1"/>
+    <col min="3" max="3" width="0.140625" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" customWidth="1"/>
+    <col min="6" max="6" width="12.28515625" customWidth="1"/>
+    <col min="7" max="7" width="10.5703125" customWidth="1"/>
+    <col min="8" max="8" width="9.5703125" customWidth="1"/>
+    <col min="9" max="9" width="12.42578125" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" customWidth="1"/>
+    <col min="13" max="13" width="7.28515625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="288"/>
       <c r="B1" s="289"/>
       <c r="C1" s="289"/>
-      <c r="D1" s="359"/>
-      <c r="E1" s="359"/>
-      <c r="F1" s="359"/>
-      <c r="G1" s="359"/>
-      <c r="H1" s="359"/>
-      <c r="I1" s="359"/>
-      <c r="J1" s="359"/>
-      <c r="K1" s="359"/>
+      <c r="D1" s="361"/>
+      <c r="E1" s="361"/>
+      <c r="F1" s="361"/>
+      <c r="G1" s="361"/>
+      <c r="H1" s="361"/>
+      <c r="I1" s="361"/>
+      <c r="J1" s="361"/>
+      <c r="K1" s="361"/>
       <c r="L1" s="290"/>
     </row>
-    <row r="2" spans="1:14" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="291"/>
       <c r="B2" s="292"/>
       <c r="C2" s="293"/>
       <c r="D2" s="293" t="s">
         <v>310</v>
       </c>
-      <c r="E2" s="382">
+      <c r="E2" s="384">
         <v>3000000</v>
       </c>
-      <c r="F2" s="382"/>
+      <c r="F2" s="384"/>
       <c r="G2" s="293"/>
       <c r="H2" s="293"/>
       <c r="I2" s="293" t="s">
@@ -4678,7 +4678,7 @@
       <c r="L2" s="296"/>
       <c r="M2" s="240"/>
     </row>
-    <row r="3" spans="1:14" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="297"/>
       <c r="B3" s="298"/>
       <c r="C3" s="298"/>
@@ -4693,170 +4693,170 @@
       <c r="L3" s="301"/>
       <c r="M3" s="240"/>
     </row>
-    <row r="4" spans="1:14" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="360" t="s">
+    <row r="4" spans="1:14" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="362" t="s">
         <v>352</v>
       </c>
-      <c r="B4" s="361"/>
-      <c r="C4" s="361"/>
-      <c r="D4" s="361"/>
-      <c r="E4" s="361"/>
-      <c r="F4" s="361"/>
-      <c r="G4" s="361"/>
-      <c r="H4" s="361"/>
-      <c r="I4" s="361"/>
-      <c r="J4" s="361"/>
-      <c r="K4" s="361"/>
-      <c r="L4" s="362"/>
+      <c r="B4" s="363"/>
+      <c r="C4" s="363"/>
+      <c r="D4" s="363"/>
+      <c r="E4" s="363"/>
+      <c r="F4" s="363"/>
+      <c r="G4" s="363"/>
+      <c r="H4" s="363"/>
+      <c r="I4" s="363"/>
+      <c r="J4" s="363"/>
+      <c r="K4" s="363"/>
+      <c r="L4" s="364"/>
       <c r="M4" s="240"/>
     </row>
-    <row r="5" spans="1:14" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="363"/>
-      <c r="B5" s="364"/>
-      <c r="C5" s="364"/>
-      <c r="D5" s="364"/>
-      <c r="E5" s="364"/>
-      <c r="F5" s="364"/>
-      <c r="G5" s="364"/>
-      <c r="H5" s="364"/>
-      <c r="I5" s="364"/>
-      <c r="J5" s="364"/>
-      <c r="K5" s="364"/>
-      <c r="L5" s="365"/>
+    <row r="5" spans="1:14" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="365"/>
+      <c r="B5" s="366"/>
+      <c r="C5" s="366"/>
+      <c r="D5" s="366"/>
+      <c r="E5" s="366"/>
+      <c r="F5" s="366"/>
+      <c r="G5" s="366"/>
+      <c r="H5" s="366"/>
+      <c r="I5" s="366"/>
+      <c r="J5" s="366"/>
+      <c r="K5" s="366"/>
+      <c r="L5" s="367"/>
       <c r="M5" s="240"/>
     </row>
-    <row r="6" spans="1:14" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="363"/>
-      <c r="B6" s="364"/>
-      <c r="C6" s="364"/>
-      <c r="D6" s="364"/>
-      <c r="E6" s="364"/>
-      <c r="F6" s="364"/>
-      <c r="G6" s="364"/>
-      <c r="H6" s="364"/>
-      <c r="I6" s="364"/>
-      <c r="J6" s="364"/>
-      <c r="K6" s="364"/>
-      <c r="L6" s="365"/>
+    <row r="6" spans="1:14" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="365"/>
+      <c r="B6" s="366"/>
+      <c r="C6" s="366"/>
+      <c r="D6" s="366"/>
+      <c r="E6" s="366"/>
+      <c r="F6" s="366"/>
+      <c r="G6" s="366"/>
+      <c r="H6" s="366"/>
+      <c r="I6" s="366"/>
+      <c r="J6" s="366"/>
+      <c r="K6" s="366"/>
+      <c r="L6" s="367"/>
       <c r="M6" s="240"/>
     </row>
-    <row r="7" spans="1:14" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="363"/>
-      <c r="B7" s="364"/>
-      <c r="C7" s="364"/>
-      <c r="D7" s="364"/>
-      <c r="E7" s="364"/>
-      <c r="F7" s="364"/>
-      <c r="G7" s="364"/>
-      <c r="H7" s="364"/>
-      <c r="I7" s="364"/>
-      <c r="J7" s="364"/>
-      <c r="K7" s="364"/>
-      <c r="L7" s="365"/>
+    <row r="7" spans="1:14" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="365"/>
+      <c r="B7" s="366"/>
+      <c r="C7" s="366"/>
+      <c r="D7" s="366"/>
+      <c r="E7" s="366"/>
+      <c r="F7" s="366"/>
+      <c r="G7" s="366"/>
+      <c r="H7" s="366"/>
+      <c r="I7" s="366"/>
+      <c r="J7" s="366"/>
+      <c r="K7" s="366"/>
+      <c r="L7" s="367"/>
       <c r="M7" s="240"/>
     </row>
-    <row r="8" spans="1:14" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="366"/>
-      <c r="B8" s="367"/>
-      <c r="C8" s="367"/>
-      <c r="D8" s="367"/>
-      <c r="E8" s="367"/>
-      <c r="F8" s="367"/>
-      <c r="G8" s="367"/>
-      <c r="H8" s="367"/>
-      <c r="I8" s="367"/>
-      <c r="J8" s="367"/>
-      <c r="K8" s="367"/>
-      <c r="L8" s="368"/>
-    </row>
-    <row r="9" spans="1:14" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="376" t="s">
+    <row r="8" spans="1:14" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="368"/>
+      <c r="B8" s="369"/>
+      <c r="C8" s="369"/>
+      <c r="D8" s="369"/>
+      <c r="E8" s="369"/>
+      <c r="F8" s="369"/>
+      <c r="G8" s="369"/>
+      <c r="H8" s="369"/>
+      <c r="I8" s="369"/>
+      <c r="J8" s="369"/>
+      <c r="K8" s="369"/>
+      <c r="L8" s="370"/>
+    </row>
+    <row r="9" spans="1:14" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="378" t="s">
         <v>350</v>
       </c>
-      <c r="B9" s="377"/>
-      <c r="C9" s="377"/>
-      <c r="D9" s="377"/>
-      <c r="E9" s="377"/>
-      <c r="F9" s="377"/>
-      <c r="G9" s="377"/>
-      <c r="H9" s="377"/>
-      <c r="I9" s="377"/>
-      <c r="J9" s="377"/>
-      <c r="K9" s="377"/>
-      <c r="L9" s="378"/>
-    </row>
-    <row r="10" spans="1:14" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="379" t="s">
+      <c r="B9" s="379"/>
+      <c r="C9" s="379"/>
+      <c r="D9" s="379"/>
+      <c r="E9" s="379"/>
+      <c r="F9" s="379"/>
+      <c r="G9" s="379"/>
+      <c r="H9" s="379"/>
+      <c r="I9" s="379"/>
+      <c r="J9" s="379"/>
+      <c r="K9" s="379"/>
+      <c r="L9" s="380"/>
+    </row>
+    <row r="10" spans="1:14" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="381" t="s">
         <v>351</v>
       </c>
-      <c r="B10" s="380"/>
-      <c r="C10" s="380"/>
-      <c r="D10" s="380"/>
-      <c r="E10" s="380"/>
-      <c r="F10" s="380"/>
-      <c r="G10" s="380"/>
-      <c r="H10" s="380"/>
-      <c r="I10" s="380"/>
-      <c r="J10" s="380"/>
-      <c r="K10" s="380"/>
-      <c r="L10" s="381"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="369" t="s">
+      <c r="B10" s="382"/>
+      <c r="C10" s="382"/>
+      <c r="D10" s="382"/>
+      <c r="E10" s="382"/>
+      <c r="F10" s="382"/>
+      <c r="G10" s="382"/>
+      <c r="H10" s="382"/>
+      <c r="I10" s="382"/>
+      <c r="J10" s="382"/>
+      <c r="K10" s="382"/>
+      <c r="L10" s="383"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="371" t="s">
         <v>312</v>
       </c>
-      <c r="B11" s="369" t="s">
+      <c r="B11" s="371" t="s">
         <v>313</v>
       </c>
-      <c r="C11" s="369" t="s">
+      <c r="C11" s="371" t="s">
         <v>314</v>
       </c>
-      <c r="D11" s="369" t="s">
+      <c r="D11" s="371" t="s">
         <v>315</v>
       </c>
-      <c r="E11" s="372" t="s">
+      <c r="E11" s="374" t="s">
         <v>316</v>
       </c>
-      <c r="F11" s="369" t="s">
+      <c r="F11" s="371" t="s">
         <v>317</v>
       </c>
-      <c r="G11" s="374" t="s">
+      <c r="G11" s="376" t="s">
         <v>318</v>
       </c>
-      <c r="H11" s="372" t="s">
+      <c r="H11" s="374" t="s">
         <v>319</v>
       </c>
-      <c r="I11" s="372" t="s">
+      <c r="I11" s="374" t="s">
         <v>311</v>
       </c>
-      <c r="J11" s="383" t="s">
+      <c r="J11" s="385" t="s">
         <v>310</v>
       </c>
       <c r="K11" s="241" t="s">
         <v>320</v>
       </c>
-      <c r="L11" s="385" t="s">
+      <c r="L11" s="358" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="370"/>
-      <c r="B12" s="370"/>
-      <c r="C12" s="371"/>
-      <c r="D12" s="370"/>
-      <c r="E12" s="373"/>
-      <c r="F12" s="370"/>
-      <c r="G12" s="375"/>
-      <c r="H12" s="373"/>
-      <c r="I12" s="373"/>
-      <c r="J12" s="384"/>
+    <row r="12" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="372"/>
+      <c r="B12" s="372"/>
+      <c r="C12" s="373"/>
+      <c r="D12" s="372"/>
+      <c r="E12" s="375"/>
+      <c r="F12" s="372"/>
+      <c r="G12" s="377"/>
+      <c r="H12" s="375"/>
+      <c r="I12" s="375"/>
+      <c r="J12" s="386"/>
       <c r="K12" s="242" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 18/02</v>
       </c>
-      <c r="L12" s="386"/>
-    </row>
-    <row r="13" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L12" s="359"/>
+    </row>
+    <row r="13" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="243">
         <v>1</v>
       </c>
@@ -4902,7 +4902,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="243">
         <v>2</v>
       </c>
@@ -4951,7 +4951,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="243">
         <v>3</v>
       </c>
@@ -4998,7 +4998,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="243">
         <v>4</v>
       </c>
@@ -5044,7 +5044,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="243">
         <v>5</v>
       </c>
@@ -5090,7 +5090,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="243">
         <v>6</v>
       </c>
@@ -5137,7 +5137,7 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="243">
         <v>7</v>
       </c>
@@ -5184,7 +5184,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="243">
         <v>8</v>
       </c>
@@ -5231,7 +5231,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="243">
         <v>9</v>
       </c>
@@ -5277,7 +5277,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="243">
         <v>10</v>
       </c>
@@ -5324,7 +5324,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="243">
         <v>11</v>
       </c>
@@ -5371,7 +5371,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="243">
         <v>12</v>
       </c>
@@ -5417,7 +5417,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="243">
         <v>13</v>
       </c>
@@ -5463,7 +5463,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="243">
         <v>14</v>
       </c>
@@ -5510,7 +5510,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="328">
         <v>15</v>
       </c>
@@ -5554,7 +5554,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="243">
         <v>16</v>
       </c>
@@ -5601,7 +5601,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="243">
         <v>17</v>
       </c>
@@ -5648,7 +5648,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="306">
         <v>18</v>
       </c>
@@ -5695,7 +5695,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="243">
         <v>19</v>
       </c>
@@ -5745,7 +5745,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="313">
         <v>20</v>
       </c>
@@ -5794,7 +5794,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="313">
         <v>21</v>
       </c>
@@ -5841,7 +5841,7 @@
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="252">
         <f>A33+1</f>
         <v>22</v>
@@ -5889,7 +5889,7 @@
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="252">
         <f t="shared" ref="A35:A98" si="9">A34+1</f>
         <v>23</v>
@@ -5936,7 +5936,7 @@
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="252">
         <f t="shared" si="9"/>
         <v>24</v>
@@ -5984,7 +5984,7 @@
         <v>0.24000000000000007</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="252">
         <f t="shared" si="9"/>
         <v>25</v>
@@ -6031,7 +6031,7 @@
         <v>0.25000000000000006</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="252">
         <f t="shared" si="9"/>
         <v>26</v>
@@ -6076,7 +6076,7 @@
         <v>0.26000000000000006</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="252">
         <f t="shared" si="9"/>
         <v>27</v>
@@ -6123,7 +6123,7 @@
         <v>0.27000000000000007</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="252">
         <f t="shared" si="9"/>
         <v>28</v>
@@ -6170,7 +6170,7 @@
         <v>0.28000000000000008</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="280">
         <f t="shared" si="9"/>
         <v>29</v>
@@ -6220,7 +6220,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="344">
         <f t="shared" si="9"/>
         <v>30</v>
@@ -6268,7 +6268,7 @@
         <v>0.3000000000000001</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="252">
         <f t="shared" si="9"/>
         <v>31</v>
@@ -6316,7 +6316,7 @@
         <v>0.31000000000000011</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="252">
         <f t="shared" si="9"/>
         <v>32</v>
@@ -6364,7 +6364,7 @@
         <v>0.32000000000000012</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="252">
         <f t="shared" si="9"/>
         <v>33</v>
@@ -6411,7 +6411,7 @@
         <v>0.33000000000000013</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="252">
         <f t="shared" si="9"/>
         <v>34</v>
@@ -6459,7 +6459,7 @@
         <v>0.34000000000000014</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="280">
         <f t="shared" si="9"/>
         <v>35</v>
@@ -6507,7 +6507,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="252">
         <f t="shared" si="9"/>
         <v>36</v>
@@ -6557,7 +6557,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="252">
         <f t="shared" si="9"/>
         <v>37</v>
@@ -6602,7 +6602,7 @@
         <v>0.37000000000000016</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="252">
         <f t="shared" si="9"/>
         <v>38</v>
@@ -6649,7 +6649,7 @@
         <v>0.38000000000000017</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="252">
         <f t="shared" si="9"/>
         <v>39</v>
@@ -6696,7 +6696,7 @@
         <v>0.39000000000000018</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="252">
         <f t="shared" si="9"/>
         <v>40</v>
@@ -6741,7 +6741,7 @@
         <v>0.40000000000000019</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" s="252">
         <f t="shared" si="9"/>
         <v>41</v>
@@ -6789,7 +6789,7 @@
         <v>0.4100000000000002</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" s="252">
         <f t="shared" si="9"/>
         <v>42</v>
@@ -6834,7 +6834,7 @@
         <v>0.42000000000000021</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="252">
         <f t="shared" si="9"/>
         <v>43</v>
@@ -6881,7 +6881,7 @@
         <v>0.43000000000000022</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="252">
         <f t="shared" si="9"/>
         <v>44</v>
@@ -6926,7 +6926,7 @@
         <v>0.44000000000000022</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" s="252">
         <f t="shared" si="9"/>
         <v>45</v>
@@ -6974,7 +6974,7 @@
         <v>0.45000000000000023</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" s="252">
         <f t="shared" si="9"/>
         <v>46</v>
@@ -7024,7 +7024,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" s="280">
         <f t="shared" si="9"/>
         <v>47</v>
@@ -7074,7 +7074,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" s="313">
         <f t="shared" si="9"/>
         <v>48</v>
@@ -7125,7 +7125,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" s="252">
         <f t="shared" si="9"/>
         <v>49</v>
@@ -7172,7 +7172,7 @@
         <v>0.49000000000000027</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" s="252">
         <f t="shared" si="9"/>
         <v>50</v>
@@ -7217,7 +7217,7 @@
         <v>0.50000000000000022</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" s="252">
         <f t="shared" si="9"/>
         <v>51</v>
@@ -7264,7 +7264,7 @@
         <v>0.51000000000000023</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" s="252">
         <f t="shared" si="9"/>
         <v>52</v>
@@ -7312,7 +7312,7 @@
         <v>0.52000000000000024</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" s="333">
         <f t="shared" si="9"/>
         <v>53</v>
@@ -7359,7 +7359,7 @@
         <v>0.53000000000000025</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" s="252">
         <f t="shared" si="9"/>
         <v>54</v>
@@ -7406,7 +7406,7 @@
         <v>0.54000000000000026</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" s="252">
         <f t="shared" si="9"/>
         <v>55</v>
@@ -7453,7 +7453,7 @@
         <v>0.55000000000000027</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" s="252">
         <f t="shared" si="9"/>
         <v>56</v>
@@ -7501,7 +7501,7 @@
         <v>0.56000000000000028</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" s="341">
         <f t="shared" si="9"/>
         <v>57</v>
@@ -7549,7 +7549,7 @@
         <v>0.57000000000000028</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" s="252">
         <f t="shared" si="9"/>
         <v>58</v>
@@ -7597,7 +7597,7 @@
         <v>0.58000000000000029</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" s="333">
         <f t="shared" si="9"/>
         <v>59</v>
@@ -7642,7 +7642,7 @@
         <v>0.5900000000000003</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" s="252">
         <f t="shared" si="9"/>
         <v>60</v>
@@ -7689,7 +7689,7 @@
         <v>0.60000000000000031</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" s="252">
         <f t="shared" si="9"/>
         <v>61</v>
@@ -7737,7 +7737,7 @@
         <v>0.61000000000000032</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" s="252">
         <f t="shared" si="9"/>
         <v>62</v>
@@ -7784,7 +7784,7 @@
         <v>0.62000000000000033</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" s="252">
         <f t="shared" si="9"/>
         <v>63</v>
@@ -7832,7 +7832,7 @@
         <v>0.63000000000000034</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" s="252">
         <f t="shared" si="9"/>
         <v>64</v>
@@ -7879,7 +7879,7 @@
         <v>0.64000000000000035</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" s="252">
         <f t="shared" si="9"/>
         <v>65</v>
@@ -7929,7 +7929,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" s="252">
         <f t="shared" si="9"/>
         <v>66</v>
@@ -7976,7 +7976,7 @@
         <v>0.66000000000000036</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" s="252">
         <f t="shared" si="9"/>
         <v>67</v>
@@ -8023,7 +8023,7 @@
         <v>0.67000000000000037</v>
       </c>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" s="252">
         <f t="shared" si="9"/>
         <v>68</v>
@@ -8070,7 +8070,7 @@
         <v>0.68000000000000038</v>
       </c>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81" s="252">
         <f t="shared" si="9"/>
         <v>69</v>
@@ -8117,7 +8117,7 @@
         <v>0.69000000000000039</v>
       </c>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82" s="280">
         <f t="shared" si="9"/>
         <v>70</v>
@@ -8168,7 +8168,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A83" s="252">
         <f t="shared" si="9"/>
         <v>71</v>
@@ -8215,7 +8215,7 @@
         <v>0.71000000000000041</v>
       </c>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" s="252">
         <f t="shared" si="9"/>
         <v>72</v>
@@ -8263,7 +8263,7 @@
         <v>0.72000000000000042</v>
       </c>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85" s="252">
         <f t="shared" si="9"/>
         <v>73</v>
@@ -8311,7 +8311,7 @@
         <v>0.73000000000000043</v>
       </c>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A86" s="252">
         <f t="shared" si="9"/>
         <v>74</v>
@@ -8358,7 +8358,7 @@
         <v>0.74000000000000044</v>
       </c>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A87" s="252">
         <f t="shared" si="9"/>
         <v>75</v>
@@ -8406,7 +8406,7 @@
         <v>0.75000000000000044</v>
       </c>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A88" s="252">
         <f t="shared" si="9"/>
         <v>76</v>
@@ -8454,7 +8454,7 @@
         <v>0.76000000000000045</v>
       </c>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A89" s="252">
         <f t="shared" si="9"/>
         <v>77</v>
@@ -8501,7 +8501,7 @@
         <v>0.77000000000000046</v>
       </c>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90" s="252">
         <f t="shared" si="9"/>
         <v>78</v>
@@ -8548,7 +8548,7 @@
         <v>0.78000000000000047</v>
       </c>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91" s="252">
         <f t="shared" si="9"/>
         <v>79</v>
@@ -8596,7 +8596,7 @@
         <v>0.79000000000000048</v>
       </c>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A92" s="252">
         <f t="shared" si="9"/>
         <v>80</v>
@@ -8641,7 +8641,7 @@
         <v>0.80000000000000049</v>
       </c>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A93" s="280">
         <f t="shared" si="9"/>
         <v>81</v>
@@ -8691,7 +8691,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94" s="252">
         <f t="shared" si="9"/>
         <v>82</v>
@@ -8739,7 +8739,7 @@
         <v>0.82000000000000051</v>
       </c>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A95" s="323">
         <f t="shared" si="9"/>
         <v>83</v>
@@ -8786,7 +8786,7 @@
         <v>0.83000000000000052</v>
       </c>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A96" s="323">
         <f t="shared" si="9"/>
         <v>84</v>
@@ -8834,7 +8834,7 @@
         <v>0.84000000000000052</v>
       </c>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A97" s="252">
         <f t="shared" si="9"/>
         <v>85</v>
@@ -8882,7 +8882,7 @@
         <v>0.85000000000000053</v>
       </c>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A98" s="252">
         <f t="shared" si="9"/>
         <v>86</v>
@@ -8930,7 +8930,7 @@
         <v>0.86000000000000054</v>
       </c>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A99" s="252">
         <f t="shared" ref="A99:A115" si="24">A98+1</f>
         <v>87</v>
@@ -8977,7 +8977,7 @@
         <v>0.87000000000000055</v>
       </c>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A100" s="252">
         <f t="shared" si="24"/>
         <v>88</v>
@@ -9024,7 +9024,7 @@
         <v>0.88000000000000056</v>
       </c>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A101" s="252">
         <f t="shared" si="24"/>
         <v>89</v>
@@ -9072,7 +9072,7 @@
         <v>0.89000000000000057</v>
       </c>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A102" s="252">
         <f t="shared" si="24"/>
         <v>90</v>
@@ -9119,7 +9119,7 @@
         <v>0.90000000000000058</v>
       </c>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A103" s="252">
         <f t="shared" si="24"/>
         <v>91</v>
@@ -9164,7 +9164,7 @@
         <v>0.91000000000000059</v>
       </c>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A104" s="252">
         <f t="shared" si="24"/>
         <v>92</v>
@@ -9212,7 +9212,7 @@
         <v>0.9200000000000006</v>
       </c>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A105" s="280">
         <f t="shared" si="24"/>
         <v>93</v>
@@ -9260,7 +9260,7 @@
         <v>0.9300000000000006</v>
       </c>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A106" s="252">
         <f t="shared" si="24"/>
         <v>94</v>
@@ -9308,7 +9308,7 @@
         <v>0.94000000000000061</v>
       </c>
     </row>
-    <row r="107" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="252">
         <f t="shared" si="24"/>
         <v>95</v>
@@ -9356,7 +9356,7 @@
         <v>0.95000000000000062</v>
       </c>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A108" s="252">
         <f t="shared" si="24"/>
         <v>96</v>
@@ -9407,7 +9407,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A109" s="252">
         <f t="shared" si="24"/>
         <v>97</v>
@@ -9455,7 +9455,7 @@
         <v>0.97000000000000064</v>
       </c>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A110" s="252">
         <f t="shared" si="24"/>
         <v>98</v>
@@ -9503,7 +9503,7 @@
         <v>0.98000000000000065</v>
       </c>
     </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A111" s="252">
         <f t="shared" si="24"/>
         <v>99</v>
@@ -9550,7 +9550,7 @@
         <v>0.99000000000000066</v>
       </c>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A112" s="252">
         <f t="shared" si="24"/>
         <v>100</v>
@@ -9598,7 +9598,7 @@
         <v>1.0000000000000007</v>
       </c>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A113" s="280">
         <f t="shared" si="24"/>
         <v>101</v>
@@ -9646,7 +9646,7 @@
         <v>1.0100000000000007</v>
       </c>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A114" s="252">
         <f t="shared" si="24"/>
         <v>102</v>
@@ -9693,7 +9693,7 @@
         <v>1.0200000000000007</v>
       </c>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:13" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A115" s="252">
         <f t="shared" si="24"/>
         <v>103</v>
@@ -9740,7 +9740,7 @@
         <v>1.0300000000000007</v>
       </c>
     </row>
-    <row r="116" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A116" s="252"/>
       <c r="B116" s="256"/>
       <c r="C116" s="251"/>
@@ -9755,7 +9755,7 @@
       <c r="L116" s="250"/>
       <c r="M116" s="205"/>
     </row>
-    <row r="117" spans="1:13" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:13" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A117" s="257"/>
       <c r="B117" s="258"/>
       <c r="C117" s="258"/>
@@ -9796,87 +9796,88 @@
         <v>36040836.560000002</v>
       </c>
     </row>
-    <row r="118" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B118" s="264"/>
       <c r="C118" s="264"/>
     </row>
-    <row r="119" spans="1:13" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="120" spans="1:13" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B120" s="358" t="s">
+    <row r="119" spans="1:13" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="120" spans="1:13" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B120" s="360" t="s">
         <v>286</v>
       </c>
-      <c r="C120" s="358"/>
-      <c r="D120" s="358"/>
-      <c r="E120" s="358"/>
-      <c r="F120" s="358"/>
-      <c r="G120" s="358"/>
-      <c r="H120" s="358"/>
-      <c r="I120" s="358"/>
-      <c r="J120" s="358"/>
-      <c r="K120" s="358"/>
-    </row>
-    <row r="121" spans="1:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B121" s="358"/>
-      <c r="C121" s="358"/>
-      <c r="D121" s="358"/>
-      <c r="E121" s="358"/>
-      <c r="F121" s="358"/>
-      <c r="G121" s="358"/>
-      <c r="H121" s="358"/>
-      <c r="I121" s="358"/>
-      <c r="J121" s="358"/>
-      <c r="K121" s="358"/>
-    </row>
-    <row r="122" spans="1:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B122" s="358"/>
-      <c r="C122" s="358"/>
-      <c r="D122" s="358"/>
-      <c r="E122" s="358"/>
-      <c r="F122" s="358"/>
-      <c r="G122" s="358"/>
-      <c r="H122" s="358"/>
-      <c r="I122" s="358"/>
-      <c r="J122" s="358"/>
-      <c r="K122" s="358"/>
-    </row>
-    <row r="123" spans="1:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B123" s="358"/>
-      <c r="C123" s="358"/>
-      <c r="D123" s="358"/>
-      <c r="E123" s="358"/>
-      <c r="F123" s="358"/>
-      <c r="G123" s="358"/>
-      <c r="H123" s="358"/>
-      <c r="I123" s="358"/>
-      <c r="J123" s="358"/>
-      <c r="K123" s="358"/>
-    </row>
-    <row r="124" spans="1:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B124" s="358"/>
-      <c r="C124" s="358"/>
-      <c r="D124" s="358"/>
-      <c r="E124" s="358"/>
-      <c r="F124" s="358"/>
-      <c r="G124" s="358"/>
-      <c r="H124" s="358"/>
-      <c r="I124" s="358"/>
-      <c r="J124" s="358"/>
-      <c r="K124" s="358"/>
-    </row>
-    <row r="125" spans="1:13" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B125" s="358"/>
-      <c r="C125" s="358"/>
-      <c r="D125" s="358"/>
-      <c r="E125" s="358"/>
-      <c r="F125" s="358"/>
-      <c r="G125" s="358"/>
-      <c r="H125" s="358"/>
-      <c r="I125" s="358"/>
-      <c r="J125" s="358"/>
-      <c r="K125" s="358"/>
+      <c r="C120" s="360"/>
+      <c r="D120" s="360"/>
+      <c r="E120" s="360"/>
+      <c r="F120" s="360"/>
+      <c r="G120" s="360"/>
+      <c r="H120" s="360"/>
+      <c r="I120" s="360"/>
+      <c r="J120" s="360"/>
+      <c r="K120" s="360"/>
+    </row>
+    <row r="121" spans="1:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B121" s="360"/>
+      <c r="C121" s="360"/>
+      <c r="D121" s="360"/>
+      <c r="E121" s="360"/>
+      <c r="F121" s="360"/>
+      <c r="G121" s="360"/>
+      <c r="H121" s="360"/>
+      <c r="I121" s="360"/>
+      <c r="J121" s="360"/>
+      <c r="K121" s="360"/>
+    </row>
+    <row r="122" spans="1:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B122" s="360"/>
+      <c r="C122" s="360"/>
+      <c r="D122" s="360"/>
+      <c r="E122" s="360"/>
+      <c r="F122" s="360"/>
+      <c r="G122" s="360"/>
+      <c r="H122" s="360"/>
+      <c r="I122" s="360"/>
+      <c r="J122" s="360"/>
+      <c r="K122" s="360"/>
+    </row>
+    <row r="123" spans="1:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B123" s="360"/>
+      <c r="C123" s="360"/>
+      <c r="D123" s="360"/>
+      <c r="E123" s="360"/>
+      <c r="F123" s="360"/>
+      <c r="G123" s="360"/>
+      <c r="H123" s="360"/>
+      <c r="I123" s="360"/>
+      <c r="J123" s="360"/>
+      <c r="K123" s="360"/>
+    </row>
+    <row r="124" spans="1:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B124" s="360"/>
+      <c r="C124" s="360"/>
+      <c r="D124" s="360"/>
+      <c r="E124" s="360"/>
+      <c r="F124" s="360"/>
+      <c r="G124" s="360"/>
+      <c r="H124" s="360"/>
+      <c r="I124" s="360"/>
+      <c r="J124" s="360"/>
+      <c r="K124" s="360"/>
+    </row>
+    <row r="125" spans="1:13" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B125" s="360"/>
+      <c r="C125" s="360"/>
+      <c r="D125" s="360"/>
+      <c r="E125" s="360"/>
+      <c r="F125" s="360"/>
+      <c r="G125" s="360"/>
+      <c r="H125" s="360"/>
+      <c r="I125" s="360"/>
+      <c r="J125" s="360"/>
+      <c r="K125" s="360"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="J11:J12"/>
     <mergeCell ref="L11:L12"/>
     <mergeCell ref="B120:K125"/>
     <mergeCell ref="D1:K1"/>
@@ -9893,7 +9894,6 @@
     <mergeCell ref="A10:L10"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="I11:I12"/>
-    <mergeCell ref="J11:J12"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="3" scale="85" orientation="portrait" r:id="rId1"/>
@@ -9903,17 +9903,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56D35F41-74CB-4294-A7A2-EC3C67574818}">
   <dimension ref="B4:Q26"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:14" ht="144" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:14" ht="165" x14ac:dyDescent="0.25">
       <c r="B4" s="226" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="6" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="387" t="s">
         <v>413</v>
       </c>
@@ -9932,12 +9932,12 @@
         <v>400</v>
       </c>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B9" s="332" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B13" s="338" t="s">
         <v>416</v>
       </c>
@@ -9954,7 +9954,7 @@
       <c r="M13" s="338"/>
       <c r="N13" s="338"/>
     </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B14" s="338" t="s">
         <v>417</v>
       </c>
@@ -9973,7 +9973,7 @@
       <c r="M14" s="338"/>
       <c r="N14" s="338"/>
     </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B15" s="338" t="s">
         <v>418</v>
       </c>
@@ -9992,7 +9992,7 @@
       <c r="M15" s="338"/>
       <c r="N15" s="338"/>
     </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B16" s="338" t="s">
         <v>419</v>
       </c>
@@ -10011,7 +10011,7 @@
       <c r="M16" s="338"/>
       <c r="N16" s="338"/>
     </row>
-    <row r="17" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B17" s="338"/>
       <c r="C17" s="338"/>
       <c r="D17" s="338"/>
@@ -10026,36 +10026,36 @@
       <c r="M17" s="338"/>
       <c r="N17" s="338"/>
     </row>
-    <row r="20" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B20" s="340" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B23" s="343" t="s">
         <v>423</v>
       </c>
       <c r="C23" s="343"/>
     </row>
-    <row r="26" spans="2:17" ht="117" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="397" t="s">
+    <row r="26" spans="2:17" ht="117" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="388" t="s">
         <v>424</v>
       </c>
-      <c r="C26" s="397"/>
-      <c r="D26" s="397"/>
-      <c r="E26" s="397"/>
-      <c r="F26" s="397"/>
-      <c r="G26" s="397"/>
-      <c r="H26" s="397"/>
-      <c r="I26" s="397"/>
-      <c r="J26" s="397"/>
-      <c r="K26" s="397"/>
-      <c r="L26" s="397"/>
-      <c r="M26" s="397"/>
-      <c r="N26" s="397"/>
-      <c r="O26" s="397"/>
-      <c r="P26" s="397"/>
-      <c r="Q26" s="397"/>
+      <c r="C26" s="388"/>
+      <c r="D26" s="388"/>
+      <c r="E26" s="388"/>
+      <c r="F26" s="388"/>
+      <c r="G26" s="388"/>
+      <c r="H26" s="388"/>
+      <c r="I26" s="388"/>
+      <c r="J26" s="388"/>
+      <c r="K26" s="388"/>
+      <c r="L26" s="388"/>
+      <c r="M26" s="388"/>
+      <c r="N26" s="388"/>
+      <c r="O26" s="388"/>
+      <c r="P26" s="388"/>
+      <c r="Q26" s="388"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -10069,27 +10069,27 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R198"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="5.88671875" style="9" customWidth="1"/>
-    <col min="3" max="3" width="11.44140625" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="62.6640625" customWidth="1"/>
-    <col min="5" max="5" width="14.5546875" customWidth="1"/>
-    <col min="6" max="6" width="14.5546875" style="12" customWidth="1"/>
-    <col min="8" max="8" width="4.5546875" customWidth="1"/>
-    <col min="9" max="9" width="35.88671875" customWidth="1"/>
-    <col min="10" max="10" width="12.33203125" customWidth="1"/>
-    <col min="11" max="11" width="9.33203125" customWidth="1"/>
-    <col min="12" max="12" width="11.109375" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" style="9" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="62.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="12" customWidth="1"/>
+    <col min="8" max="8" width="4.5703125" customWidth="1"/>
+    <col min="9" max="9" width="35.85546875" customWidth="1"/>
+    <col min="10" max="10" width="12.28515625" customWidth="1"/>
+    <col min="11" max="11" width="9.28515625" customWidth="1"/>
+    <col min="12" max="12" width="11.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="388" t="s">
+    <row r="1" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="389" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="388"/>
-      <c r="C1" s="388"/>
+      <c r="B1" s="389"/>
+      <c r="C1" s="389"/>
       <c r="I1" s="40"/>
       <c r="J1" s="40" t="s">
         <v>20</v>
@@ -10103,31 +10103,31 @@
       <c r="Q1" s="40"/>
       <c r="R1" s="40"/>
     </row>
-    <row r="2" spans="1:18" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="388"/>
-      <c r="B2" s="388"/>
-      <c r="C2" s="388"/>
+    <row r="2" spans="1:18" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="389"/>
+      <c r="B2" s="389"/>
+      <c r="C2" s="389"/>
       <c r="J2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="15.6" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:18" ht="16.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="30" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
       <c r="D3" s="1"/>
-      <c r="E3" s="389" t="s">
+      <c r="E3" s="390" t="s">
         <v>49</v>
       </c>
-      <c r="F3" s="390"/>
+      <c r="F3" s="391"/>
       <c r="G3" s="1"/>
       <c r="J3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B4" s="8" t="s">
         <v>6</v>
       </c>
@@ -10146,7 +10146,7 @@
       <c r="N4" s="9"/>
       <c r="O4" s="36"/>
     </row>
-    <row r="5" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="8" t="s">
         <v>0</v>
       </c>
@@ -10159,7 +10159,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:18" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="8" t="s">
         <v>40</v>
       </c>
@@ -10186,7 +10186,7 @@
       <c r="Q6" s="32"/>
       <c r="R6" s="32"/>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
       <c r="D7" s="8" t="s">
@@ -10206,7 +10206,7 @@
       <c r="P7"/>
       <c r="Q7"/>
     </row>
-    <row r="8" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="8" t="s">
         <v>7</v>
       </c>
@@ -10229,7 +10229,7 @@
       <c r="Q8" s="35"/>
       <c r="R8" s="35"/>
     </row>
-    <row r="9" spans="1:18" s="3" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:18" s="3" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="4">
         <v>1</v>
       </c>
@@ -10256,7 +10256,7 @@
       <c r="Q9" s="35"/>
       <c r="R9" s="35"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B10" s="7"/>
       <c r="D10" t="s">
         <v>248</v>
@@ -10282,7 +10282,7 @@
       <c r="Q10" s="35"/>
       <c r="R10" s="35"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B11" s="7"/>
       <c r="D11" t="s">
         <v>50</v>
@@ -10303,7 +10303,7 @@
       <c r="Q11" s="35"/>
       <c r="R11" s="35"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B12" s="7"/>
       <c r="D12" t="s">
         <v>51</v>
@@ -10329,7 +10329,7 @@
       <c r="Q12" s="35"/>
       <c r="R12" s="35"/>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B13" s="7"/>
       <c r="D13" t="s">
         <v>52</v>
@@ -10350,7 +10350,7 @@
       <c r="Q13" s="35"/>
       <c r="R13" s="35"/>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B14" s="7"/>
       <c r="D14" t="s">
         <v>53</v>
@@ -10371,7 +10371,7 @@
       <c r="Q14" s="35"/>
       <c r="R14" s="35"/>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B15" s="7"/>
       <c r="D15" t="s">
         <v>255</v>
@@ -10392,7 +10392,7 @@
       <c r="Q15" s="35"/>
       <c r="R15" s="35"/>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B16" s="7"/>
       <c r="D16" t="s">
         <v>256</v>
@@ -10413,7 +10413,7 @@
       <c r="Q16" s="35"/>
       <c r="R16" s="35"/>
     </row>
-    <row r="17" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B17" s="7"/>
       <c r="D17" t="s">
         <v>55</v>
@@ -10435,7 +10435,7 @@
       <c r="O17" s="35"/>
       <c r="P17" s="35"/>
     </row>
-    <row r="18" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B18" s="7"/>
       <c r="D18" t="s">
         <v>56</v>
@@ -10461,7 +10461,7 @@
       <c r="O18" s="35"/>
       <c r="P18" s="35"/>
     </row>
-    <row r="19" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B19" s="7"/>
       <c r="D19" t="s">
         <v>57</v>
@@ -10483,7 +10483,7 @@
       <c r="O19" s="35"/>
       <c r="P19" s="35"/>
     </row>
-    <row r="20" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B20" s="7"/>
       <c r="D20" t="s">
         <v>58</v>
@@ -10502,7 +10502,7 @@
       <c r="O20" s="35"/>
       <c r="P20" s="35"/>
     </row>
-    <row r="21" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B21" s="7"/>
       <c r="D21" t="s">
         <v>59</v>
@@ -10524,7 +10524,7 @@
       <c r="O21" s="35"/>
       <c r="P21" s="35"/>
     </row>
-    <row r="22" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B22" s="7"/>
       <c r="D22" t="s">
         <v>60</v>
@@ -10543,7 +10543,7 @@
       <c r="O22" s="35"/>
       <c r="P22" s="35"/>
     </row>
-    <row r="23" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B23" s="7"/>
       <c r="D23" t="s">
         <v>61</v>
@@ -10562,7 +10562,7 @@
       <c r="O23" s="35"/>
       <c r="P23" s="35"/>
     </row>
-    <row r="24" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B24" s="7"/>
       <c r="D24" t="s">
         <v>62</v>
@@ -10588,7 +10588,7 @@
       <c r="O24" s="35"/>
       <c r="P24" s="35"/>
     </row>
-    <row r="25" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B25" s="7"/>
       <c r="D25" t="s">
         <v>54</v>
@@ -10615,7 +10615,7 @@
       <c r="O25" s="35"/>
       <c r="P25" s="35"/>
     </row>
-    <row r="26" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B26" s="7"/>
       <c r="D26" t="s">
         <v>262</v>
@@ -10636,7 +10636,7 @@
       <c r="O26" s="35"/>
       <c r="P26" s="35"/>
     </row>
-    <row r="27" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B27" s="7">
         <v>2</v>
       </c>
@@ -10659,7 +10659,7 @@
       <c r="O27" s="35"/>
       <c r="P27" s="35"/>
     </row>
-    <row r="28" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B28" s="7"/>
       <c r="D28" t="s">
         <v>63</v>
@@ -10683,7 +10683,7 @@
       <c r="O28" s="35"/>
       <c r="P28" s="35"/>
     </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B29" s="7"/>
       <c r="D29" t="s">
         <v>64</v>
@@ -10705,7 +10705,7 @@
       <c r="O29" s="35"/>
       <c r="P29" s="35"/>
     </row>
-    <row r="30" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B30" s="7"/>
       <c r="D30" t="s">
         <v>65</v>
@@ -10727,7 +10727,7 @@
       <c r="O30" s="35"/>
       <c r="P30" s="35"/>
     </row>
-    <row r="31" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B31" s="7"/>
       <c r="D31" t="s">
         <v>66</v>
@@ -10746,7 +10746,7 @@
       <c r="O31" s="35"/>
       <c r="P31" s="35"/>
     </row>
-    <row r="32" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B32" s="7"/>
       <c r="D32" t="s">
         <v>67</v>
@@ -10765,7 +10765,7 @@
       <c r="O32" s="35"/>
       <c r="P32" s="35"/>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B33" s="7"/>
       <c r="D33" t="s">
         <v>68</v>
@@ -10784,7 +10784,7 @@
       <c r="O33" s="35"/>
       <c r="P33" s="35"/>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B34" s="7"/>
       <c r="D34" t="s">
         <v>259</v>
@@ -10806,7 +10806,7 @@
       <c r="O34" s="35"/>
       <c r="P34" s="35"/>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B35" s="7"/>
       <c r="D35" t="s">
         <v>260</v>
@@ -10828,7 +10828,7 @@
       <c r="O35" s="35"/>
       <c r="P35" s="35"/>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B36" s="7"/>
       <c r="D36" t="s">
         <v>261</v>
@@ -10850,7 +10850,7 @@
       <c r="O36" s="35"/>
       <c r="P36" s="35"/>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B37" s="7"/>
       <c r="D37" t="s">
         <v>257</v>
@@ -10872,7 +10872,7 @@
       <c r="O37" s="35"/>
       <c r="P37" s="35"/>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B38" s="7"/>
       <c r="D38" t="s">
         <v>258</v>
@@ -10894,7 +10894,7 @@
       <c r="O38" s="35"/>
       <c r="P38" s="35"/>
     </row>
-    <row r="39" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B39" s="7"/>
       <c r="D39" t="s">
         <v>20</v>
@@ -10921,7 +10921,7 @@
       <c r="O39" s="35"/>
       <c r="P39" s="35"/>
     </row>
-    <row r="40" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B40" s="7">
         <v>3</v>
       </c>
@@ -10944,7 +10944,7 @@
       <c r="O40" s="35"/>
       <c r="P40" s="35"/>
     </row>
-    <row r="41" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B41" s="7">
         <v>4</v>
       </c>
@@ -10967,7 +10967,7 @@
       <c r="Q41" s="35"/>
       <c r="R41" s="35"/>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B42" s="7"/>
       <c r="D42" s="96" t="s">
         <v>263</v>
@@ -10990,7 +10990,7 @@
       <c r="Q42" s="35"/>
       <c r="R42" s="35"/>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B43" s="7"/>
       <c r="D43" s="97" t="s">
         <v>264</v>
@@ -11018,7 +11018,7 @@
       <c r="Q43" s="12"/>
       <c r="R43" s="35"/>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B44" s="7"/>
       <c r="D44" s="97" t="s">
         <v>265</v>
@@ -11034,7 +11034,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B45" s="7"/>
       <c r="D45" s="97" t="s">
         <v>266</v>
@@ -11048,7 +11048,7 @@
       </c>
       <c r="J45" s="34"/>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B46" s="7"/>
       <c r="D46" s="97" t="s">
         <v>267</v>
@@ -11061,7 +11061,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="47" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B47" s="7"/>
       <c r="D47" s="58" t="s">
         <v>20</v>
@@ -11080,7 +11080,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="48" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="2"/>
       <c r="B48" s="7">
         <v>5</v>
@@ -11098,7 +11098,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="49" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B49" s="7"/>
       <c r="D49" t="s">
         <v>268</v>
@@ -11113,7 +11113,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="50" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B50" s="7"/>
       <c r="D50" t="s">
         <v>269</v>
@@ -11126,7 +11126,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="51" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B51" s="7"/>
       <c r="D51" t="s">
         <v>71</v>
@@ -11137,7 +11137,7 @@
       <c r="F51" s="56"/>
       <c r="G51" s="33"/>
     </row>
-    <row r="52" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B52" s="7"/>
       <c r="D52" t="s">
         <v>270</v>
@@ -11153,7 +11153,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="53" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B53" s="7">
         <v>6</v>
       </c>
@@ -11168,7 +11168,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="54" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B54" s="7"/>
       <c r="D54" s="63" t="s">
         <v>271</v>
@@ -11181,7 +11181,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="55" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B55" s="7"/>
       <c r="D55" t="s">
         <v>20</v>
@@ -11197,7 +11197,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="56" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B56" s="7">
         <v>7</v>
       </c>
@@ -11212,7 +11212,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="57" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B57" s="7"/>
       <c r="D57" s="63" t="s">
         <v>272</v>
@@ -11225,7 +11225,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="58" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B58" s="7"/>
       <c r="D58" s="63" t="s">
         <v>74</v>
@@ -11238,7 +11238,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="59" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B59" s="7"/>
       <c r="D59" s="63" t="s">
         <v>70</v>
@@ -11248,7 +11248,7 @@
       </c>
       <c r="F59" s="10"/>
     </row>
-    <row r="60" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B60" s="7"/>
       <c r="D60" s="63" t="s">
         <v>75</v>
@@ -11261,7 +11261,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="61" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B61" s="7"/>
       <c r="D61" s="63" t="s">
         <v>231</v>
@@ -11280,7 +11280,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="62" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B62" s="7"/>
       <c r="D62" s="63" t="s">
         <v>232</v>
@@ -11293,7 +11293,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="63" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B63" s="7"/>
       <c r="D63" s="63" t="s">
         <v>233</v>
@@ -11308,7 +11308,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="64" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B64" s="7"/>
       <c r="D64" s="63" t="s">
         <v>230</v>
@@ -11321,7 +11321,7 @@
         <v>3822364.73</v>
       </c>
     </row>
-    <row r="65" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B65" s="7">
         <v>8</v>
       </c>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="F65" s="10"/>
     </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B66" s="7"/>
       <c r="D66" s="63" t="s">
         <v>229</v>
@@ -11346,7 +11346,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="67" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B67" s="7"/>
       <c r="D67" t="s">
         <v>16</v>
@@ -11368,7 +11368,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="68" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B68" s="7">
         <v>9</v>
       </c>
@@ -11390,7 +11390,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B69" s="7"/>
       <c r="D69" s="63" t="s">
         <v>78</v>
@@ -11412,7 +11412,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="70" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B70" s="7"/>
       <c r="D70" s="63" t="s">
         <v>79</v>
@@ -11437,7 +11437,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="71" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B71" s="7">
         <v>10</v>
       </c>
@@ -11457,7 +11457,7 @@
       </c>
       <c r="L71" s="9"/>
     </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B72" s="7"/>
       <c r="D72" s="101" t="s">
         <v>80</v>
@@ -11479,7 +11479,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B73" s="7"/>
       <c r="D73" s="63" t="s">
         <v>81</v>
@@ -11501,7 +11501,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B74" s="7"/>
       <c r="D74" s="2" t="s">
         <v>82</v>
@@ -11520,7 +11520,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="75" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B75" s="7"/>
       <c r="D75" s="63" t="s">
         <v>83</v>
@@ -11539,7 +11539,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="76" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B76" s="7"/>
       <c r="D76" s="6" t="s">
         <v>17</v>
@@ -11557,7 +11557,7 @@
       <c r="J76" s="9"/>
       <c r="K76" s="9"/>
     </row>
-    <row r="77" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B77" s="7"/>
       <c r="D77" s="6" t="s">
         <v>84</v>
@@ -11569,7 +11569,7 @@
       <c r="J77" s="9"/>
       <c r="K77" s="9"/>
     </row>
-    <row r="78" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B78" s="7"/>
       <c r="D78" s="6" t="s">
         <v>39</v>
@@ -11581,7 +11581,7 @@
       <c r="J78" s="9"/>
       <c r="K78" s="9"/>
     </row>
-    <row r="79" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B79" s="7"/>
       <c r="D79" s="81" t="s">
         <v>20</v>
@@ -11595,7 +11595,7 @@
       <c r="J79" s="9"/>
       <c r="K79" s="9"/>
     </row>
-    <row r="80" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B80" s="7" t="s">
         <v>20</v>
       </c>
@@ -11611,7 +11611,7 @@
       <c r="J80" s="9"/>
       <c r="K80" s="9"/>
     </row>
-    <row r="81" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B81" s="7"/>
       <c r="D81" s="97"/>
       <c r="E81" s="14">
@@ -11623,7 +11623,7 @@
       <c r="J81" s="9"/>
       <c r="K81" s="9"/>
     </row>
-    <row r="82" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B82" s="7" t="s">
         <v>20</v>
       </c>
@@ -11638,7 +11638,7 @@
       <c r="J82" s="9"/>
       <c r="K82" s="9"/>
     </row>
-    <row r="83" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B83" s="7"/>
       <c r="D83" s="106" t="s">
         <v>85</v>
@@ -11652,7 +11652,7 @@
       <c r="J83" s="9"/>
       <c r="K83" s="9"/>
     </row>
-    <row r="84" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B84" s="7"/>
       <c r="D84" s="58" t="s">
         <v>88</v>
@@ -11667,7 +11667,7 @@
       <c r="J84" s="9"/>
       <c r="K84" s="9"/>
     </row>
-    <row r="85" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B85" s="7"/>
       <c r="D85" s="58" t="s">
         <v>89</v>
@@ -11681,7 +11681,7 @@
       </c>
       <c r="K85" s="9"/>
     </row>
-    <row r="86" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B86" s="7"/>
       <c r="D86" s="58" t="s">
         <v>274</v>
@@ -11695,7 +11695,7 @@
       </c>
       <c r="K86" s="9"/>
     </row>
-    <row r="87" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B87" s="7"/>
       <c r="D87" s="58" t="s">
         <v>90</v>
@@ -11709,7 +11709,7 @@
       </c>
       <c r="K87" s="9"/>
     </row>
-    <row r="88" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B88" s="7"/>
       <c r="D88" s="58" t="s">
         <v>91</v>
@@ -11728,7 +11728,7 @@
       </c>
       <c r="K88" s="9"/>
     </row>
-    <row r="89" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B89" s="7"/>
       <c r="D89" s="106" t="s">
         <v>78</v>
@@ -11740,7 +11740,7 @@
       </c>
       <c r="K89" s="9"/>
     </row>
-    <row r="90" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B90" s="7"/>
       <c r="D90" s="58" t="s">
         <v>92</v>
@@ -11754,7 +11754,7 @@
       </c>
       <c r="K90" s="9"/>
     </row>
-    <row r="91" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B91" s="7"/>
       <c r="D91" s="58" t="s">
         <v>93</v>
@@ -11768,7 +11768,7 @@
       </c>
       <c r="K91" s="9"/>
     </row>
-    <row r="92" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B92" s="7"/>
       <c r="D92" s="58" t="s">
         <v>94</v>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="K92" s="9"/>
     </row>
-    <row r="93" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B93" s="7"/>
       <c r="D93" s="58" t="s">
         <v>95</v>
@@ -11798,7 +11798,7 @@
       </c>
       <c r="K93" s="9"/>
     </row>
-    <row r="94" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B94" s="7"/>
       <c r="D94" s="58" t="s">
         <v>91</v>
@@ -11820,7 +11820,7 @@
       </c>
       <c r="K94" s="9"/>
     </row>
-    <row r="95" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B95" s="7" t="s">
         <v>20</v>
       </c>
@@ -11836,7 +11836,7 @@
       </c>
       <c r="K95" s="9"/>
     </row>
-    <row r="96" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B96" s="7"/>
       <c r="D96" s="96" t="s">
         <v>88</v>
@@ -11850,7 +11850,7 @@
       </c>
       <c r="K96" s="9"/>
     </row>
-    <row r="97" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B97" s="7"/>
       <c r="D97" s="96" t="s">
         <v>93</v>
@@ -11864,7 +11864,7 @@
       </c>
       <c r="K97" s="9"/>
     </row>
-    <row r="98" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B98" s="7"/>
       <c r="D98" s="96" t="s">
         <v>94</v>
@@ -11878,7 +11878,7 @@
       </c>
       <c r="K98" s="9"/>
     </row>
-    <row r="99" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B99" s="7"/>
       <c r="D99" s="96" t="s">
         <v>95</v>
@@ -11893,7 +11893,7 @@
       <c r="J99" s="9"/>
       <c r="K99" s="9"/>
     </row>
-    <row r="100" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B100" s="7"/>
       <c r="D100" s="96" t="s">
         <v>275</v>
@@ -11905,7 +11905,7 @@
       <c r="J100" s="9"/>
       <c r="K100" s="9"/>
     </row>
-    <row r="101" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B101" s="7"/>
       <c r="D101" s="96" t="s">
         <v>91</v>
@@ -11923,7 +11923,7 @@
       <c r="J101" s="9"/>
       <c r="K101" s="9"/>
     </row>
-    <row r="102" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B102" s="7"/>
       <c r="D102" s="4" t="s">
         <v>96</v>
@@ -11941,7 +11941,7 @@
       <c r="J102" s="9"/>
       <c r="K102" s="9"/>
     </row>
-    <row r="103" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B103" s="7"/>
       <c r="D103" s="113" t="s">
         <v>97</v>
@@ -11953,7 +11953,7 @@
       <c r="J103" s="9"/>
       <c r="K103" s="9"/>
     </row>
-    <row r="104" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B104" s="7"/>
       <c r="D104" s="113" t="s">
         <v>86</v>
@@ -11970,7 +11970,7 @@
       <c r="J104" s="9"/>
       <c r="K104" s="9"/>
     </row>
-    <row r="105" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B105" s="7"/>
       <c r="D105" s="113" t="s">
         <v>98</v>
@@ -11982,7 +11982,7 @@
       <c r="J105" s="9"/>
       <c r="K105" s="9"/>
     </row>
-    <row r="106" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B106" s="7"/>
       <c r="D106" s="113" t="s">
         <v>91</v>
@@ -11997,7 +11997,7 @@
       <c r="J106" s="9"/>
       <c r="K106" s="9"/>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B107"/>
       <c r="F107"/>
       <c r="G107" s="12" t="s">
@@ -12006,7 +12006,7 @@
       <c r="J107" s="9"/>
       <c r="K107" s="9"/>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>99</v>
       </c>
@@ -12018,7 +12018,7 @@
       <c r="J108" s="9"/>
       <c r="K108" s="9"/>
     </row>
-    <row r="109" spans="1:11" ht="18" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>100</v>
       </c>
@@ -12031,7 +12031,7 @@
       <c r="J109" s="9"/>
       <c r="K109" s="9"/>
     </row>
-    <row r="110" spans="1:11" ht="18" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B110" s="3"/>
       <c r="D110" s="40"/>
       <c r="E110" s="12"/>
@@ -12041,7 +12041,7 @@
       <c r="J110" s="9"/>
       <c r="K110" s="9"/>
     </row>
-    <row r="111" spans="1:11" ht="18" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A111" s="115" t="s">
         <v>101</v>
       </c>
@@ -12054,7 +12054,7 @@
       <c r="J111" s="9"/>
       <c r="K111" s="9"/>
     </row>
-    <row r="112" spans="1:11" ht="18" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>102</v>
       </c>
@@ -12067,7 +12067,7 @@
       <c r="J112" s="9"/>
       <c r="K112" s="9"/>
     </row>
-    <row r="113" spans="1:11" ht="18" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>103</v>
       </c>
@@ -12081,7 +12081,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="114" spans="1:11" ht="18" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>241</v>
       </c>
@@ -12095,7 +12095,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="115" spans="1:11" ht="18" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>104</v>
       </c>
@@ -12111,7 +12111,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="116" spans="1:11" ht="18" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>105</v>
       </c>
@@ -12122,7 +12122,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="117" spans="1:11" ht="18" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>106</v>
       </c>
@@ -12130,7 +12130,7 @@
       <c r="D117" s="40"/>
       <c r="E117" s="12"/>
     </row>
-    <row r="118" spans="1:11" ht="18" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>243</v>
       </c>
@@ -12138,7 +12138,7 @@
       <c r="D118" s="40"/>
       <c r="E118" s="12"/>
     </row>
-    <row r="119" spans="1:11" ht="18" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>242</v>
       </c>
@@ -12146,7 +12146,7 @@
       <c r="D119" s="40"/>
       <c r="E119" s="12"/>
     </row>
-    <row r="120" spans="1:11" ht="18" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>24</v>
       </c>
@@ -12156,7 +12156,7 @@
       </c>
       <c r="E120" s="12"/>
     </row>
-    <row r="121" spans="1:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>105</v>
       </c>
@@ -12164,14 +12164,14 @@
       <c r="D121" s="40"/>
       <c r="E121" s="12"/>
     </row>
-    <row r="122" spans="1:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B122" s="3"/>
       <c r="D122" s="117" t="s">
         <v>107</v>
       </c>
       <c r="E122" s="12"/>
     </row>
-    <row r="123" spans="1:11" ht="18" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>108</v>
       </c>
@@ -12179,7 +12179,7 @@
       <c r="D123" s="116"/>
       <c r="E123" s="12"/>
     </row>
-    <row r="124" spans="1:11" ht="18" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>109</v>
       </c>
@@ -12187,7 +12187,7 @@
       <c r="D124" s="116"/>
       <c r="E124" s="12"/>
     </row>
-    <row r="125" spans="1:11" ht="18" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>110</v>
       </c>
@@ -12195,7 +12195,7 @@
       <c r="D125" s="116"/>
       <c r="E125" s="12"/>
     </row>
-    <row r="126" spans="1:11" ht="18" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>111</v>
       </c>
@@ -12203,12 +12203,12 @@
       <c r="D126" s="116"/>
       <c r="E126" s="12"/>
     </row>
-    <row r="127" spans="1:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B127" s="3"/>
       <c r="D127" s="116"/>
       <c r="E127" s="12"/>
     </row>
-    <row r="128" spans="1:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A128" s="121" t="s">
         <v>112</v>
       </c>
@@ -12218,7 +12218,7 @@
       <c r="E128" s="124"/>
       <c r="F128" s="125"/>
     </row>
-    <row r="129" spans="1:6" ht="18" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A129" s="118" t="s">
         <v>113</v>
       </c>
@@ -12228,7 +12228,7 @@
       <c r="E129" s="120"/>
       <c r="F129" s="120"/>
     </row>
-    <row r="130" spans="1:6" ht="18" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A130" s="118" t="s">
         <v>114</v>
       </c>
@@ -12238,7 +12238,7 @@
       <c r="E130" s="120"/>
       <c r="F130" s="120"/>
     </row>
-    <row r="131" spans="1:6" ht="18" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A131" s="118" t="s">
         <v>115</v>
       </c>
@@ -12248,7 +12248,7 @@
       <c r="E131" s="120"/>
       <c r="F131" s="120"/>
     </row>
-    <row r="132" spans="1:6" ht="18" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A132" s="118" t="s">
         <v>116</v>
       </c>
@@ -12258,7 +12258,7 @@
       <c r="E132" s="120"/>
       <c r="F132" s="120"/>
     </row>
-    <row r="133" spans="1:6" ht="18" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A133" s="118" t="s">
         <v>117</v>
       </c>
@@ -12268,7 +12268,7 @@
       <c r="E133" s="120"/>
       <c r="F133" s="120"/>
     </row>
-    <row r="134" spans="1:6" ht="18" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A134" s="118" t="s">
         <v>118</v>
       </c>
@@ -12278,7 +12278,7 @@
       <c r="E134" s="120"/>
       <c r="F134" s="120"/>
     </row>
-    <row r="135" spans="1:6" ht="18" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A135" s="118" t="s">
         <v>119</v>
       </c>
@@ -12288,7 +12288,7 @@
       <c r="E135" s="120"/>
       <c r="F135" s="120"/>
     </row>
-    <row r="136" spans="1:6" ht="18" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A136" s="118" t="s">
         <v>120</v>
       </c>
@@ -12298,7 +12298,7 @@
       <c r="E136" s="120"/>
       <c r="F136" s="120"/>
     </row>
-    <row r="137" spans="1:6" ht="18" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A137" s="118" t="s">
         <v>254</v>
       </c>
@@ -12308,7 +12308,7 @@
       <c r="E137" s="120"/>
       <c r="F137" s="120"/>
     </row>
-    <row r="138" spans="1:6" ht="18" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A138" s="118" t="s">
         <v>121</v>
       </c>
@@ -12318,7 +12318,7 @@
       <c r="E138" s="120"/>
       <c r="F138" s="120"/>
     </row>
-    <row r="139" spans="1:6" ht="18" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A139" s="118" t="s">
         <v>122</v>
       </c>
@@ -12328,7 +12328,7 @@
       <c r="E139" s="120"/>
       <c r="F139" s="120"/>
     </row>
-    <row r="140" spans="1:6" ht="18" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A140" s="118" t="s">
         <v>123</v>
       </c>
@@ -12338,7 +12338,7 @@
       <c r="E140" s="120"/>
       <c r="F140" s="120"/>
     </row>
-    <row r="141" spans="1:6" ht="18" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A141" s="118"/>
       <c r="B141" s="118"/>
       <c r="C141" s="118"/>
@@ -12346,63 +12346,63 @@
       <c r="E141" s="120"/>
       <c r="F141" s="120"/>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>45</v>
       </c>
       <c r="B142" s="3"/>
       <c r="F142"/>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>30</v>
       </c>
       <c r="B143" s="3"/>
       <c r="F143"/>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>31</v>
       </c>
       <c r="B144" s="3"/>
       <c r="F144"/>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>32</v>
       </c>
       <c r="B145" s="3"/>
       <c r="F145"/>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>33</v>
       </c>
       <c r="B146" s="3"/>
       <c r="F146"/>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>34</v>
       </c>
       <c r="B147" s="3"/>
       <c r="F147"/>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>35</v>
       </c>
       <c r="B148" s="3"/>
       <c r="F148"/>
     </row>
-    <row r="149" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>36</v>
       </c>
       <c r="B149" s="3"/>
       <c r="F149"/>
     </row>
-    <row r="150" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A150" s="59" t="s">
         <v>47</v>
       </c>
@@ -12412,7 +12412,7 @@
       <c r="E150" s="90"/>
       <c r="F150" s="91"/>
     </row>
-    <row r="151" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A151" s="59" t="s">
         <v>48</v>
       </c>
@@ -12422,11 +12422,11 @@
       <c r="E151" s="90"/>
       <c r="F151" s="91"/>
     </row>
-    <row r="152" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B152"/>
       <c r="F152"/>
     </row>
-    <row r="153" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="153" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A153" s="136" t="s">
         <v>278</v>
       </c>
@@ -12436,7 +12436,7 @@
       <c r="E153" s="137"/>
       <c r="F153" s="138"/>
     </row>
-    <row r="154" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="154" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A154" s="136" t="s">
         <v>276</v>
       </c>
@@ -12446,7 +12446,7 @@
       <c r="E154" s="137"/>
       <c r="F154" s="138"/>
     </row>
-    <row r="155" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="155" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A155" s="139" t="s">
         <v>277</v>
       </c>
@@ -12456,126 +12456,126 @@
       <c r="E155" s="9"/>
       <c r="F155" s="9"/>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B156"/>
       <c r="F156"/>
     </row>
-    <row r="157" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B157"/>
       <c r="F157"/>
     </row>
-    <row r="158" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="158" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B158"/>
       <c r="D158" s="142" t="s">
         <v>279</v>
       </c>
       <c r="F158"/>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B159"/>
       <c r="F159"/>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B160"/>
       <c r="F160"/>
     </row>
-    <row r="161" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="161" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B161"/>
       <c r="F161"/>
     </row>
-    <row r="162" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="162" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B162"/>
       <c r="F162"/>
     </row>
-    <row r="163" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="163" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B163"/>
       <c r="F163"/>
     </row>
-    <row r="164" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="164" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B164"/>
       <c r="F164"/>
     </row>
-    <row r="165" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="165" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B165"/>
       <c r="F165"/>
     </row>
-    <row r="166" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="166" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B166"/>
       <c r="F166"/>
     </row>
-    <row r="167" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="167" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B167"/>
       <c r="F167"/>
     </row>
-    <row r="168" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="168" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B168"/>
       <c r="F168"/>
     </row>
-    <row r="169" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="169" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B169"/>
       <c r="F169"/>
     </row>
-    <row r="170" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="170" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B170"/>
       <c r="F170"/>
     </row>
-    <row r="171" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="171" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B171"/>
       <c r="F171"/>
     </row>
-    <row r="172" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="172" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B172"/>
       <c r="F172"/>
     </row>
-    <row r="180" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="180" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E180" s="93"/>
     </row>
-    <row r="181" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="181" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E181" s="93"/>
     </row>
-    <row r="182" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="182" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E182" s="93"/>
     </row>
-    <row r="183" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="183" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E183" s="93"/>
     </row>
-    <row r="184" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="184" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E184" s="93"/>
     </row>
-    <row r="185" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="185" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E185" s="93"/>
     </row>
-    <row r="186" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="186" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E186" s="93"/>
     </row>
-    <row r="187" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="187" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E187" s="93"/>
     </row>
-    <row r="188" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="188" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E188" s="93"/>
     </row>
-    <row r="189" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="189" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E189" s="93"/>
     </row>
-    <row r="190" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="190" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E190" s="93"/>
     </row>
-    <row r="191" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="191" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E191" s="93"/>
     </row>
-    <row r="192" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="192" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E192" s="93"/>
     </row>
-    <row r="193" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="193" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E193" s="93"/>
     </row>
-    <row r="194" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="194" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E194" s="93"/>
     </row>
-    <row r="195" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="195" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E195" s="93"/>
     </row>
-    <row r="198" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="198" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E198" s="93"/>
     </row>
   </sheetData>
@@ -12594,46 +12594,46 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q121"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.88671875" customWidth="1"/>
-    <col min="2" max="2" width="34.109375" customWidth="1"/>
-    <col min="3" max="3" width="5.6640625" customWidth="1"/>
+    <col min="1" max="1" width="5.85546875" customWidth="1"/>
+    <col min="2" max="2" width="34.140625" customWidth="1"/>
+    <col min="3" max="3" width="5.7109375" customWidth="1"/>
     <col min="4" max="4" width="9" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="5.6640625" customWidth="1"/>
-    <col min="6" max="6" width="12.6640625" customWidth="1"/>
+    <col min="5" max="5" width="5.7109375" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
-    <col min="8" max="8" width="12.5546875" customWidth="1"/>
-    <col min="9" max="9" width="13.109375" customWidth="1"/>
-    <col min="10" max="10" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.33203125" customWidth="1"/>
-    <col min="12" max="12" width="13.6640625" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.88671875" customWidth="1"/>
+    <col min="8" max="8" width="12.5703125" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" customWidth="1"/>
+    <col min="10" max="10" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.28515625" customWidth="1"/>
+    <col min="12" max="12" width="13.7109375" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="391" t="s">
+    <row r="1" spans="1:17" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B1" s="392" t="s">
         <v>124</v>
       </c>
-      <c r="C1" s="392"/>
-      <c r="D1" s="392"/>
-      <c r="E1" s="392"/>
-      <c r="F1" s="392"/>
-      <c r="G1" s="392"/>
-      <c r="H1" s="392"/>
-      <c r="I1" s="392"/>
-      <c r="J1" s="392"/>
-      <c r="K1" s="392"/>
-      <c r="L1" s="392"/>
-      <c r="M1" s="392"/>
-      <c r="N1" s="392"/>
-      <c r="O1" s="393"/>
+      <c r="C1" s="393"/>
+      <c r="D1" s="393"/>
+      <c r="E1" s="393"/>
+      <c r="F1" s="393"/>
+      <c r="G1" s="393"/>
+      <c r="H1" s="393"/>
+      <c r="I1" s="393"/>
+      <c r="J1" s="393"/>
+      <c r="K1" s="393"/>
+      <c r="L1" s="393"/>
+      <c r="M1" s="393"/>
+      <c r="N1" s="393"/>
+      <c r="O1" s="394"/>
       <c r="P1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="I2" t="s">
         <v>18</v>
       </c>
@@ -12644,16 +12644,16 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="394" t="s">
+    <row r="3" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="395" t="s">
         <v>273</v>
       </c>
-      <c r="C3" s="395"/>
-      <c r="D3" s="395"/>
-      <c r="E3" s="395"/>
-      <c r="F3" s="395"/>
-      <c r="G3" s="395"/>
-      <c r="H3" s="395"/>
+      <c r="C3" s="396"/>
+      <c r="D3" s="396"/>
+      <c r="E3" s="396"/>
+      <c r="F3" s="396"/>
+      <c r="G3" s="396"/>
+      <c r="H3" s="396"/>
       <c r="I3" s="31">
         <v>6905337</v>
       </c>
@@ -12667,8 +12667,8 @@
         <v>4000000</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="5" spans="1:17" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="5" spans="1:17" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="19" t="s">
         <v>10</v>
       </c>
@@ -12715,7 +12715,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7"/>
       <c r="B6" s="46"/>
       <c r="C6" s="46"/>
@@ -12732,7 +12732,7 @@
       <c r="N6" s="46"/>
       <c r="O6" s="47"/>
     </row>
-    <row r="7" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="48">
         <v>1</v>
       </c>
@@ -12787,7 +12787,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="20">
         <v>2</v>
       </c>
@@ -12836,7 +12836,7 @@
       </c>
       <c r="P8" s="65"/>
     </row>
-    <row r="9" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="20">
         <v>3</v>
       </c>
@@ -12888,7 +12888,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="20">
         <v>4</v>
       </c>
@@ -12940,7 +12940,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="20">
         <v>5</v>
       </c>
@@ -12992,7 +12992,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="20">
         <v>6</v>
       </c>
@@ -13047,7 +13047,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="20">
         <v>7</v>
       </c>
@@ -13102,7 +13102,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="20">
         <v>8</v>
       </c>
@@ -13157,7 +13157,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="20">
         <v>9</v>
       </c>
@@ -13209,7 +13209,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="20">
         <v>10</v>
       </c>
@@ -13261,7 +13261,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="20">
         <v>11</v>
       </c>
@@ -13313,7 +13313,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="20">
         <v>12</v>
       </c>
@@ -13364,7 +13364,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="20">
         <v>13</v>
       </c>
@@ -13416,7 +13416,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="20">
         <v>14</v>
       </c>
@@ -13468,7 +13468,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="20">
         <v>15</v>
       </c>
@@ -13520,7 +13520,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="20">
         <v>16</v>
       </c>
@@ -13571,7 +13571,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="20">
         <v>17</v>
       </c>
@@ -13623,7 +13623,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="20">
         <v>18</v>
       </c>
@@ -13675,7 +13675,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="20">
         <v>19</v>
       </c>
@@ -13726,7 +13726,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="20">
         <v>20</v>
       </c>
@@ -13780,7 +13780,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="20">
         <v>21</v>
       </c>
@@ -13832,7 +13832,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="20">
         <v>22</v>
       </c>
@@ -13884,7 +13884,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="20">
         <v>23</v>
       </c>
@@ -13936,7 +13936,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="20">
         <v>24</v>
       </c>
@@ -13990,7 +13990,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="20">
         <v>25</v>
       </c>
@@ -14042,7 +14042,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="20">
         <v>26</v>
       </c>
@@ -14093,7 +14093,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="20">
         <v>27</v>
       </c>
@@ -14145,7 +14145,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="20">
         <v>28</v>
       </c>
@@ -14199,7 +14199,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="66">
         <v>29</v>
       </c>
@@ -14250,7 +14250,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="71">
         <v>30</v>
       </c>
@@ -14300,7 +14300,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="37" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="71">
         <v>31</v>
       </c>
@@ -14350,7 +14350,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="71">
         <v>32</v>
       </c>
@@ -14400,7 +14400,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="71">
         <v>33</v>
       </c>
@@ -14450,7 +14450,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="71">
         <v>34</v>
       </c>
@@ -14500,7 +14500,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="71">
         <v>35</v>
       </c>
@@ -14553,7 +14553,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="42" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="71">
         <v>36</v>
       </c>
@@ -14602,7 +14602,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="43" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="71">
         <v>37</v>
       </c>
@@ -14652,7 +14652,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="71">
         <v>38</v>
       </c>
@@ -14702,7 +14702,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="71">
         <v>39</v>
       </c>
@@ -14752,7 +14752,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="46" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="71">
         <v>40</v>
       </c>
@@ -14802,7 +14802,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="47" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="71">
         <v>41</v>
       </c>
@@ -14852,7 +14852,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="71">
         <v>42</v>
       </c>
@@ -14904,7 +14904,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="71">
         <v>43</v>
       </c>
@@ -14953,7 +14953,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="71">
         <v>44</v>
       </c>
@@ -15002,7 +15002,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="71">
         <v>45</v>
       </c>
@@ -15052,7 +15052,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="52" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="71">
         <v>46</v>
       </c>
@@ -15102,7 +15102,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="53" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="71">
         <v>47</v>
       </c>
@@ -15151,7 +15151,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="54" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="71">
         <v>48</v>
       </c>
@@ -15201,7 +15201,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="55" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="71">
         <v>49</v>
       </c>
@@ -15251,7 +15251,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="71">
         <v>50</v>
       </c>
@@ -15301,7 +15301,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="57" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="71">
         <v>51</v>
       </c>
@@ -15351,7 +15351,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="71">
         <v>52</v>
       </c>
@@ -15401,7 +15401,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="71">
         <v>53</v>
       </c>
@@ -15454,7 +15454,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="71">
         <v>54</v>
       </c>
@@ -15504,7 +15504,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="71">
         <v>55</v>
       </c>
@@ -15554,7 +15554,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="71">
         <v>56</v>
       </c>
@@ -15604,7 +15604,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="71">
         <v>57</v>
       </c>
@@ -15657,7 +15657,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="71">
         <v>58</v>
       </c>
@@ -15707,7 +15707,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="65" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="71">
         <v>59</v>
       </c>
@@ -15760,7 +15760,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="71">
         <v>60</v>
       </c>
@@ -15813,7 +15813,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="67" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="71">
         <v>61</v>
       </c>
@@ -15863,7 +15863,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="68" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="71">
         <v>62</v>
       </c>
@@ -15913,7 +15913,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="69" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="71">
         <v>63</v>
       </c>
@@ -15963,7 +15963,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="70" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="126">
         <v>64</v>
       </c>
@@ -16013,7 +16013,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="71" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="71">
         <v>65</v>
       </c>
@@ -16061,7 +16061,7 @@
       </c>
       <c r="P71" s="65"/>
     </row>
-    <row r="72" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="71">
         <v>66</v>
       </c>
@@ -16111,7 +16111,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="73" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="71">
         <v>67</v>
       </c>
@@ -16161,7 +16161,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="71">
         <v>68</v>
       </c>
@@ -16208,7 +16208,7 @@
       </c>
       <c r="P74" s="65"/>
     </row>
-    <row r="75" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="71">
         <v>69</v>
       </c>
@@ -16258,7 +16258,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="71">
         <v>70</v>
       </c>
@@ -16305,7 +16305,7 @@
       </c>
       <c r="P76" s="65"/>
     </row>
-    <row r="77" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="71">
         <v>71</v>
       </c>
@@ -16355,7 +16355,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="71">
         <v>72</v>
       </c>
@@ -16404,7 +16404,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="71">
         <v>73</v>
       </c>
@@ -16454,7 +16454,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="71">
         <v>74</v>
       </c>
@@ -16501,7 +16501,7 @@
       </c>
       <c r="P80" s="65"/>
     </row>
-    <row r="81" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="71">
         <v>75</v>
       </c>
@@ -16551,7 +16551,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="82" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="71">
         <v>76</v>
       </c>
@@ -16601,7 +16601,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="83" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="71">
         <v>77</v>
       </c>
@@ -16651,7 +16651,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="84" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="71">
         <v>78</v>
       </c>
@@ -16699,7 +16699,7 @@
       </c>
       <c r="P84" s="65"/>
     </row>
-    <row r="85" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="71">
         <v>79</v>
       </c>
@@ -16749,7 +16749,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="86" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="71">
         <v>80</v>
       </c>
@@ -16799,7 +16799,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="87" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="71">
         <v>81</v>
       </c>
@@ -16849,7 +16849,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="88" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="71">
         <v>82</v>
       </c>
@@ -16899,7 +16899,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="89" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="71">
         <v>83</v>
       </c>
@@ -16949,7 +16949,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="90" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="71">
         <v>84</v>
       </c>
@@ -16999,7 +16999,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="91" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="71">
         <v>85</v>
       </c>
@@ -17049,7 +17049,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="92" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="71">
         <v>86</v>
       </c>
@@ -17099,7 +17099,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="93" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="71">
         <v>87</v>
       </c>
@@ -17149,7 +17149,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="94" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="71">
         <v>88</v>
       </c>
@@ -17199,7 +17199,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="95" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A95" s="71">
         <v>89</v>
       </c>
@@ -17249,7 +17249,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="96" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="71">
         <v>90</v>
       </c>
@@ -17300,7 +17300,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="97" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" s="71">
         <v>91</v>
       </c>
@@ -17352,7 +17352,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="98" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="71">
         <v>92</v>
       </c>
@@ -17404,7 +17404,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="99" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="71">
         <v>93</v>
       </c>
@@ -17456,7 +17456,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="100" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="71">
         <v>94</v>
       </c>
@@ -17508,7 +17508,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="101" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" s="71">
         <v>95</v>
       </c>
@@ -17560,7 +17560,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="102" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="71">
         <v>96</v>
       </c>
@@ -17612,7 +17612,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="103" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="71">
         <v>97</v>
       </c>
@@ -17664,7 +17664,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="104" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" s="71">
         <v>98</v>
       </c>
@@ -17716,7 +17716,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="105" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A105" s="71">
         <v>99</v>
       </c>
@@ -17768,7 +17768,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="106" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A106" s="71">
         <v>100</v>
       </c>
@@ -17817,7 +17817,7 @@
       </c>
       <c r="P106" s="65"/>
     </row>
-    <row r="107" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A107" s="71">
         <v>101</v>
       </c>
@@ -17869,7 +17869,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A108" s="71">
         <v>102</v>
       </c>
@@ -17921,7 +17921,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="109" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="71">
         <v>103</v>
       </c>
@@ -17973,7 +17973,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="110" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
         <v>20</v>
       </c>
@@ -18033,17 +18033,17 @@
         <v>20</v>
       </c>
     </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C111" s="396" t="s">
-        <v>20</v>
-      </c>
-      <c r="D111" s="396"/>
+    <row r="111" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C111" s="397" t="s">
+        <v>20</v>
+      </c>
+      <c r="D111" s="397"/>
       <c r="E111" s="99"/>
       <c r="G111" s="12" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="112" spans="1:16" ht="18" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
       <c r="C112" s="3"/>
       <c r="D112" s="3"/>
       <c r="E112" s="3"/>
@@ -18053,7 +18053,7 @@
       <c r="K112" s="40"/>
       <c r="L112" s="40"/>
     </row>
-    <row r="113" spans="1:16" ht="18" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A113" s="40" t="s">
         <v>22</v>
       </c>
@@ -18077,7 +18077,7 @@
       <c r="N113" s="40"/>
       <c r="O113" s="40"/>
     </row>
-    <row r="114" spans="1:16" ht="18" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A114" s="78" t="s">
         <v>23</v>
       </c>
@@ -18108,7 +18108,7 @@
       </c>
       <c r="O114" s="9"/>
     </row>
-    <row r="115" spans="1:16" ht="18" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A115" s="78" t="s">
         <v>24</v>
       </c>
@@ -18129,7 +18129,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="116" spans="1:16" ht="18" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:16" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A116" s="78" t="s">
         <v>25</v>
       </c>
@@ -18151,7 +18151,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="117" spans="1:16" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A117" s="78" t="s">
         <v>46</v>
       </c>
@@ -18176,7 +18176,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="118" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D118" s="29"/>
       <c r="E118" s="29"/>
       <c r="J118" s="131">
@@ -18195,7 +18195,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:16" x14ac:dyDescent="0.25">
       <c r="J119" s="131">
         <v>45707</v>
       </c>
@@ -18206,7 +18206,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:16" x14ac:dyDescent="0.25">
       <c r="J120" s="131" t="s">
         <v>20</v>
       </c>
@@ -18217,7 +18217,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B121" s="3"/>
       <c r="C121" s="3"/>
       <c r="D121" s="3"/>
